--- a/XAUUSD_Predictivo.xlsx
+++ b/XAUUSD_Predictivo.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E395"/>
+  <dimension ref="A1:E397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6641 +449,6675 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45900</v>
+        <v>45916</v>
       </c>
       <c r="B2" t="n">
-        <v>3558.525687697997</v>
+        <v>3679.98083328355</v>
       </c>
       <c r="C2" t="n">
-        <v>3401.476458221041</v>
+        <v>3504.158284557758</v>
       </c>
       <c r="D2" t="n">
-        <v>3730.815712447408</v>
+        <v>3845.548265381387</v>
       </c>
       <c r="E2" t="n">
-        <v>3462.173828125</v>
+        <v>3706.650146484375</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45901</v>
+        <v>45917</v>
       </c>
       <c r="B3" t="n">
-        <v>3579.670689885649</v>
+        <v>3686.017184185088</v>
       </c>
       <c r="C3" t="n">
-        <v>3407.849712493656</v>
+        <v>3530.527270426483</v>
       </c>
       <c r="D3" t="n">
-        <v>3765.695215589183</v>
+        <v>3860.742222606353</v>
       </c>
       <c r="E3" t="n">
-        <v>3502.559326171875</v>
+        <v>3674.03955078125</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45902</v>
+        <v>45918</v>
       </c>
       <c r="B4" t="n">
-        <v>3589.648386628995</v>
+        <v>3669.516951580054</v>
       </c>
       <c r="C4" t="n">
-        <v>3429.480088388712</v>
+        <v>3500.862663587928</v>
       </c>
       <c r="D4" t="n">
-        <v>3771.391011132261</v>
+        <v>3841.921362598886</v>
       </c>
       <c r="E4" t="n">
-        <v>3549.216552734375</v>
+        <v>3646.354248046875</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45903</v>
+        <v>45919</v>
       </c>
       <c r="B5" t="n">
-        <v>3607.806012890605</v>
+        <v>3662.327410083399</v>
       </c>
       <c r="C5" t="n">
-        <v>3438.444016780248</v>
+        <v>3489.980836353495</v>
       </c>
       <c r="D5" t="n">
-        <v>3790.165999059092</v>
+        <v>3839.363610979202</v>
       </c>
       <c r="E5" t="n">
-        <v>3575.163818359375</v>
+        <v>3690.746337890625</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45904</v>
+        <v>45920</v>
       </c>
       <c r="B6" t="n">
-        <v>3601.637469512906</v>
+        <v>3666.149500847964</v>
       </c>
       <c r="C6" t="n">
-        <v>3418.776217891483</v>
+        <v>3501.820914968039</v>
       </c>
       <c r="D6" t="n">
-        <v>3775.060996151919</v>
+        <v>3841.17504734113</v>
       </c>
       <c r="E6" t="n">
-        <v>3560.2392578125</v>
+        <v>3688.934326171875</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45905</v>
+        <v>45921</v>
       </c>
       <c r="B7" t="n">
-        <v>3600.379342963802</v>
+        <v>3668.518898794471</v>
       </c>
       <c r="C7" t="n">
-        <v>3429.968081737831</v>
+        <v>3492.244451335695</v>
       </c>
       <c r="D7" t="n">
-        <v>3766.550307861392</v>
+        <v>3840.804174300255</v>
       </c>
       <c r="E7" t="n">
-        <v>3593.828857421875</v>
+        <v>3693.28857421875</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45906</v>
+        <v>45922</v>
       </c>
       <c r="B8" t="n">
-        <v>3608.402568376251</v>
+        <v>3691.092875275434</v>
       </c>
       <c r="C8" t="n">
-        <v>3424.249007421674</v>
+        <v>3527.280622450407</v>
       </c>
       <c r="D8" t="n">
-        <v>3786.808025847033</v>
+        <v>3854.303618522702</v>
       </c>
       <c r="E8" t="n">
-        <v>3627.05126953125</v>
+        <v>3761.20703125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45907</v>
+        <v>45923</v>
       </c>
       <c r="B9" t="n">
-        <v>3605.199975931101</v>
+        <v>3697.102745825419</v>
       </c>
       <c r="C9" t="n">
-        <v>3440.881128050788</v>
+        <v>3542.746299166445</v>
       </c>
       <c r="D9" t="n">
-        <v>3771.460230621731</v>
+        <v>3871.104148597615</v>
       </c>
       <c r="E9" t="n">
-        <v>3603.125</v>
+        <v>3774.19580078125</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45908</v>
+        <v>45924</v>
       </c>
       <c r="B10" t="n">
-        <v>3617.630588570068</v>
+        <v>3726.892084549927</v>
       </c>
       <c r="C10" t="n">
-        <v>3448.414806181216</v>
+        <v>3567.951078819339</v>
       </c>
       <c r="D10" t="n">
-        <v>3793.260994758205</v>
+        <v>3899.047198318294</v>
       </c>
       <c r="E10" t="n">
-        <v>3639.5869140625</v>
+        <v>3757.54638671875</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45909</v>
+        <v>45925</v>
       </c>
       <c r="B11" t="n">
-        <v>3619.720682674981</v>
+        <v>3733.890231437271</v>
       </c>
       <c r="C11" t="n">
-        <v>3453.280248171561</v>
+        <v>3554.097547658839</v>
       </c>
       <c r="D11" t="n">
-        <v>3779.98504345321</v>
+        <v>3899.645348453991</v>
       </c>
       <c r="E11" t="n">
-        <v>3643.721435546875</v>
+        <v>3755.103759765625</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45910</v>
+        <v>45926</v>
       </c>
       <c r="B12" t="n">
-        <v>3631.042545066654</v>
+        <v>3749.495818761786</v>
       </c>
       <c r="C12" t="n">
-        <v>3473.083360743701</v>
+        <v>3568.65979851777</v>
       </c>
       <c r="D12" t="n">
-        <v>3804.874785903724</v>
+        <v>3921.363645353184</v>
       </c>
       <c r="E12" t="n">
-        <v>3643.07958984375</v>
+        <v>3775.42431640625</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45911</v>
+        <v>45927</v>
       </c>
       <c r="B13" t="n">
-        <v>3619.297259095731</v>
+        <v>3774.973593058987</v>
       </c>
       <c r="C13" t="n">
-        <v>3443.287858790275</v>
+        <v>3610.31514695008</v>
       </c>
       <c r="D13" t="n">
-        <v>3780.266334509353</v>
+        <v>3941.963347560436</v>
       </c>
       <c r="E13" t="n">
-        <v>3633.432373046875</v>
+        <v>3776.893310546875</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45912</v>
+        <v>45928</v>
       </c>
       <c r="B14" t="n">
-        <v>3613.904242512138</v>
+        <v>3797.445527639396</v>
       </c>
       <c r="C14" t="n">
-        <v>3425.533188262515</v>
+        <v>3630.608660801517</v>
       </c>
       <c r="D14" t="n">
-        <v>3790.393643028039</v>
+        <v>3961.206249037003</v>
       </c>
       <c r="E14" t="n">
-        <v>3643.882080078125</v>
+        <v>3778.170654296875</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45913</v>
+        <v>45929</v>
       </c>
       <c r="B15" t="n">
-        <v>3619.386941296587</v>
+        <v>3838.187261945236</v>
       </c>
       <c r="C15" t="n">
-        <v>3440.952729131566</v>
+        <v>3660.330588193615</v>
       </c>
       <c r="D15" t="n">
-        <v>3792.337847000098</v>
+        <v>4018.659354507531</v>
       </c>
       <c r="E15" t="n">
-        <v>3639.729736328125</v>
+        <v>3848.826416015625</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45914</v>
+        <v>45930</v>
       </c>
       <c r="B16" t="n">
-        <v>3615.355108674831</v>
+        <v>3860.089405422192</v>
       </c>
       <c r="C16" t="n">
-        <v>3445.304555754973</v>
+        <v>3698.743939717142</v>
       </c>
       <c r="D16" t="n">
-        <v>3787.26071087767</v>
+        <v>4045.073155184002</v>
       </c>
       <c r="E16" t="n">
-        <v>3645.18603515625</v>
+        <v>3875.141357421875</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45915</v>
+        <v>45931</v>
       </c>
       <c r="B17" t="n">
-        <v>3628.744707325819</v>
+        <v>3903.203651774035</v>
       </c>
       <c r="C17" t="n">
-        <v>3449.968075918662</v>
+        <v>3738.357354264796</v>
       </c>
       <c r="D17" t="n">
-        <v>3801.084964066137</v>
+        <v>4086.38047529124</v>
       </c>
       <c r="E17" t="n">
-        <v>3685.96630859375</v>
+        <v>3874.288330078125</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45916</v>
+        <v>45932</v>
       </c>
       <c r="B18" t="n">
-        <v>3633.615594370357</v>
+        <v>3920.7230197826</v>
       </c>
       <c r="C18" t="n">
-        <v>3463.557368973966</v>
+        <v>3752.529874158814</v>
       </c>
       <c r="D18" t="n">
-        <v>3795.091757354255</v>
+        <v>4101.158778207985</v>
       </c>
       <c r="E18" t="n">
-        <v>3706.650146484375</v>
+        <v>3866.750244140625</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45917</v>
+        <v>45933</v>
       </c>
       <c r="B19" t="n">
-        <v>3649.528041204376</v>
+        <v>3943.870765813413</v>
       </c>
       <c r="C19" t="n">
-        <v>3466.256552239524</v>
+        <v>3775.534513491252</v>
       </c>
       <c r="D19" t="n">
-        <v>3804.236310703814</v>
+        <v>4113.282923596983</v>
       </c>
       <c r="E19" t="n">
-        <v>3674.03955078125</v>
+        <v>3886.2197265625</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45918</v>
+        <v>45934</v>
       </c>
       <c r="B20" t="n">
-        <v>3644.124507989913</v>
+        <v>3973.80109928985</v>
       </c>
       <c r="C20" t="n">
-        <v>3470.222539872567</v>
+        <v>3798.488927093038</v>
       </c>
       <c r="D20" t="n">
-        <v>3834.051350305549</v>
+        <v>4144.409050518306</v>
       </c>
       <c r="E20" t="n">
-        <v>3646.354248046875</v>
+        <v>3902.44921875</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45919</v>
+        <v>45935</v>
       </c>
       <c r="B21" t="n">
-        <v>3646.719447417671</v>
+        <v>3997.592590502234</v>
       </c>
       <c r="C21" t="n">
-        <v>3460.406757199452</v>
+        <v>3828.61582828885</v>
       </c>
       <c r="D21" t="n">
-        <v>3810.810604142648</v>
+        <v>4169.059241024563</v>
       </c>
       <c r="E21" t="n">
-        <v>3690.746337890625</v>
+        <v>3915.343017578125</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45920</v>
+        <v>45936</v>
       </c>
       <c r="B22" t="n">
-        <v>3661.686556957085</v>
+        <v>4036.545244356017</v>
       </c>
       <c r="C22" t="n">
-        <v>3487.476148113782</v>
+        <v>3869.01345597101</v>
       </c>
       <c r="D22" t="n">
-        <v>3830.603900645729</v>
+        <v>4219.819222719959</v>
       </c>
       <c r="E22" t="n">
-        <v>3688.934326171875</v>
+        <v>3984.27783203125</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45921</v>
+        <v>45937</v>
       </c>
       <c r="B23" t="n">
-        <v>3668.443885639426</v>
+        <v>4053.640759371051</v>
       </c>
       <c r="C23" t="n">
-        <v>3481.475249392978</v>
+        <v>3881.979892181364</v>
       </c>
       <c r="D23" t="n">
-        <v>3850.845203422782</v>
+        <v>4227.922060024126</v>
       </c>
       <c r="E23" t="n">
-        <v>3693.28857421875</v>
+        <v>4003.220703125</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45922</v>
+        <v>45938</v>
       </c>
       <c r="B24" t="n">
-        <v>3693.697773787797</v>
+        <v>4089.085946012002</v>
       </c>
       <c r="C24" t="n">
-        <v>3521.073924371917</v>
+        <v>3925.66849134036</v>
       </c>
       <c r="D24" t="n">
-        <v>3860.362334245047</v>
+        <v>4256.547988810617</v>
       </c>
       <c r="E24" t="n">
-        <v>3761.20703125</v>
+        <v>4033.29296875</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45923</v>
+        <v>45939</v>
       </c>
       <c r="B25" t="n">
-        <v>3711.245688245633</v>
+        <v>4096.288692123832</v>
       </c>
       <c r="C25" t="n">
-        <v>3543.124693880501</v>
+        <v>3924.443231215124</v>
       </c>
       <c r="D25" t="n">
-        <v>3898.857656638936</v>
+        <v>4265.5979388037</v>
       </c>
       <c r="E25" t="n">
-        <v>3774.19580078125</v>
+        <v>4002.012939453125</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45924</v>
+        <v>45940</v>
       </c>
       <c r="B26" t="n">
-        <v>3740.358875806195</v>
+        <v>4106.741136148163</v>
       </c>
       <c r="C26" t="n">
-        <v>3559.086954802953</v>
+        <v>3931.599986463362</v>
       </c>
       <c r="D26" t="n">
-        <v>3903.171769402541</v>
+        <v>4280.014196322201</v>
       </c>
       <c r="E26" t="n">
-        <v>3757.54638671875</v>
+        <v>3991.026611328125</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45925</v>
+        <v>45941</v>
       </c>
       <c r="B27" t="n">
-        <v>3748.371094159135</v>
+        <v>4121.91333501499</v>
       </c>
       <c r="C27" t="n">
-        <v>3583.527077979743</v>
+        <v>3949.380927729744</v>
       </c>
       <c r="D27" t="n">
-        <v>3909.830240085712</v>
+        <v>4284.66981690064</v>
       </c>
       <c r="E27" t="n">
-        <v>3755.103759765625</v>
+        <v>3996.272216796875</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45926</v>
+        <v>45942</v>
       </c>
       <c r="B28" t="n">
-        <v>3764.276010963131</v>
+        <v>4129.238505676614</v>
       </c>
       <c r="C28" t="n">
-        <v>3592.191662127321</v>
+        <v>3958.853264489142</v>
       </c>
       <c r="D28" t="n">
-        <v>3936.219093438773</v>
+        <v>4298.207169104555</v>
       </c>
       <c r="E28" t="n">
-        <v>3775.42431640625</v>
+        <v>4041.53369140625</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45927</v>
+        <v>45943</v>
       </c>
       <c r="B29" t="n">
-        <v>3792.122483491996</v>
+        <v>4150.401035957357</v>
       </c>
       <c r="C29" t="n">
-        <v>3618.345977704686</v>
+        <v>3991.099666982571</v>
       </c>
       <c r="D29" t="n">
-        <v>3973.86497906506</v>
+        <v>4325.129842951778</v>
       </c>
       <c r="E29" t="n">
-        <v>3776.893310546875</v>
+        <v>4144.38818359375</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45928</v>
+        <v>45944</v>
       </c>
       <c r="B30" t="n">
-        <v>3811.007905703797</v>
+        <v>4148.78702853277</v>
       </c>
       <c r="C30" t="n">
-        <v>3641.529649005026</v>
+        <v>3977.789855780652</v>
       </c>
       <c r="D30" t="n">
-        <v>3982.734459245533</v>
+        <v>4309.731383617989</v>
       </c>
       <c r="E30" t="n">
-        <v>3778.170654296875</v>
+        <v>4180.63134765625</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45929</v>
+        <v>45945</v>
       </c>
       <c r="B31" t="n">
-        <v>3847.330373218565</v>
+        <v>4165.01761448621</v>
       </c>
       <c r="C31" t="n">
-        <v>3680.348539063424</v>
+        <v>3991.804257396494</v>
       </c>
       <c r="D31" t="n">
-        <v>4020.92903102259</v>
+        <v>4329.587814944636</v>
       </c>
       <c r="E31" t="n">
-        <v>3848.826416015625</v>
+        <v>4241.47607421875</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45930</v>
+        <v>45946</v>
       </c>
       <c r="B32" t="n">
-        <v>3874.599499601625</v>
+        <v>4152.914696292678</v>
       </c>
       <c r="C32" t="n">
-        <v>3704.28568832775</v>
+        <v>3989.685685697978</v>
       </c>
       <c r="D32" t="n">
-        <v>4052.091367512406</v>
+        <v>4318.543028760267</v>
       </c>
       <c r="E32" t="n">
-        <v>3875.141357421875</v>
+        <v>4442.3642578125</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45931</v>
+        <v>45947</v>
       </c>
       <c r="B33" t="n">
-        <v>3911.826582728048</v>
+        <v>4144.374055233611</v>
       </c>
       <c r="C33" t="n">
-        <v>3751.001721403045</v>
+        <v>3961.239174774665</v>
       </c>
       <c r="D33" t="n">
-        <v>4088.243432863253</v>
+        <v>4309.643204887405</v>
       </c>
       <c r="E33" t="n">
-        <v>3874.288330078125</v>
+        <v>4241.09033203125</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45932</v>
+        <v>45948</v>
       </c>
       <c r="B34" t="n">
-        <v>3926.120169309596</v>
+        <v>4141.249378201778</v>
       </c>
       <c r="C34" t="n">
-        <v>3744.203382063532</v>
+        <v>3970.557168357983</v>
       </c>
       <c r="D34" t="n">
-        <v>4106.421411478193</v>
+        <v>4310.937787323826</v>
       </c>
       <c r="E34" t="n">
-        <v>3866.750244140625</v>
+        <v>4244.9248046875</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45933</v>
+        <v>45949</v>
       </c>
       <c r="B35" t="n">
-        <v>3946.289413230536</v>
+        <v>4131.32853938781</v>
       </c>
       <c r="C35" t="n">
-        <v>3769.972371221261</v>
+        <v>3971.097806590483</v>
       </c>
       <c r="D35" t="n">
-        <v>4116.71938586214</v>
+        <v>4303.038503964092</v>
       </c>
       <c r="E35" t="n">
-        <v>3886.2197265625</v>
+        <v>4245.95068359375</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45934</v>
+        <v>45950</v>
       </c>
       <c r="B36" t="n">
-        <v>3976.244271640327</v>
+        <v>4136.613566440396</v>
       </c>
       <c r="C36" t="n">
-        <v>3807.024900766815</v>
+        <v>3959.841276702241</v>
       </c>
       <c r="D36" t="n">
-        <v>4160.218695176227</v>
+        <v>4304.145025207499</v>
       </c>
       <c r="E36" t="n">
-        <v>3902.44921875</v>
+        <v>4366.8720703125</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45935</v>
+        <v>45951</v>
       </c>
       <c r="B37" t="n">
-        <v>3994.992584224783</v>
+        <v>4120.7642634564</v>
       </c>
       <c r="C37" t="n">
-        <v>3812.170508771479</v>
+        <v>3958.95909793175</v>
       </c>
       <c r="D37" t="n">
-        <v>4156.720545729908</v>
+        <v>4273.883040455215</v>
       </c>
       <c r="E37" t="n">
-        <v>3915.343017578125</v>
+        <v>4106.2548828125</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45936</v>
+        <v>45952</v>
       </c>
       <c r="B38" t="n">
-        <v>4028.894678722543</v>
+        <v>4124.586078716541</v>
       </c>
       <c r="C38" t="n">
-        <v>3864.938535037199</v>
+        <v>3957.333248021819</v>
       </c>
       <c r="D38" t="n">
-        <v>4193.429744472822</v>
+        <v>4295.092663281217</v>
       </c>
       <c r="E38" t="n">
-        <v>3984.27783203125</v>
+        <v>4096.44775390625</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45937</v>
+        <v>45953</v>
       </c>
       <c r="B39" t="n">
-        <v>4051.475264651326</v>
+        <v>4102.111132131103</v>
       </c>
       <c r="C39" t="n">
-        <v>3886.446510733938</v>
+        <v>3924.491844331415</v>
       </c>
       <c r="D39" t="n">
-        <v>4218.477628875025</v>
+        <v>4273.118262831422</v>
       </c>
       <c r="E39" t="n">
-        <v>4003.220703125</v>
+        <v>4118.24072265625</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45938</v>
+        <v>45954</v>
       </c>
       <c r="B40" t="n">
-        <v>4081.813282039926</v>
+        <v>4085.349197729486</v>
       </c>
       <c r="C40" t="n">
-        <v>3913.284278066398</v>
+        <v>3917.283661401903</v>
       </c>
       <c r="D40" t="n">
-        <v>4238.840139048812</v>
+        <v>4248.024533911571</v>
       </c>
       <c r="E40" t="n">
-        <v>4033.29296875</v>
+        <v>4112.50732421875</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45939</v>
+        <v>45955</v>
       </c>
       <c r="B41" t="n">
-        <v>4087.135759834062</v>
+        <v>4076.210483340957</v>
       </c>
       <c r="C41" t="n">
-        <v>3916.07599634703</v>
+        <v>3910.68472483911</v>
       </c>
       <c r="D41" t="n">
-        <v>4253.700527680045</v>
+        <v>4249.947621943275</v>
       </c>
       <c r="E41" t="n">
-        <v>4002.012939453125</v>
+        <v>4110.4404296875</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45940</v>
+        <v>45956</v>
       </c>
       <c r="B42" t="n">
-        <v>4096.418126587218</v>
+        <v>4062.482431482849</v>
       </c>
       <c r="C42" t="n">
-        <v>3929.052496304399</v>
+        <v>3881.260212548028</v>
       </c>
       <c r="D42" t="n">
-        <v>4269.604581254763</v>
+        <v>4228.386782676483</v>
       </c>
       <c r="E42" t="n">
-        <v>3991.026611328125</v>
+        <v>4060.7724609375</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45941</v>
+        <v>45957</v>
       </c>
       <c r="B43" t="n">
-        <v>4113.780102271919</v>
+        <v>4066.111755469501</v>
       </c>
       <c r="C43" t="n">
-        <v>3947.552138099672</v>
+        <v>3890.260683458306</v>
       </c>
       <c r="D43" t="n">
-        <v>4286.335633596069</v>
+        <v>4244.51867829717</v>
       </c>
       <c r="E43" t="n">
-        <v>3996.272216796875</v>
+        <v>3990.343994140625</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45942</v>
+        <v>45958</v>
       </c>
       <c r="B44" t="n">
-        <v>4118.477337407491</v>
+        <v>4050.651599930293</v>
       </c>
       <c r="C44" t="n">
-        <v>3953.602674703013</v>
+        <v>3886.105393235133</v>
       </c>
       <c r="D44" t="n">
-        <v>4292.04928842887</v>
+        <v>4223.601470178025</v>
       </c>
       <c r="E44" t="n">
-        <v>4041.53369140625</v>
+        <v>3967.261962890625</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45943</v>
+        <v>45959</v>
       </c>
       <c r="B45" t="n">
-        <v>4137.149595628724</v>
+        <v>4056.794112619266</v>
       </c>
       <c r="C45" t="n">
-        <v>3966.295727574408</v>
+        <v>3873.392534459476</v>
       </c>
       <c r="D45" t="n">
-        <v>4324.607248292455</v>
+        <v>4231.424525811029</v>
       </c>
       <c r="E45" t="n">
-        <v>4144.38818359375</v>
+        <v>3953.506591796875</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45944</v>
+        <v>45960</v>
       </c>
       <c r="B46" t="n">
-        <v>4143.625422940463</v>
+        <v>4038.338062592251</v>
       </c>
       <c r="C46" t="n">
-        <v>3971.374706148454</v>
+        <v>3866.560941764771</v>
       </c>
       <c r="D46" t="n">
-        <v>4315.22909072463</v>
+        <v>4200.874381376351</v>
       </c>
       <c r="E46" t="n">
-        <v>4180.63134765625</v>
+        <v>4038.202392578125</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45945</v>
+        <v>45961</v>
       </c>
       <c r="B47" t="n">
-        <v>4157.304173513243</v>
+        <v>4027.066340805009</v>
       </c>
       <c r="C47" t="n">
-        <v>3982.623052322701</v>
+        <v>3854.586061813833</v>
       </c>
       <c r="D47" t="n">
-        <v>4334.021594675487</v>
+        <v>4188.861577367719</v>
       </c>
       <c r="E47" t="n">
-        <v>4241.47607421875</v>
+        <v>3998.996826171875</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45946</v>
+        <v>45962</v>
       </c>
       <c r="B48" t="n">
-        <v>4145.741667508652</v>
+        <v>4024.636728276019</v>
       </c>
       <c r="C48" t="n">
-        <v>3985.301150644174</v>
+        <v>3848.977301826964</v>
       </c>
       <c r="D48" t="n">
-        <v>4324.152951395305</v>
+        <v>4194.088682557625</v>
       </c>
       <c r="E48" t="n">
-        <v>4442.3642578125</v>
+        <v>4007.91015625</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45947</v>
+        <v>45963</v>
       </c>
       <c r="B49" t="n">
-        <v>4138.242153704879</v>
+        <v>4018.567031980841</v>
       </c>
       <c r="C49" t="n">
-        <v>3971.106811831075</v>
+        <v>3843.980385694907</v>
       </c>
       <c r="D49" t="n">
-        <v>4300.659493653613</v>
+        <v>4184.631847595447</v>
       </c>
       <c r="E49" t="n">
-        <v>4241.09033203125</v>
+        <v>3978.682373046875</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45948</v>
+        <v>45964</v>
       </c>
       <c r="B50" t="n">
-        <v>4139.245939896869</v>
+        <v>4030.525724487632</v>
       </c>
       <c r="C50" t="n">
-        <v>3965.976691581957</v>
+        <v>3852.792093612567</v>
       </c>
       <c r="D50" t="n">
-        <v>4319.134751013723</v>
+        <v>4206.12612521906</v>
       </c>
       <c r="E50" t="n">
-        <v>4244.9248046875</v>
+        <v>3991.654541015625</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45949</v>
+        <v>45965</v>
       </c>
       <c r="B51" t="n">
-        <v>4128.313087438915</v>
+        <v>4023.787716956515</v>
       </c>
       <c r="C51" t="n">
-        <v>3961.623522461343</v>
+        <v>3840.992496753285</v>
       </c>
       <c r="D51" t="n">
-        <v>4298.39837845297</v>
+        <v>4201.975120987146</v>
       </c>
       <c r="E51" t="n">
-        <v>4245.95068359375</v>
+        <v>3929.777099609375</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45950</v>
+        <v>45966</v>
       </c>
       <c r="B52" t="n">
-        <v>4132.364186722324</v>
+        <v>4038.775294984217</v>
       </c>
       <c r="C52" t="n">
-        <v>3957.508374703382</v>
+        <v>3872.50475682435</v>
       </c>
       <c r="D52" t="n">
-        <v>4311.049052173094</v>
+        <v>4209.29747682813</v>
       </c>
       <c r="E52" t="n">
-        <v>4366.8720703125</v>
+        <v>3971.510498046875</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45951</v>
+        <v>45967</v>
       </c>
       <c r="B53" t="n">
-        <v>4125.478360378469</v>
+        <v>4029.033605560076</v>
       </c>
       <c r="C53" t="n">
-        <v>3959.817067732864</v>
+        <v>3868.644400961068</v>
       </c>
       <c r="D53" t="n">
-        <v>4305.86783245399</v>
+        <v>4196.411478285037</v>
       </c>
       <c r="E53" t="n">
-        <v>4106.2548828125</v>
+        <v>3984.83203125</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45952</v>
+        <v>45968</v>
       </c>
       <c r="B54" t="n">
-        <v>4127.269545234947</v>
+        <v>4026.115301511744</v>
       </c>
       <c r="C54" t="n">
-        <v>3945.551334823504</v>
+        <v>3851.255225786634</v>
       </c>
       <c r="D54" t="n">
-        <v>4288.358278930069</v>
+        <v>4208.694512818191</v>
       </c>
       <c r="E54" t="n">
-        <v>4096.44775390625</v>
+        <v>3989.748046875</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45953</v>
+        <v>45969</v>
       </c>
       <c r="B55" t="n">
-        <v>4105.467481794152</v>
+        <v>4031.477523297552</v>
       </c>
       <c r="C55" t="n">
-        <v>3923.19786310335</v>
+        <v>3859.84443834714</v>
       </c>
       <c r="D55" t="n">
-        <v>4290.068141081624</v>
+        <v>4202.024715179336</v>
       </c>
       <c r="E55" t="n">
-        <v>4118.24072265625</v>
+        <v>3988.74072265625</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45954</v>
+        <v>45970</v>
       </c>
       <c r="B56" t="n">
-        <v>4089.506205026726</v>
+        <v>4032.472143312809</v>
       </c>
       <c r="C56" t="n">
-        <v>3919.565129861239</v>
+        <v>3861.274593918728</v>
       </c>
       <c r="D56" t="n">
-        <v>4258.363202210275</v>
+        <v>4198.769465651539</v>
       </c>
       <c r="E56" t="n">
-        <v>4112.50732421875</v>
+        <v>4002.193115234375</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45955</v>
+        <v>45971</v>
       </c>
       <c r="B57" t="n">
-        <v>4083.909484506107</v>
+        <v>4050.640269165031</v>
       </c>
       <c r="C57" t="n">
-        <v>3921.150720997598</v>
+        <v>3875.059226729391</v>
       </c>
       <c r="D57" t="n">
-        <v>4258.253587866947</v>
+        <v>4227.972900882432</v>
       </c>
       <c r="E57" t="n">
-        <v>4110.4404296875</v>
+        <v>4111.927734375</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45956</v>
+        <v>45972</v>
       </c>
       <c r="B58" t="n">
-        <v>4068.273657636287</v>
+        <v>4049.170535331076</v>
       </c>
       <c r="C58" t="n">
-        <v>3876.750933000657</v>
+        <v>3886.372697030104</v>
       </c>
       <c r="D58" t="n">
-        <v>4221.329962265559</v>
+        <v>4216.440201712197</v>
       </c>
       <c r="E58" t="n">
-        <v>4060.7724609375</v>
+        <v>4127.6044921875</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45957</v>
+        <v>45973</v>
       </c>
       <c r="B59" t="n">
-        <v>4069.50888006505</v>
+        <v>4068.441155139883</v>
       </c>
       <c r="C59" t="n">
-        <v>3895.762058904982</v>
+        <v>3892.011233160719</v>
       </c>
       <c r="D59" t="n">
-        <v>4246.625390407601</v>
+        <v>4230.80284389538</v>
       </c>
       <c r="E59" t="n">
-        <v>3990.343994140625</v>
+        <v>4179.14697265625</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45958</v>
+        <v>45974</v>
       </c>
       <c r="B60" t="n">
-        <v>4061.638908388634</v>
+        <v>4061.995107250401</v>
       </c>
       <c r="C60" t="n">
-        <v>3900.376943975115</v>
+        <v>3896.262566485404</v>
       </c>
       <c r="D60" t="n">
-        <v>4235.64554543276</v>
+        <v>4222.786821298028</v>
       </c>
       <c r="E60" t="n">
-        <v>3967.261962890625</v>
+        <v>4172.74658203125</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45959</v>
+        <v>45975</v>
       </c>
       <c r="B61" t="n">
-        <v>4064.18039594805</v>
+        <v>4061.423093336321</v>
       </c>
       <c r="C61" t="n">
-        <v>3891.905892775021</v>
+        <v>3886.598112787671</v>
       </c>
       <c r="D61" t="n">
-        <v>4230.257767926386</v>
+        <v>4221.55940538202</v>
       </c>
       <c r="E61" t="n">
-        <v>3953.506591796875</v>
+        <v>4069.39794921875</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45960</v>
+        <v>45976</v>
       </c>
       <c r="B62" t="n">
-        <v>4044.728024032888</v>
+        <v>4068.257520402572</v>
       </c>
       <c r="C62" t="n">
-        <v>3873.401550636896</v>
+        <v>3895.732440484211</v>
       </c>
       <c r="D62" t="n">
-        <v>4228.045865014603</v>
+        <v>4244.004433101946</v>
       </c>
       <c r="E62" t="n">
-        <v>4038.202392578125</v>
+        <v>4091.458740234375</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45961</v>
+        <v>45977</v>
       </c>
       <c r="B63" t="n">
-        <v>4032.548123517131</v>
+        <v>4069.958546286593</v>
       </c>
       <c r="C63" t="n">
-        <v>3855.136324276335</v>
+        <v>3877.942053807123</v>
       </c>
       <c r="D63" t="n">
-        <v>4212.126019422529</v>
+        <v>4240.865877834759</v>
       </c>
       <c r="E63" t="n">
-        <v>3998.996826171875</v>
+        <v>4090.231201171875</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45962</v>
+        <v>45978</v>
       </c>
       <c r="B64" t="n">
-        <v>4031.970067224064</v>
+        <v>4088.203336297971</v>
       </c>
       <c r="C64" t="n">
-        <v>3863.845560596596</v>
+        <v>3919.522000132935</v>
       </c>
       <c r="D64" t="n">
-        <v>4206.715860160985</v>
+        <v>4256.972862828757</v>
       </c>
       <c r="E64" t="n">
-        <v>4007.91015625</v>
+        <v>4023.780517578125</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45963</v>
+        <v>45979</v>
       </c>
       <c r="B65" t="n">
-        <v>4022.375686260716</v>
+        <v>4086.338243295263</v>
       </c>
       <c r="C65" t="n">
-        <v>3849.449094326753</v>
+        <v>3909.365165928529</v>
       </c>
       <c r="D65" t="n">
-        <v>4206.414689879171</v>
+        <v>4255.469227106907</v>
       </c>
       <c r="E65" t="n">
-        <v>3978.682373046875</v>
+        <v>4065.880126953125</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45964</v>
+        <v>45980</v>
       </c>
       <c r="B66" t="n">
-        <v>4030.447526419432</v>
+        <v>4104.914092834551</v>
       </c>
       <c r="C66" t="n">
-        <v>3852.513982824152</v>
+        <v>3937.533332828321</v>
       </c>
       <c r="D66" t="n">
-        <v>4212.104557264513</v>
+        <v>4283.766956162192</v>
       </c>
       <c r="E66" t="n">
-        <v>3991.654541015625</v>
+        <v>4093.896240234375</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45965</v>
+        <v>45981</v>
       </c>
       <c r="B67" t="n">
-        <v>4029.97584086582</v>
+        <v>4097.654177115735</v>
       </c>
       <c r="C67" t="n">
-        <v>3855.338004070833</v>
+        <v>3930.057717443474</v>
       </c>
       <c r="D67" t="n">
-        <v>4188.313288434733</v>
+        <v>4278.412459237645</v>
       </c>
       <c r="E67" t="n">
-        <v>3929.777099609375</v>
+        <v>4068.984375</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>45966</v>
+        <v>45982</v>
       </c>
       <c r="B68" t="n">
-        <v>4040.245076810591</v>
+        <v>4096.329836780767</v>
       </c>
       <c r="C68" t="n">
-        <v>3864.492677091625</v>
+        <v>3926.493855262593</v>
       </c>
       <c r="D68" t="n">
-        <v>4210.414750494922</v>
+        <v>4267.145369320202</v>
       </c>
       <c r="E68" t="n">
-        <v>3971.510498046875</v>
+        <v>4062.59423828125</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>45967</v>
+        <v>45983</v>
       </c>
       <c r="B69" t="n">
-        <v>4028.625958195471</v>
+        <v>4102.647131168213</v>
       </c>
       <c r="C69" t="n">
-        <v>3852.487723288469</v>
+        <v>3937.325896494297</v>
       </c>
       <c r="D69" t="n">
-        <v>4213.824075794709</v>
+        <v>4272.563564582486</v>
       </c>
       <c r="E69" t="n">
-        <v>3984.83203125</v>
+        <v>4055.166015625</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>45968</v>
+        <v>45984</v>
       </c>
       <c r="B70" t="n">
-        <v>4024.175608103591</v>
+        <v>4104.225881020062</v>
       </c>
       <c r="C70" t="n">
-        <v>3859.79511443816</v>
+        <v>3939.173059976891</v>
       </c>
       <c r="D70" t="n">
-        <v>4192.951830771915</v>
+        <v>4283.32781853832</v>
       </c>
       <c r="E70" t="n">
-        <v>3989.748046875</v>
+        <v>4064.7265625</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>45969</v>
+        <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>4031.034796293502</v>
+        <v>4122.882465676184</v>
       </c>
       <c r="C71" t="n">
-        <v>3870.97950482489</v>
+        <v>3956.747962591118</v>
       </c>
       <c r="D71" t="n">
-        <v>4200.85328901508</v>
+        <v>4305.471462809241</v>
       </c>
       <c r="E71" t="n">
-        <v>3988.74072265625</v>
+        <v>4139.75537109375</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>45970</v>
+        <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>4028.422391580263</v>
+        <v>4122.076304358305</v>
       </c>
       <c r="C72" t="n">
-        <v>3859.123010631228</v>
+        <v>3944.432634135541</v>
       </c>
       <c r="D72" t="n">
-        <v>4190.3591304088</v>
+        <v>4287.916386491131</v>
       </c>
       <c r="E72" t="n">
-        <v>4002.193115234375</v>
+        <v>4124.7265625</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>45971</v>
+        <v>45987</v>
       </c>
       <c r="B73" t="n">
-        <v>4042.887688891716</v>
+        <v>4142.440395536507</v>
       </c>
       <c r="C73" t="n">
-        <v>3864.659289455207</v>
+        <v>3968.048409406009</v>
       </c>
       <c r="D73" t="n">
-        <v>4211.240162081123</v>
+        <v>4311.040044298414</v>
       </c>
       <c r="E73" t="n">
-        <v>4111.927734375</v>
+        <v>4166.796875</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>45972</v>
+        <v>45988</v>
       </c>
       <c r="B74" t="n">
-        <v>4048.120392457591</v>
+        <v>4137.745680849137</v>
       </c>
       <c r="C74" t="n">
-        <v>3872.155558538118</v>
+        <v>3975.377114505161</v>
       </c>
       <c r="D74" t="n">
-        <v>4211.730978274722</v>
+        <v>4308.242656068154</v>
       </c>
       <c r="E74" t="n">
-        <v>4127.6044921875</v>
+        <v>4160.1474609375</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>45973</v>
+        <v>45989</v>
       </c>
       <c r="B75" t="n">
-        <v>4063.338933022777</v>
+        <v>4139.774237367299</v>
       </c>
       <c r="C75" t="n">
-        <v>3876.131734876154</v>
+        <v>3972.887524221773</v>
       </c>
       <c r="D75" t="n">
-        <v>4237.309950261214</v>
+        <v>4307.156068834139</v>
       </c>
       <c r="E75" t="n">
-        <v>4179.14697265625</v>
+        <v>4231.93359375</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>45974</v>
+        <v>45990</v>
       </c>
       <c r="B76" t="n">
-        <v>4055.883178707229</v>
+        <v>4150.204886699297</v>
       </c>
       <c r="C76" t="n">
-        <v>3878.612339129727</v>
+        <v>3976.671606229506</v>
       </c>
       <c r="D76" t="n">
-        <v>4238.141873553212</v>
+        <v>4325.292903130395</v>
       </c>
       <c r="E76" t="n">
-        <v>4172.74658203125</v>
+        <v>4250.109375</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>45975</v>
+        <v>45991</v>
       </c>
       <c r="B77" t="n">
-        <v>4054.813979373997</v>
+        <v>4156.592547834725</v>
       </c>
       <c r="C77" t="n">
-        <v>3884.044963933427</v>
+        <v>3997.654166676367</v>
       </c>
       <c r="D77" t="n">
-        <v>4216.301915937314</v>
+        <v>4326.426714054623</v>
       </c>
       <c r="E77" t="n">
-        <v>4069.39794921875</v>
+        <v>4240.22265625</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>45976</v>
+        <v>45992</v>
       </c>
       <c r="B78" t="n">
-        <v>4064.308664666787</v>
+        <v>4180.65271526003</v>
       </c>
       <c r="C78" t="n">
-        <v>3902.139183450924</v>
+        <v>3999.174962434759</v>
       </c>
       <c r="D78" t="n">
-        <v>4243.312809437113</v>
+        <v>4355.403055238859</v>
       </c>
       <c r="E78" t="n">
-        <v>4091.458740234375</v>
+        <v>4246.2890625</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>45977</v>
+        <v>45993</v>
       </c>
       <c r="B79" t="n">
-        <v>4063.652647631291</v>
+        <v>4185.710946779891</v>
       </c>
       <c r="C79" t="n">
-        <v>3873.138514848136</v>
+        <v>4002.631328696591</v>
       </c>
       <c r="D79" t="n">
-        <v>4242.469481449903</v>
+        <v>4356.973267020708</v>
       </c>
       <c r="E79" t="n">
-        <v>4090.231201171875</v>
+        <v>4215.837890625</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>45978</v>
+        <v>45994</v>
       </c>
       <c r="B80" t="n">
-        <v>4079.487911022279</v>
+        <v>4212.237646664912</v>
       </c>
       <c r="C80" t="n">
-        <v>3905.06861720197</v>
+        <v>4045.543904520634</v>
       </c>
       <c r="D80" t="n">
-        <v>4245.183339375249</v>
+        <v>4373.305993421724</v>
       </c>
       <c r="E80" t="n">
-        <v>4023.780517578125</v>
+        <v>4215.3046875</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>45979</v>
+        <v>45995</v>
       </c>
       <c r="B81" t="n">
-        <v>4085.618296659425</v>
+        <v>4213.817780487472</v>
       </c>
       <c r="C81" t="n">
-        <v>3915.657768311442</v>
+        <v>4036.083863771838</v>
       </c>
       <c r="D81" t="n">
-        <v>4254.455689663829</v>
+        <v>4382.665024823003</v>
       </c>
       <c r="E81" t="n">
-        <v>4065.880126953125</v>
+        <v>4213.90283203125</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>45980</v>
+        <v>45996</v>
       </c>
       <c r="B82" t="n">
-        <v>4101.392441864545</v>
+        <v>4222.03036053188</v>
       </c>
       <c r="C82" t="n">
-        <v>3924.767867827484</v>
+        <v>4049.598396542247</v>
       </c>
       <c r="D82" t="n">
-        <v>4255.717730186737</v>
+        <v>4382.364350680275</v>
       </c>
       <c r="E82" t="n">
-        <v>4093.896240234375</v>
+        <v>4211.54150390625</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>45981</v>
+        <v>45997</v>
       </c>
       <c r="B83" t="n">
-        <v>4094.29061062482</v>
+        <v>4238.341090279037</v>
       </c>
       <c r="C83" t="n">
-        <v>3938.167469811652</v>
+        <v>4082.02544086709</v>
       </c>
       <c r="D83" t="n">
-        <v>4293.982504715594</v>
+        <v>4407.136906080794</v>
       </c>
       <c r="E83" t="n">
-        <v>4068.984375</v>
+        <v>4215.07421875</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>45982</v>
+        <v>45998</v>
       </c>
       <c r="B84" t="n">
-        <v>4093.518063236748</v>
+        <v>4250.089270997601</v>
       </c>
       <c r="C84" t="n">
-        <v>3913.279192333302</v>
+        <v>4080.226418949735</v>
       </c>
       <c r="D84" t="n">
-        <v>4258.409471093044</v>
+        <v>4416.204256430809</v>
       </c>
       <c r="E84" t="n">
-        <v>4062.59423828125</v>
+        <v>4214.52880859375</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>45983</v>
+        <v>45999</v>
       </c>
       <c r="B85" t="n">
-        <v>4103.394298405414</v>
+        <v>4278.780108095391</v>
       </c>
       <c r="C85" t="n">
-        <v>3931.076276611528</v>
+        <v>4102.003433070071</v>
       </c>
       <c r="D85" t="n">
-        <v>4285.723196993535</v>
+        <v>4447.096953825467</v>
       </c>
       <c r="E85" t="n">
-        <v>4055.166015625</v>
+        <v>4203.466796875</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>45984</v>
+        <v>46000</v>
       </c>
       <c r="B86" t="n">
-        <v>4103.33853488515</v>
+        <v>4287.542045765228</v>
       </c>
       <c r="C86" t="n">
-        <v>3932.816443490437</v>
+        <v>4116.513540642393</v>
       </c>
       <c r="D86" t="n">
-        <v>4281.007087629425</v>
+        <v>4454.498596446073</v>
       </c>
       <c r="E86" t="n">
-        <v>4064.7265625</v>
+        <v>4215.78662109375</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>45985</v>
+        <v>46001</v>
       </c>
       <c r="B87" t="n">
-        <v>4120.112422298634</v>
+        <v>4316.669156289901</v>
       </c>
       <c r="C87" t="n">
-        <v>3965.54726098592</v>
+        <v>4143.665699673745</v>
       </c>
       <c r="D87" t="n">
-        <v>4299.68688998148</v>
+        <v>4494.026386885651</v>
       </c>
       <c r="E87" t="n">
-        <v>4139.75537109375</v>
+        <v>4240.0341796875</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>45986</v>
+        <v>46002</v>
       </c>
       <c r="B88" t="n">
-        <v>4127.620101663943</v>
+        <v>4319.597964933631</v>
       </c>
       <c r="C88" t="n">
-        <v>3946.443406937125</v>
+        <v>4149.602152179915</v>
       </c>
       <c r="D88" t="n">
-        <v>4300.978625856307</v>
+        <v>4497.161893063881</v>
       </c>
       <c r="E88" t="n">
-        <v>4124.7265625</v>
+        <v>4286.09228515625</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>45987</v>
+        <v>46003</v>
       </c>
       <c r="B89" t="n">
-        <v>4145.286642728352</v>
+        <v>4327.793306276973</v>
       </c>
       <c r="C89" t="n">
-        <v>3970.314227464414</v>
+        <v>4175.239275753636</v>
       </c>
       <c r="D89" t="n">
-        <v>4317.34654578835</v>
+        <v>4494.415226317838</v>
       </c>
       <c r="E89" t="n">
-        <v>4166.796875</v>
+        <v>4309.79052734375</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>45988</v>
+        <v>46004</v>
       </c>
       <c r="B90" t="n">
-        <v>4140.641265175228</v>
+        <v>4342.646377405978</v>
       </c>
       <c r="C90" t="n">
-        <v>3968.280476138737</v>
+        <v>4166.494084117518</v>
       </c>
       <c r="D90" t="n">
-        <v>4310.722082740897</v>
+        <v>4505.588396103951</v>
       </c>
       <c r="E90" t="n">
-        <v>4160.1474609375</v>
+        <v>4318.52587890625</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>45989</v>
+        <v>46005</v>
       </c>
       <c r="B91" t="n">
-        <v>4142.908118154278</v>
+        <v>4351.465895090539</v>
       </c>
       <c r="C91" t="n">
-        <v>3951.371051973882</v>
+        <v>4183.281216409249</v>
       </c>
       <c r="D91" t="n">
-        <v>4319.790766790982</v>
+        <v>4507.019560135985</v>
       </c>
       <c r="E91" t="n">
-        <v>4231.93359375</v>
+        <v>4319.2890625</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>45990</v>
+        <v>46006</v>
       </c>
       <c r="B92" t="n">
-        <v>4156.394049132417</v>
+        <v>4375.773332126081</v>
       </c>
       <c r="C92" t="n">
-        <v>3983.437913029568</v>
+        <v>4213.964827345787</v>
       </c>
       <c r="D92" t="n">
-        <v>4335.082200241863</v>
+        <v>4546.515922431883</v>
       </c>
       <c r="E92" t="n">
-        <v>4250.109375</v>
+        <v>4316.8115234375</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>45991</v>
+        <v>46007</v>
       </c>
       <c r="B93" t="n">
-        <v>4160.473790903646</v>
+        <v>4378.761738326404</v>
       </c>
       <c r="C93" t="n">
-        <v>3988.886035456358</v>
+        <v>4208.437600686695</v>
       </c>
       <c r="D93" t="n">
-        <v>4331.927614080442</v>
+        <v>4555.812875113013</v>
       </c>
       <c r="E93" t="n">
-        <v>4240.22265625</v>
+        <v>4322.4453125</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>45992</v>
+        <v>46008</v>
       </c>
       <c r="B94" t="n">
-        <v>4181.833577744742</v>
+        <v>4400.838092321217</v>
       </c>
       <c r="C94" t="n">
-        <v>3996.661005656804</v>
+        <v>4235.576568649813</v>
       </c>
       <c r="D94" t="n">
-        <v>4351.158961604347</v>
+        <v>4585.711637741809</v>
       </c>
       <c r="E94" t="n">
-        <v>4246.2890625</v>
+        <v>4359.79248046875</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>45993</v>
+        <v>46009</v>
       </c>
       <c r="B95" t="n">
-        <v>4194.27329410612</v>
+        <v>4395.598531661879</v>
       </c>
       <c r="C95" t="n">
-        <v>4031.238479732139</v>
+        <v>4210.771612192776</v>
       </c>
       <c r="D95" t="n">
-        <v>4368.477996822864</v>
+        <v>4578.004975194413</v>
       </c>
       <c r="E95" t="n">
-        <v>4215.837890625</v>
+        <v>4345.7919921875</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>45994</v>
+        <v>46010</v>
       </c>
       <c r="B96" t="n">
-        <v>4217.088125710477</v>
+        <v>4394.711071600616</v>
       </c>
       <c r="C96" t="n">
-        <v>4055.524103015062</v>
+        <v>4224.56731063591</v>
       </c>
       <c r="D96" t="n">
-        <v>4404.895886734341</v>
+        <v>4555.54238525123</v>
       </c>
       <c r="E96" t="n">
-        <v>4215.3046875</v>
+        <v>4349.39208984375</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>45995</v>
+        <v>46011</v>
       </c>
       <c r="B97" t="n">
-        <v>4217.656025447032</v>
+        <v>4399.809040562117</v>
       </c>
       <c r="C97" t="n">
-        <v>4050.373307761703</v>
+        <v>4225.188750019611</v>
       </c>
       <c r="D97" t="n">
-        <v>4392.881699115648</v>
+        <v>4567.33093979678</v>
       </c>
       <c r="E97" t="n">
-        <v>4213.90283203125</v>
+        <v>4350.67431640625</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>45996</v>
+        <v>46012</v>
       </c>
       <c r="B98" t="n">
-        <v>4225.033637309749</v>
+        <v>4398.476249550194</v>
       </c>
       <c r="C98" t="n">
-        <v>4055.025864058743</v>
+        <v>4227.996691537754</v>
       </c>
       <c r="D98" t="n">
-        <v>4407.860853201316</v>
+        <v>4575.93939397342</v>
       </c>
       <c r="E98" t="n">
-        <v>4211.54150390625</v>
+        <v>4364.52685546875</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>45997</v>
+        <v>46013</v>
       </c>
       <c r="B99" t="n">
-        <v>4243.349948286891</v>
+        <v>4412.535024447312</v>
       </c>
       <c r="C99" t="n">
-        <v>4058.738220604136</v>
+        <v>4236.395543960552</v>
       </c>
       <c r="D99" t="n">
-        <v>4424.888838428014</v>
+        <v>4594.321266767024</v>
       </c>
       <c r="E99" t="n">
-        <v>4215.07421875</v>
+        <v>4481.84814453125</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>45998</v>
+        <v>46014</v>
       </c>
       <c r="B100" t="n">
-        <v>4251.797908119106</v>
+        <v>4405.496801216519</v>
       </c>
       <c r="C100" t="n">
-        <v>4079.464598901924</v>
+        <v>4223.038602259031</v>
       </c>
       <c r="D100" t="n">
-        <v>4430.912575791776</v>
+        <v>4575.421052823316</v>
       </c>
       <c r="E100" t="n">
-        <v>4214.52880859375</v>
+        <v>4530.59375</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>45999</v>
+        <v>46015</v>
       </c>
       <c r="B101" t="n">
-        <v>4276.884818581202</v>
+        <v>4418.095459409892</v>
       </c>
       <c r="C101" t="n">
-        <v>4097.036756112358</v>
+        <v>4241.53330972717</v>
       </c>
       <c r="D101" t="n">
-        <v>4455.320336333834</v>
+        <v>4581.912630419843</v>
       </c>
       <c r="E101" t="n">
-        <v>4203.466796875</v>
+        <v>4493.84716796875</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46000</v>
+        <v>46016</v>
       </c>
       <c r="B102" t="n">
-        <v>4292.241371833067</v>
+        <v>4404.252999240022</v>
       </c>
       <c r="C102" t="n">
-        <v>4126.90984217105</v>
+        <v>4233.160841452145</v>
       </c>
       <c r="D102" t="n">
-        <v>4457.958186882937</v>
+        <v>4578.187230304836</v>
       </c>
       <c r="E102" t="n">
-        <v>4215.78662109375</v>
+        <v>4513.3798828125</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46001</v>
+        <v>46017</v>
       </c>
       <c r="B103" t="n">
-        <v>4317.01007648851</v>
+        <v>4395.952451384594</v>
       </c>
       <c r="C103" t="n">
-        <v>4149.425256563105</v>
+        <v>4227.391873060053</v>
       </c>
       <c r="D103" t="n">
-        <v>4486.440139286641</v>
+        <v>4557.183969332498</v>
       </c>
       <c r="E103" t="n">
-        <v>4240.0341796875</v>
+        <v>4553.92822265625</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46002</v>
+        <v>46018</v>
       </c>
       <c r="B104" t="n">
-        <v>4318.439151910165</v>
+        <v>4395.121539517026</v>
       </c>
       <c r="C104" t="n">
-        <v>4145.546543445882</v>
+        <v>4225.872608037533</v>
       </c>
       <c r="D104" t="n">
-        <v>4481.911790023897</v>
+        <v>4564.493353614807</v>
       </c>
       <c r="E104" t="n">
-        <v>4286.09228515625</v>
+        <v>4567.81787109375</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46003</v>
+        <v>46019</v>
       </c>
       <c r="B105" t="n">
-        <v>4325.484310498686</v>
+        <v>4389.608408665712</v>
       </c>
       <c r="C105" t="n">
-        <v>4145.444798766065</v>
+        <v>4224.531614662536</v>
       </c>
       <c r="D105" t="n">
-        <v>4486.235117189554</v>
+        <v>4573.855768360176</v>
       </c>
       <c r="E105" t="n">
-        <v>4309.79052734375</v>
+        <v>4548.640625</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46004</v>
+        <v>46020</v>
       </c>
       <c r="B106" t="n">
-        <v>4342.207487222737</v>
+        <v>4401.460840403241</v>
       </c>
       <c r="C106" t="n">
-        <v>4186.396858535503</v>
+        <v>4242.243632217984</v>
       </c>
       <c r="D106" t="n">
-        <v>4496.703892957677</v>
+        <v>4562.437543868713</v>
       </c>
       <c r="E106" t="n">
-        <v>4318.52587890625</v>
+        <v>4357.6005859375</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46005</v>
+        <v>46021</v>
       </c>
       <c r="B107" t="n">
-        <v>4347.772568116246</v>
+        <v>4394.368933152747</v>
       </c>
       <c r="C107" t="n">
-        <v>4159.506950598744</v>
+        <v>4217.441748816957</v>
       </c>
       <c r="D107" t="n">
-        <v>4508.120250122674</v>
+        <v>4556.238808318609</v>
       </c>
       <c r="E107" t="n">
-        <v>4319.2890625</v>
+        <v>4355.40380859375</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46006</v>
+        <v>46022</v>
       </c>
       <c r="B108" t="n">
-        <v>4368.698758478313</v>
+        <v>4409.19167975584</v>
       </c>
       <c r="C108" t="n">
-        <v>4189.940839155142</v>
+        <v>4235.420863433837</v>
       </c>
       <c r="D108" t="n">
-        <v>4544.562032150571</v>
+        <v>4583.568749510269</v>
       </c>
       <c r="E108" t="n">
-        <v>4316.8115234375</v>
+        <v>4330.3779296875</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46007</v>
+        <v>46023</v>
       </c>
       <c r="B109" t="n">
-        <v>4378.671342121301</v>
+        <v>4399.91727398007</v>
       </c>
       <c r="C109" t="n">
-        <v>4210.566765966523</v>
+        <v>4227.99479093967</v>
       </c>
       <c r="D109" t="n">
-        <v>4549.725333431166</v>
+        <v>4584.95492872417</v>
       </c>
       <c r="E109" t="n">
-        <v>4322.4453125</v>
+        <v>4356.462890625</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46008</v>
+        <v>46024</v>
       </c>
       <c r="B110" t="n">
-        <v>4396.930480349123</v>
+        <v>4398.532225770298</v>
       </c>
       <c r="C110" t="n">
-        <v>4228.488019277071</v>
+        <v>4235.390487366489</v>
       </c>
       <c r="D110" t="n">
-        <v>4568.381647878998</v>
+        <v>4576.474922245006</v>
       </c>
       <c r="E110" t="n">
-        <v>4359.79248046875</v>
+        <v>4341.74072265625</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46009</v>
+        <v>46025</v>
       </c>
       <c r="B111" t="n">
-        <v>4390.86408183528</v>
+        <v>4406.90295104133</v>
       </c>
       <c r="C111" t="n">
-        <v>4212.059690842485</v>
+        <v>4232.968498940666</v>
       </c>
       <c r="D111" t="n">
-        <v>4567.293472799928</v>
+        <v>4585.292099529777</v>
       </c>
       <c r="E111" t="n">
-        <v>4345.7919921875</v>
+        <v>4353.5283203125</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46010</v>
+        <v>46026</v>
       </c>
       <c r="B112" t="n">
-        <v>4389.60715730732</v>
+        <v>4412.751247931885</v>
       </c>
       <c r="C112" t="n">
-        <v>4230.091579087255</v>
+        <v>4243.93203598864</v>
       </c>
       <c r="D112" t="n">
-        <v>4564.543867429329</v>
+        <v>4584.18070567848</v>
       </c>
       <c r="E112" t="n">
-        <v>4349.39208984375</v>
+        <v>4383.18310546875</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46011</v>
+        <v>46027</v>
       </c>
       <c r="B113" t="n">
-        <v>4397.436756602048</v>
+        <v>4437.935127010409</v>
       </c>
       <c r="C113" t="n">
-        <v>4217.647713410411</v>
+        <v>4258.613750801009</v>
       </c>
       <c r="D113" t="n">
-        <v>4558.377698224817</v>
+        <v>4608.3734944217</v>
       </c>
       <c r="E113" t="n">
-        <v>4350.67431640625</v>
+        <v>4445.12109375</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46012</v>
+        <v>46028</v>
       </c>
       <c r="B114" t="n">
-        <v>4393.762621932871</v>
+        <v>4445.894966285233</v>
       </c>
       <c r="C114" t="n">
-        <v>4219.24842177005</v>
+        <v>4279.206602364949</v>
       </c>
       <c r="D114" t="n">
-        <v>4565.741749349248</v>
+        <v>4628.96693801865</v>
       </c>
       <c r="E114" t="n">
-        <v>4364.52685546875</v>
+        <v>4509.8115234375</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46013</v>
+        <v>46029</v>
       </c>
       <c r="B115" t="n">
-        <v>4405.374322024783</v>
+        <v>4477.185361053229</v>
       </c>
       <c r="C115" t="n">
-        <v>4235.389063759285</v>
+        <v>4318.800218030116</v>
       </c>
       <c r="D115" t="n">
-        <v>4562.442194796748</v>
+        <v>4654.766093936721</v>
       </c>
       <c r="E115" t="n">
-        <v>4481.84814453125</v>
+        <v>4472.72314453125</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46014</v>
+        <v>46030</v>
       </c>
       <c r="B116" t="n">
-        <v>4406.244781703864</v>
+        <v>4485.442385044565</v>
       </c>
       <c r="C116" t="n">
-        <v>4229.537544185752</v>
+        <v>4316.999541762024</v>
       </c>
       <c r="D116" t="n">
-        <v>4581.3551465921</v>
+        <v>4649.691847132833</v>
       </c>
       <c r="E116" t="n">
-        <v>4530.59375</v>
+        <v>4478.43115234375</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46015</v>
+        <v>46031</v>
       </c>
       <c r="B117" t="n">
-        <v>4415.911052806913</v>
+        <v>4502.261175214153</v>
       </c>
       <c r="C117" t="n">
-        <v>4238.229652075827</v>
+        <v>4331.98946664482</v>
       </c>
       <c r="D117" t="n">
-        <v>4590.785445284012</v>
+        <v>4683.205894122827</v>
       </c>
       <c r="E117" t="n">
-        <v>4493.84716796875</v>
+        <v>4503.35595703125</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46016</v>
+        <v>46032</v>
       </c>
       <c r="B118" t="n">
-        <v>4402.05858429204</v>
+        <v>4529.087293246559</v>
       </c>
       <c r="C118" t="n">
-        <v>4231.894842432515</v>
+        <v>4361.612983746247</v>
       </c>
       <c r="D118" t="n">
-        <v>4578.214231188655</v>
+        <v>4691.360986469832</v>
       </c>
       <c r="E118" t="n">
-        <v>4513.3798828125</v>
+        <v>4516.80322265625</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46017</v>
+        <v>46033</v>
       </c>
       <c r="B119" t="n">
-        <v>4394.111639079125</v>
+        <v>4553.203020360659</v>
       </c>
       <c r="C119" t="n">
-        <v>4222.670084007654</v>
+        <v>4375.701718158091</v>
       </c>
       <c r="D119" t="n">
-        <v>4571.905684519506</v>
+        <v>4731.265875970312</v>
       </c>
       <c r="E119" t="n">
-        <v>4553.92822265625</v>
+        <v>4538.0986328125</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46018</v>
+        <v>46034</v>
       </c>
       <c r="B120" t="n">
-        <v>4396.619297676143</v>
+        <v>4596.019763544189</v>
       </c>
       <c r="C120" t="n">
-        <v>4215.281344720784</v>
+        <v>4418.50172919032</v>
       </c>
       <c r="D120" t="n">
-        <v>4576.037321446385</v>
+        <v>4776.057325829493</v>
       </c>
       <c r="E120" t="n">
-        <v>4567.81787109375</v>
+        <v>4605.93798828125</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46019</v>
+        <v>46035</v>
       </c>
       <c r="B121" t="n">
-        <v>4389.237299104973</v>
+        <v>4620.536227823192</v>
       </c>
       <c r="C121" t="n">
-        <v>4228.848796442639</v>
+        <v>4460.375951098629</v>
       </c>
       <c r="D121" t="n">
-        <v>4566.502245872111</v>
+        <v>4789.800118976399</v>
       </c>
       <c r="E121" t="n">
-        <v>4548.640625</v>
+        <v>4601.09033203125</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46020</v>
+        <v>46036</v>
       </c>
       <c r="B122" t="n">
-        <v>4398.966911285737</v>
+        <v>4666.882390627512</v>
       </c>
       <c r="C122" t="n">
-        <v>4220.7760546561</v>
+        <v>4498.050603989465</v>
       </c>
       <c r="D122" t="n">
-        <v>4568.088597336486</v>
+        <v>4829.209501310938</v>
       </c>
       <c r="E122" t="n">
-        <v>4357.6005859375</v>
+        <v>4627.44287109375</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46021</v>
+        <v>46037</v>
       </c>
       <c r="B123" t="n">
-        <v>4399.950930772772</v>
+        <v>4688.298652094956</v>
       </c>
       <c r="C123" t="n">
-        <v>4223.877033222556</v>
+        <v>4531.362866067643</v>
       </c>
       <c r="D123" t="n">
-        <v>4578.251626839561</v>
+        <v>4870.038215569027</v>
       </c>
       <c r="E123" t="n">
-        <v>4355.40380859375</v>
+        <v>4621.1728515625</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46022</v>
+        <v>46038</v>
       </c>
       <c r="B124" t="n">
-        <v>4411.847919579514</v>
+        <v>4716.024732351225</v>
       </c>
       <c r="C124" t="n">
-        <v>4243.510977813315</v>
+        <v>4543.265549753465</v>
       </c>
       <c r="D124" t="n">
-        <v>4577.59132187363</v>
+        <v>4879.009549928642</v>
       </c>
       <c r="E124" t="n">
-        <v>4330.3779296875</v>
+        <v>4601.5517578125</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46023</v>
+        <v>46039</v>
       </c>
       <c r="B125" t="n">
-        <v>4402.411158728777</v>
+        <v>4751.20143859398</v>
       </c>
       <c r="C125" t="n">
-        <v>4233.426409386261</v>
+        <v>4602.643680808054</v>
       </c>
       <c r="D125" t="n">
-        <v>4574.927265498135</v>
+        <v>4920.99860064998</v>
       </c>
       <c r="E125" t="n">
-        <v>4356.462890625</v>
+        <v>4609.82177734375</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46024</v>
+        <v>46040</v>
       </c>
       <c r="B126" t="n">
-        <v>4401.075171721307</v>
+        <v>4780.866149059434</v>
       </c>
       <c r="C126" t="n">
-        <v>4237.731517967844</v>
+        <v>4608.32601131926</v>
       </c>
       <c r="D126" t="n">
-        <v>4580.205198290421</v>
+        <v>4955.244729703289</v>
       </c>
       <c r="E126" t="n">
-        <v>4341.74072265625</v>
+        <v>4686.02978515625</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46025</v>
+        <v>46041</v>
       </c>
       <c r="B127" t="n">
-        <v>4412.33933232592</v>
+        <v>4826.252912318194</v>
       </c>
       <c r="C127" t="n">
-        <v>4253.447548485338</v>
+        <v>4656.873020406229</v>
       </c>
       <c r="D127" t="n">
-        <v>4584.387588437072</v>
+        <v>4999.508802877783</v>
       </c>
       <c r="E127" t="n">
-        <v>4353.5283203125</v>
+        <v>4681.861328125</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46026</v>
+        <v>46042</v>
       </c>
       <c r="B128" t="n">
-        <v>4415.749071873546</v>
+        <v>4850.256575231139</v>
       </c>
       <c r="C128" t="n">
-        <v>4236.090278479222</v>
+        <v>4685.026317649916</v>
       </c>
       <c r="D128" t="n">
-        <v>4593.473282896563</v>
+        <v>5025.502964744303</v>
       </c>
       <c r="E128" t="n">
-        <v>4383.18310546875</v>
+        <v>4802.517578125</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46027</v>
+        <v>46043</v>
       </c>
       <c r="B129" t="n">
-        <v>4438.135784397886</v>
+        <v>4892.980779856387</v>
       </c>
       <c r="C129" t="n">
-        <v>4254.624784003187</v>
+        <v>4717.293973146627</v>
       </c>
       <c r="D129" t="n">
-        <v>4612.879018127722</v>
+        <v>5050.020457100441</v>
       </c>
       <c r="E129" t="n">
-        <v>4445.12109375</v>
+        <v>4807.76416015625</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46028</v>
+        <v>46044</v>
       </c>
       <c r="B130" t="n">
-        <v>4453.415619308937</v>
+        <v>4907.719059372949</v>
       </c>
       <c r="C130" t="n">
-        <v>4277.435365824882</v>
+        <v>4745.423684881164</v>
       </c>
       <c r="D130" t="n">
-        <v>4612.998564678443</v>
+        <v>5072.024033198537</v>
       </c>
       <c r="E130" t="n">
-        <v>4509.8115234375</v>
+        <v>4974.0048828125</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46029</v>
+        <v>46045</v>
       </c>
       <c r="B131" t="n">
-        <v>4480.968214602208</v>
+        <v>4925.843516840465</v>
       </c>
       <c r="C131" t="n">
-        <v>4315.785282911269</v>
+        <v>4760.731917171539</v>
       </c>
       <c r="D131" t="n">
-        <v>4661.433387903642</v>
+        <v>5091.081195155939</v>
       </c>
       <c r="E131" t="n">
-        <v>4472.72314453125</v>
+        <v>5001.9541015625</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46030</v>
+        <v>46046</v>
       </c>
       <c r="B132" t="n">
-        <v>4488.221760356608</v>
+        <v>4948.704182312458</v>
       </c>
       <c r="C132" t="n">
-        <v>4310.337432680422</v>
+        <v>4781.599753922397</v>
       </c>
       <c r="D132" t="n">
-        <v>4652.957793239389</v>
+        <v>5121.134611384064</v>
       </c>
       <c r="E132" t="n">
-        <v>4478.43115234375</v>
+        <v>5075.52392578125</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46031</v>
+        <v>46047</v>
       </c>
       <c r="B133" t="n">
-        <v>4504.247106341494</v>
+        <v>4963.619929254116</v>
       </c>
       <c r="C133" t="n">
-        <v>4334.858078423971</v>
+        <v>4784.852448543853</v>
       </c>
       <c r="D133" t="n">
-        <v>4670.847095576992</v>
+        <v>5144.399577962139</v>
       </c>
       <c r="E133" t="n">
-        <v>4503.35595703125</v>
+        <v>5063.904296875</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46032</v>
+        <v>46048</v>
       </c>
       <c r="B134" t="n">
-        <v>4533.150243382891</v>
+        <v>4992.171943974606</v>
       </c>
       <c r="C134" t="n">
-        <v>4374.372985666815</v>
+        <v>4830.7072923361</v>
       </c>
       <c r="D134" t="n">
-        <v>4695.278738005156</v>
+        <v>5162.727766286954</v>
       </c>
       <c r="E134" t="n">
-        <v>4516.80322265625</v>
+        <v>5057.650390625</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46033</v>
+        <v>46049</v>
       </c>
       <c r="B135" t="n">
-        <v>4554.063447283283</v>
+        <v>4997.659315713945</v>
       </c>
       <c r="C135" t="n">
-        <v>4378.495057508023</v>
+        <v>4815.593864012533</v>
       </c>
       <c r="D135" t="n">
-        <v>4729.815643588081</v>
+        <v>5171.653174778126</v>
       </c>
       <c r="E135" t="n">
-        <v>4538.0986328125</v>
+        <v>5187.36669921875</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46034</v>
+        <v>46050</v>
       </c>
       <c r="B136" t="n">
-        <v>4593.395922046613</v>
+        <v>5020.636797629644</v>
       </c>
       <c r="C136" t="n">
-        <v>4420.679334196976</v>
+        <v>4849.621904176636</v>
       </c>
       <c r="D136" t="n">
-        <v>4766.455816928915</v>
+        <v>5196.512145676096</v>
       </c>
       <c r="E136" t="n">
-        <v>4605.93798828125</v>
+        <v>5536.52734375</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46035</v>
+        <v>46051</v>
       </c>
       <c r="B137" t="n">
-        <v>4624.643842156398</v>
+        <v>5014.884229012263</v>
       </c>
       <c r="C137" t="n">
-        <v>4445.491088589097</v>
+        <v>4841.837706687272</v>
       </c>
       <c r="D137" t="n">
-        <v>4787.798253582931</v>
+        <v>5190.22357458344</v>
       </c>
       <c r="E137" t="n">
-        <v>4601.09033203125</v>
+        <v>5467.4462890625</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46036</v>
+        <v>46052</v>
       </c>
       <c r="B138" t="n">
-        <v>4666.780536629718</v>
+        <v>5012.282406406678</v>
       </c>
       <c r="C138" t="n">
-        <v>4480.111005511629</v>
+        <v>4839.875154801764</v>
       </c>
       <c r="D138" t="n">
-        <v>4841.932847749396</v>
+        <v>5185.776255499069</v>
       </c>
       <c r="E138" t="n">
-        <v>4627.44287109375</v>
+        <v>4912.69970703125</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46037</v>
+        <v>46053</v>
       </c>
       <c r="B139" t="n">
-        <v>4686.852882478173</v>
+        <v>5014.698838494355</v>
       </c>
       <c r="C139" t="n">
-        <v>4504.913193477703</v>
+        <v>4843.688561855582</v>
       </c>
       <c r="D139" t="n">
-        <v>4857.352326673659</v>
+        <v>5198.13222506133</v>
       </c>
       <c r="E139" t="n">
-        <v>4621.1728515625</v>
+        <v>4834.16162109375</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46038</v>
+        <v>46054</v>
       </c>
       <c r="B140" t="n">
-        <v>4713.586297094176</v>
+        <v>5009.964631621449</v>
       </c>
       <c r="C140" t="n">
-        <v>4539.405397580339</v>
+        <v>4836.03930810257</v>
       </c>
       <c r="D140" t="n">
-        <v>4884.340847537702</v>
+        <v>5166.310278187486</v>
       </c>
       <c r="E140" t="n">
-        <v>4601.5517578125</v>
+        <v>4760.32666015625</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46039</v>
+        <v>46055</v>
       </c>
       <c r="B141" t="n">
-        <v>4750.787341194304</v>
+        <v>5020.153881855362</v>
       </c>
       <c r="C141" t="n">
-        <v>4578.940089389584</v>
+        <v>4836.826248418905</v>
       </c>
       <c r="D141" t="n">
-        <v>4920.235543886612</v>
+        <v>5184.085091610219</v>
       </c>
       <c r="E141" t="n">
-        <v>4609.82177734375</v>
+        <v>4785.6171875</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46040</v>
+        <v>46056</v>
       </c>
       <c r="B142" t="n">
-        <v>4777.343919483053</v>
+        <v>5009.025529507306</v>
       </c>
       <c r="C142" t="n">
-        <v>4611.075825587508</v>
+        <v>4853.481994058684</v>
       </c>
       <c r="D142" t="n">
-        <v>4951.046747352459</v>
+        <v>5178.290421917505</v>
       </c>
       <c r="E142" t="n">
-        <v>4686.02978515625</v>
+        <v>4956.98681640625</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46041</v>
+        <v>46057</v>
       </c>
       <c r="B143" t="n">
-        <v>4819.483639360757</v>
+        <v>5017.548109512907</v>
       </c>
       <c r="C143" t="n">
-        <v>4640.516910169944</v>
+        <v>4846.607394808568</v>
       </c>
       <c r="D143" t="n">
-        <v>5005.633857581915</v>
+        <v>5190.999448876049</v>
       </c>
       <c r="E143" t="n">
-        <v>4681.861328125</v>
+        <v>5023.80615234375</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46042</v>
+        <v>46058</v>
       </c>
       <c r="B144" t="n">
-        <v>4850.589983531055</v>
+        <v>4999.857257037736</v>
       </c>
       <c r="C144" t="n">
-        <v>4666.685490383435</v>
+        <v>4824.180423685173</v>
       </c>
       <c r="D144" t="n">
-        <v>5029.522751730326</v>
+        <v>5161.664739432748</v>
       </c>
       <c r="E144" t="n">
-        <v>4802.517578125</v>
+        <v>4695.63037109375</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46043</v>
+        <v>46059</v>
       </c>
       <c r="B145" t="n">
-        <v>4889.596837336381</v>
+        <v>4988.121095358596</v>
       </c>
       <c r="C145" t="n">
-        <v>4718.46560837885</v>
+        <v>4824.45715731221</v>
       </c>
       <c r="D145" t="n">
-        <v>5058.740576532169</v>
+        <v>5153.59053134142</v>
       </c>
       <c r="E145" t="n">
-        <v>4807.76416015625</v>
+        <v>4940.42236328125</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46044</v>
+        <v>46060</v>
       </c>
       <c r="B146" t="n">
-        <v>4903.587283001561</v>
+        <v>4984.417249352306</v>
       </c>
       <c r="C146" t="n">
-        <v>4733.478250993123</v>
+        <v>4804.833309229332</v>
       </c>
       <c r="D146" t="n">
-        <v>5074.274628953414</v>
+        <v>5164.694909649383</v>
       </c>
       <c r="E146" t="n">
-        <v>4974.0048828125</v>
+        <v>4989.26904296875</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46045</v>
+        <v>46061</v>
       </c>
       <c r="B147" t="n">
-        <v>4921.398947642301</v>
+        <v>4976.702991645579</v>
       </c>
       <c r="C147" t="n">
-        <v>4744.867964947788</v>
+        <v>4806.970464335334</v>
       </c>
       <c r="D147" t="n">
-        <v>5095.85028676596</v>
+        <v>5147.553129619774</v>
       </c>
       <c r="E147" t="n">
-        <v>5001.9541015625</v>
+        <v>5042.5322265625</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46046</v>
+        <v>46062</v>
       </c>
       <c r="B148" t="n">
-        <v>4947.02487012552</v>
+        <v>4987.0901065998</v>
       </c>
       <c r="C148" t="n">
-        <v>4772.057277292213</v>
+        <v>4807.660347531133</v>
       </c>
       <c r="D148" t="n">
-        <v>5120.258803324821</v>
+        <v>5154.043035907172</v>
       </c>
       <c r="E148" t="n">
-        <v>5075.52392578125</v>
+        <v>5035.80712890625</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46047</v>
+        <v>46063</v>
       </c>
       <c r="B149" t="n">
-        <v>4959.609885788224</v>
+        <v>4979.284578472212</v>
       </c>
       <c r="C149" t="n">
-        <v>4784.120578226284</v>
+        <v>4805.012687153277</v>
       </c>
       <c r="D149" t="n">
-        <v>5131.335705825047</v>
+        <v>5152.852960001039</v>
       </c>
       <c r="E149" t="n">
-        <v>5063.904296875</v>
+        <v>5041.4326171875</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46048</v>
+        <v>46064</v>
       </c>
       <c r="B150" t="n">
-        <v>4985.703159698522</v>
+        <v>4994.111624438245</v>
       </c>
       <c r="C150" t="n">
-        <v>4822.628147945048</v>
+        <v>4814.603689857313</v>
       </c>
       <c r="D150" t="n">
-        <v>5154.858140862224</v>
+        <v>5151.314464013124</v>
       </c>
       <c r="E150" t="n">
-        <v>5057.650390625</v>
+        <v>5075.75927734375</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46049</v>
+        <v>46065</v>
       </c>
       <c r="B151" t="n">
-        <v>4999.066653225707</v>
+        <v>4985.475951311962</v>
       </c>
       <c r="C151" t="n">
-        <v>4816.627307500248</v>
+        <v>4813.608658586528</v>
       </c>
       <c r="D151" t="n">
-        <v>5181.820947229663</v>
+        <v>5158.043353577128</v>
       </c>
       <c r="E151" t="n">
-        <v>5187.36669921875</v>
+        <v>4920.12548828125</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46050</v>
+        <v>46066</v>
       </c>
       <c r="B152" t="n">
-        <v>5019.060247419912</v>
+        <v>4985.232318630234</v>
       </c>
       <c r="C152" t="n">
-        <v>4852.015327166203</v>
+        <v>4806.573068066156</v>
       </c>
       <c r="D152" t="n">
-        <v>5168.759622913696</v>
+        <v>5149.333654290877</v>
       </c>
       <c r="E152" t="n">
-        <v>5536.52734375</v>
+        <v>5043.77783203125</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46051</v>
+        <v>46067</v>
       </c>
       <c r="B153" t="n">
-        <v>5013.229669384166</v>
+        <v>4995.0700353334</v>
       </c>
       <c r="C153" t="n">
-        <v>4850.521547245372</v>
+        <v>4830.691195428444</v>
       </c>
       <c r="D153" t="n">
-        <v>5179.440753047313</v>
+        <v>5171.595949174343</v>
       </c>
       <c r="E153" t="n">
-        <v>5467.4462890625</v>
+        <v>5021.64599609375</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46052</v>
+        <v>46068</v>
       </c>
       <c r="B154" t="n">
-        <v>5010.899786773303</v>
+        <v>5002.492720664041</v>
       </c>
       <c r="C154" t="n">
-        <v>4845.031952170444</v>
+        <v>4829.904610276092</v>
       </c>
       <c r="D154" t="n">
-        <v>5193.725055974137</v>
+        <v>5178.334116341261</v>
       </c>
       <c r="E154" t="n">
-        <v>4912.69970703125</v>
+        <v>5022.30224609375</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="B155" t="n">
-        <v>5016.562550996196</v>
+        <v>5029.104674999034</v>
       </c>
       <c r="C155" t="n">
-        <v>4855.004111401163</v>
+        <v>4859.503960552755</v>
       </c>
       <c r="D155" t="n">
-        <v>5190.861127130815</v>
+        <v>5199.687706241644</v>
       </c>
       <c r="E155" t="n">
-        <v>4834.16162109375</v>
+        <v>4996.603515625</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46054</v>
+        <v>46070</v>
       </c>
       <c r="B156" t="n">
-        <v>5009.859933061692</v>
+        <v>5038.063677979701</v>
       </c>
       <c r="C156" t="n">
-        <v>4834.659984255068</v>
+        <v>4872.520670850408</v>
       </c>
       <c r="D156" t="n">
-        <v>5183.879920727379</v>
+        <v>5207.755274773753</v>
       </c>
       <c r="E156" t="n">
-        <v>4760.32666015625</v>
+        <v>4864.6728515625</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46055</v>
+        <v>46071</v>
       </c>
       <c r="B157" t="n">
-        <v>5017.822846705309</v>
+        <v>5069.620393877576</v>
       </c>
       <c r="C157" t="n">
-        <v>4841.61443821203</v>
+        <v>4901.505630517239</v>
       </c>
       <c r="D157" t="n">
-        <v>5200.12346673453</v>
+        <v>5240.906506672187</v>
       </c>
       <c r="E157" t="n">
-        <v>4785.6171875</v>
+        <v>4977.79296875</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46056</v>
+        <v>46072</v>
       </c>
       <c r="B158" t="n">
-        <v>5014.666217695274</v>
+        <v>5077.093889005126</v>
       </c>
       <c r="C158" t="n">
-        <v>4851.698002703891</v>
+        <v>4902.809293429342</v>
       </c>
       <c r="D158" t="n">
-        <v>5191.498194414022</v>
+        <v>5231.159742791514</v>
       </c>
       <c r="E158" t="n">
-        <v>4956.98681640625</v>
+        <v>4998.19921875</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46057</v>
+        <v>46073</v>
       </c>
       <c r="B159" t="n">
-        <v>5020.161296095217</v>
+        <v>5091.757940777432</v>
       </c>
       <c r="C159" t="n">
-        <v>4839.053246304612</v>
+        <v>4926.129223462964</v>
       </c>
       <c r="D159" t="n">
-        <v>5203.219662409762</v>
+        <v>5266.288990154475</v>
       </c>
       <c r="E159" t="n">
-        <v>5023.80615234375</v>
+        <v>5113.32421875</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46058</v>
+        <v>46074</v>
       </c>
       <c r="B160" t="n">
-        <v>5002.211719860756</v>
+        <v>5114.741346297295</v>
       </c>
       <c r="C160" t="n">
-        <v>4825.128251251445</v>
+        <v>4934.888154092763</v>
       </c>
       <c r="D160" t="n">
-        <v>5183.305881803974</v>
+        <v>5281.085672745211</v>
       </c>
       <c r="E160" t="n">
-        <v>4695.63037109375</v>
+        <v>5140.05224609375</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46059</v>
+        <v>46075</v>
       </c>
       <c r="B161" t="n">
-        <v>4990.436235692759</v>
+        <v>5133.023136212798</v>
       </c>
       <c r="C161" t="n">
-        <v>4826.100801295114</v>
+        <v>4966.498939900103</v>
       </c>
       <c r="D161" t="n">
-        <v>5164.906058123669</v>
+        <v>5304.048152269485</v>
       </c>
       <c r="E161" t="n">
-        <v>4940.42236328125</v>
+        <v>5187.380859375</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46060</v>
+        <v>46076</v>
       </c>
       <c r="B162" t="n">
-        <v>4989.547667557759</v>
+        <v>5167.733622647159</v>
       </c>
       <c r="C162" t="n">
-        <v>4824.428850846169</v>
+        <v>5007.972374415309</v>
       </c>
       <c r="D162" t="n">
-        <v>5174.115623154834</v>
+        <v>5345.562827914383</v>
       </c>
       <c r="E162" t="n">
-        <v>4989.26904296875</v>
+        <v>5255.55078125</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46061</v>
+        <v>46077</v>
       </c>
       <c r="B163" t="n">
-        <v>4979.328746020044</v>
+        <v>5181.620695292757</v>
       </c>
       <c r="C163" t="n">
-        <v>4785.149075309858</v>
+        <v>5031.062818781224</v>
       </c>
       <c r="D163" t="n">
-        <v>5155.989634862502</v>
+        <v>5352.497963113022</v>
       </c>
       <c r="E163" t="n">
-        <v>5042.5322265625</v>
+        <v>5168.69970703125</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46062</v>
+        <v>46078</v>
       </c>
       <c r="B164" t="n">
-        <v>4986.866014745759</v>
+        <v>5214.601176576673</v>
       </c>
       <c r="C164" t="n">
-        <v>4828.360063378632</v>
+        <v>5052.372328324819</v>
       </c>
       <c r="D164" t="n">
-        <v>5157.734671972365</v>
+        <v>5385.541298819861</v>
       </c>
       <c r="E164" t="n">
-        <v>5035.80712890625</v>
+        <v>5179.78759765625</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46063</v>
+        <v>46079</v>
       </c>
       <c r="B165" t="n">
-        <v>4986.34213937312</v>
+        <v>5219.746406620298</v>
       </c>
       <c r="C165" t="n">
-        <v>4826.441072414104</v>
+        <v>5062.828989949597</v>
       </c>
       <c r="D165" t="n">
-        <v>5143.026361781644</v>
+        <v>5381.062596431814</v>
       </c>
       <c r="E165" t="n">
-        <v>5041.4326171875</v>
+        <v>5196.6904296875</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46064</v>
+        <v>46080</v>
       </c>
       <c r="B166" t="n">
-        <v>4997.407822610746</v>
+        <v>5228.176453396662</v>
       </c>
       <c r="C166" t="n">
-        <v>4830.606301513664</v>
+        <v>5040.502831557616</v>
       </c>
       <c r="D166" t="n">
-        <v>5174.918172775112</v>
+        <v>5399.137401642704</v>
       </c>
       <c r="E166" t="n">
-        <v>5075.75927734375</v>
+        <v>5291.09228515625</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46065</v>
+        <v>46081</v>
       </c>
       <c r="B167" t="n">
-        <v>4987.759875607119</v>
+        <v>5240.965928210644</v>
       </c>
       <c r="C167" t="n">
-        <v>4814.5752784486</v>
+        <v>5086.729003540501</v>
       </c>
       <c r="D167" t="n">
-        <v>5173.074221377979</v>
+        <v>5416.14302286124</v>
       </c>
       <c r="E167" t="n">
-        <v>4920.12548828125</v>
+        <v>5372.89599609375</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46066</v>
+        <v>46082</v>
       </c>
       <c r="B168" t="n">
-        <v>4986.728329845077</v>
+        <v>5245.14214620344</v>
       </c>
       <c r="C168" t="n">
-        <v>4813.826529569396</v>
+        <v>5079.203877123245</v>
       </c>
       <c r="D168" t="n">
-        <v>5152.540097028117</v>
+        <v>5418.36889986171</v>
       </c>
       <c r="E168" t="n">
-        <v>5043.77783203125</v>
+        <v>5435.98974609375</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46067</v>
+        <v>46083</v>
       </c>
       <c r="B169" t="n">
-        <v>4998.662090963975</v>
+        <v>5261.986463641984</v>
       </c>
       <c r="C169" t="n">
-        <v>4828.932554158261</v>
+        <v>5083.821342430119</v>
       </c>
       <c r="D169" t="n">
-        <v>5174.133629769712</v>
+        <v>5430.639109763146</v>
       </c>
       <c r="E169" t="n">
-        <v>5021.64599609375</v>
+        <v>5357.2265625</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46068</v>
+        <v>46084</v>
       </c>
       <c r="B170" t="n">
-        <v>5002.913595418325</v>
+        <v>5254.498178503613</v>
       </c>
       <c r="C170" t="n">
-        <v>4818.064840027454</v>
+        <v>5082.661684492316</v>
       </c>
       <c r="D170" t="n">
-        <v>5161.608615020628</v>
+        <v>5415.644926616896</v>
       </c>
       <c r="E170" t="n">
-        <v>5022.30224609375</v>
+        <v>5144.81201171875</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46069</v>
+        <v>46085</v>
       </c>
       <c r="B171" t="n">
-        <v>5026.083473626094</v>
+        <v>5262.94084969988</v>
       </c>
       <c r="C171" t="n">
-        <v>4850.416971061177</v>
+        <v>5084.913642609607</v>
       </c>
       <c r="D171" t="n">
-        <v>5199.879156318846</v>
+        <v>5441.867620221787</v>
       </c>
       <c r="E171" t="n">
-        <v>4996.603515625</v>
+        <v>5176.455078125</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="B172" t="n">
-        <v>5041.82527709995</v>
+        <v>5240.820320717487</v>
       </c>
       <c r="C172" t="n">
-        <v>4870.164307346056</v>
+        <v>5077.803201220724</v>
       </c>
       <c r="D172" t="n">
-        <v>5218.831366793674</v>
+        <v>5406.546813184456</v>
       </c>
       <c r="E172" t="n">
-        <v>4864.6728515625</v>
+        <v>5102.1650390625</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46071</v>
+        <v>46087</v>
       </c>
       <c r="B173" t="n">
-        <v>5069.231156764709</v>
+        <v>5219.76902607283</v>
       </c>
       <c r="C173" t="n">
-        <v>4897.202855394612</v>
+        <v>5045.340600345266</v>
       </c>
       <c r="D173" t="n">
-        <v>5242.282272281647</v>
+        <v>5389.942120282913</v>
       </c>
       <c r="E173" t="n">
-        <v>4977.79296875</v>
+        <v>5180.2177734375</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46072</v>
+        <v>46088</v>
       </c>
       <c r="B174" t="n">
-        <v>5075.424687465161</v>
+        <v>5201.439806449669</v>
       </c>
       <c r="C174" t="n">
-        <v>4905.8855641912</v>
+        <v>5022.8469421658</v>
       </c>
       <c r="D174" t="n">
-        <v>5255.418190903624</v>
+        <v>5384.590980957792</v>
       </c>
       <c r="E174" t="n">
-        <v>4998.19921875</v>
+        <v>5174.09228515625</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46073</v>
+        <v>46089</v>
       </c>
       <c r="B175" t="n">
-        <v>5089.163334964967</v>
+        <v>5173.490275815291</v>
       </c>
       <c r="C175" t="n">
-        <v>4901.104682549684</v>
+        <v>5007.05032952161</v>
       </c>
       <c r="D175" t="n">
-        <v>5265.78824710136</v>
+        <v>5348.261052771883</v>
       </c>
       <c r="E175" t="n">
-        <v>5113.32421875</v>
+        <v>5082.99365234375</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46074</v>
+        <v>46090</v>
       </c>
       <c r="B176" t="n">
-        <v>5114.239660220802</v>
+        <v>5157.868923227566</v>
       </c>
       <c r="C176" t="n">
-        <v>4925.881054429458</v>
+        <v>4977.421756454161</v>
       </c>
       <c r="D176" t="n">
-        <v>5297.992467809187</v>
+        <v>5324.452975441386</v>
       </c>
       <c r="E176" t="n">
-        <v>5140.05224609375</v>
+        <v>5146.44091796875</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46075</v>
+        <v>46091</v>
       </c>
       <c r="B177" t="n">
-        <v>5129.481305051047</v>
+        <v>5118.262727354587</v>
       </c>
       <c r="C177" t="n">
-        <v>4960.438660632728</v>
+        <v>4947.197638248085</v>
       </c>
       <c r="D177" t="n">
-        <v>5293.369470053267</v>
+        <v>5279.866795600266</v>
       </c>
       <c r="E177" t="n">
-        <v>5187.380859375</v>
+        <v>5195.64208984375</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46076</v>
+        <v>46092</v>
       </c>
       <c r="B178" t="n">
-        <v>5161.010348738978</v>
+        <v>5095.626559268118</v>
       </c>
       <c r="C178" t="n">
-        <v>4981.534235321312</v>
+        <v>4927.077914269885</v>
       </c>
       <c r="D178" t="n">
-        <v>5328.589511043079</v>
+        <v>5266.023195823162</v>
       </c>
       <c r="E178" t="n">
-        <v>5255.55078125</v>
+        <v>5144.99365234375</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46077</v>
+        <v>46093</v>
       </c>
       <c r="B179" t="n">
-        <v>5182.061690587566</v>
+        <v>5044.144097067217</v>
       </c>
       <c r="C179" t="n">
-        <v>4997.270132970641</v>
+        <v>4876.847963246971</v>
       </c>
       <c r="D179" t="n">
-        <v>5354.218258578328</v>
+        <v>5207.845744886057</v>
       </c>
       <c r="E179" t="n">
-        <v>5168.69970703125</v>
+        <v>5111.07470703125</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46078</v>
+        <v>46094</v>
       </c>
       <c r="B180" t="n">
-        <v>5211.380969608154</v>
+        <v>4996.095275590428</v>
       </c>
       <c r="C180" t="n">
-        <v>5040.180310879688</v>
+        <v>4821.27445270107</v>
       </c>
       <c r="D180" t="n">
-        <v>5377.85641078682</v>
+        <v>5174.419272059876</v>
       </c>
       <c r="E180" t="n">
-        <v>5179.78759765625</v>
+        <v>5029.34423828125</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46079</v>
+        <v>46095</v>
       </c>
       <c r="B181" t="n">
-        <v>5215.827873478634</v>
+        <v>4953.733934962402</v>
       </c>
       <c r="C181" t="n">
-        <v>5024.458267389385</v>
+        <v>4787.463100813634</v>
       </c>
       <c r="D181" t="n">
-        <v>5376.584991206063</v>
+        <v>5126.465624468696</v>
       </c>
       <c r="E181" t="n">
-        <v>5196.6904296875</v>
+        <v>5021.23486328125</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46080</v>
+        <v>46096</v>
       </c>
       <c r="B182" t="n">
-        <v>5223.98703519326</v>
+        <v>4905.25713259</v>
       </c>
       <c r="C182" t="n">
-        <v>5050.193881561567</v>
+        <v>4735.41933497558</v>
       </c>
       <c r="D182" t="n">
-        <v>5409.027755507087</v>
+        <v>5072.568941836215</v>
       </c>
       <c r="E182" t="n">
-        <v>5291.09228515625</v>
+        <v>4984.1162109375</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46081</v>
+        <v>46097</v>
       </c>
       <c r="B183" t="n">
-        <v>5239.575366964773</v>
+        <v>4873.077693505968</v>
       </c>
       <c r="C183" t="n">
-        <v>5065.719373176253</v>
+        <v>4694.551792666667</v>
       </c>
       <c r="D183" t="n">
-        <v>5407.133013546052</v>
+        <v>5032.669408993667</v>
       </c>
       <c r="E183" t="n">
-        <v>5372.89599609375</v>
+        <v>5000.9228515625</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46082</v>
+        <v>46098</v>
       </c>
       <c r="B184" t="n">
-        <v>5241.445690179065</v>
+        <v>4821.260130053191</v>
       </c>
       <c r="C184" t="n">
-        <v>5065.199981118526</v>
+        <v>4654.032524380462</v>
       </c>
       <c r="D184" t="n">
-        <v>5422.509557672882</v>
+        <v>5001.626691702385</v>
       </c>
       <c r="E184" t="n">
-        <v>5435.98974609375</v>
+        <v>4994.1279296875</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46083</v>
+        <v>46099</v>
       </c>
       <c r="B185" t="n">
-        <v>5255.847130205669</v>
+        <v>4791.040510677137</v>
       </c>
       <c r="C185" t="n">
-        <v>5090.379659525101</v>
+        <v>4614.442873718252</v>
       </c>
       <c r="D185" t="n">
-        <v>5434.835679995047</v>
+        <v>4956.307909617383</v>
       </c>
       <c r="E185" t="n">
-        <v>5357.2265625</v>
+        <v>4827.228515625</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46084</v>
+        <v>46100</v>
       </c>
       <c r="B186" t="n">
-        <v>5256.241880867425</v>
+        <v>4736.780249130609</v>
       </c>
       <c r="C186" t="n">
-        <v>5073.267645927103</v>
+        <v>4565.196810695485</v>
       </c>
       <c r="D186" t="n">
-        <v>5432.747477308068</v>
+        <v>4907.216176435798</v>
       </c>
       <c r="E186" t="n">
-        <v>5144.81201171875</v>
+        <v>4654.67138671875</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46085</v>
+        <v>46101</v>
       </c>
       <c r="B187" t="n">
-        <v>5261.698868114676</v>
+        <v>4690.829020757859</v>
       </c>
       <c r="C187" t="n">
-        <v>5080.616478469898</v>
+        <v>4519.597198211464</v>
       </c>
       <c r="D187" t="n">
-        <v>5428.050719721677</v>
+        <v>4860.979795677799</v>
       </c>
       <c r="E187" t="n">
-        <v>5176.455078125</v>
+        <v>4509.33447265625</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46086</v>
+        <v>46102</v>
       </c>
       <c r="B188" t="n">
-        <v>5239.490255637514</v>
+        <v>4655.400585992004</v>
       </c>
       <c r="C188" t="n">
-        <v>5064.829143919025</v>
+        <v>4498.67392396233</v>
       </c>
       <c r="D188" t="n">
-        <v>5408.711811874372</v>
+        <v>4821.653733127099</v>
       </c>
       <c r="E188" t="n">
-        <v>5102.1650390625</v>
+        <v>4504.21630859375</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46087</v>
+        <v>46103</v>
       </c>
       <c r="B189" t="n">
-        <v>5218.693149189161</v>
+        <v>4618.543029846405</v>
       </c>
       <c r="C189" t="n">
-        <v>5052.624516456342</v>
+        <v>4464.381572937156</v>
       </c>
       <c r="D189" t="n">
-        <v>5386.21129390745</v>
+        <v>4798.722365513062</v>
       </c>
       <c r="E189" t="n">
-        <v>5180.2177734375</v>
+        <v>4471.259765625</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46088</v>
+        <v>46104</v>
       </c>
       <c r="B190" t="n">
-        <v>5203.585573472923</v>
+        <v>4602.414964602078</v>
       </c>
       <c r="C190" t="n">
-        <v>5034.667946965204</v>
+        <v>4429.313106171187</v>
       </c>
       <c r="D190" t="n">
-        <v>5376.261935087009</v>
+        <v>4766.386914049674</v>
       </c>
       <c r="E190" t="n">
-        <v>5174.09228515625</v>
+        <v>4444.1826171875</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46089</v>
+        <v>46105</v>
       </c>
       <c r="B191" t="n">
-        <v>5173.636860785366</v>
+        <v>4570.727727167768</v>
       </c>
       <c r="C191" t="n">
-        <v>4991.293779407052</v>
+        <v>4398.97549864115</v>
       </c>
       <c r="D191" t="n">
-        <v>5358.209566037361</v>
+        <v>4726.085795528194</v>
       </c>
       <c r="E191" t="n">
-        <v>5082.99365234375</v>
+        <v>4548.10546875</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46090</v>
+        <v>46106</v>
       </c>
       <c r="B192" t="n">
-        <v>5155.75325612602</v>
+        <v>4564.27398308856</v>
       </c>
       <c r="C192" t="n">
-        <v>4983.266540360835</v>
+        <v>4389.188267289177</v>
       </c>
       <c r="D192" t="n">
-        <v>5330.212486671432</v>
+        <v>4738.191260573411</v>
       </c>
       <c r="E192" t="n">
-        <v>5146.44091796875</v>
+        <v>4499.9892578125</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46091</v>
+        <v>46107</v>
       </c>
       <c r="B193" t="n">
-        <v>5124.078719506824</v>
+        <v>4536.892476421621</v>
       </c>
       <c r="C193" t="n">
-        <v>4956.235091279804</v>
+        <v>4363.598494246233</v>
       </c>
       <c r="D193" t="n">
-        <v>5295.951485840462</v>
+        <v>4724.503863661687</v>
       </c>
       <c r="E193" t="n">
-        <v>5195.64208984375</v>
+        <v>4406.93994140625</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46092</v>
+        <v>46108</v>
       </c>
       <c r="B194" t="n">
-        <v>5098.371865049046</v>
+        <v>4520.343842540509</v>
       </c>
       <c r="C194" t="n">
-        <v>4921.92099074309</v>
+        <v>4350.606638079514</v>
       </c>
       <c r="D194" t="n">
-        <v>5272.838418022106</v>
+        <v>4692.327290652293</v>
       </c>
       <c r="E194" t="n">
-        <v>5144.99365234375</v>
+        <v>4499.17333984375</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46093</v>
+        <v>46109</v>
       </c>
       <c r="B195" t="n">
-        <v>5046.585411523402</v>
+        <v>4516.200924655754</v>
       </c>
       <c r="C195" t="n">
-        <v>4874.2223099657</v>
+        <v>4329.284980755664</v>
       </c>
       <c r="D195" t="n">
-        <v>5212.797716274241</v>
+        <v>4687.231646578345</v>
       </c>
       <c r="E195" t="n">
-        <v>5111.07470703125</v>
+        <v>4497.9765625</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46094</v>
+        <v>46110</v>
       </c>
       <c r="B196" t="n">
-        <v>4998.450943779158</v>
+        <v>4511.83472300892</v>
       </c>
       <c r="C196" t="n">
-        <v>4830.8920916665</v>
+        <v>4336.821108396872</v>
       </c>
       <c r="D196" t="n">
-        <v>5170.087565956408</v>
+        <v>4685.673882479366</v>
       </c>
       <c r="E196" t="n">
-        <v>5029.34423828125</v>
+        <v>4452.71044921875</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46095</v>
+        <v>46111</v>
       </c>
       <c r="B197" t="n">
-        <v>4958.858499155624</v>
+        <v>4528.707113789611</v>
       </c>
       <c r="C197" t="n">
-        <v>4780.740950174483</v>
+        <v>4352.918013583164</v>
       </c>
       <c r="D197" t="n">
-        <v>5129.865929371652</v>
+        <v>4711.821103526208</v>
       </c>
       <c r="E197" t="n">
-        <v>5021.23486328125</v>
+        <v>4507.97314453125</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46096</v>
+        <v>46112</v>
       </c>
       <c r="B198" t="n">
-        <v>4907.831548086088</v>
+        <v>4529.829940253106</v>
       </c>
       <c r="C198" t="n">
-        <v>4725.846060653525</v>
+        <v>4373.690064856034</v>
       </c>
       <c r="D198" t="n">
-        <v>5090.355542613444</v>
+        <v>4692.94991053618</v>
       </c>
       <c r="E198" t="n">
-        <v>4984.1162109375</v>
+        <v>4683.30615234375</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46097</v>
+        <v>46113</v>
       </c>
       <c r="B199" t="n">
-        <v>4872.758575169125</v>
+        <v>4555.310451010809</v>
       </c>
       <c r="C199" t="n">
-        <v>4699.522746560195</v>
+        <v>4383.823742477703</v>
       </c>
       <c r="D199" t="n">
-        <v>5033.733539999538</v>
+        <v>4733.581225983522</v>
       </c>
       <c r="E199" t="n">
-        <v>5000.9228515625</v>
+        <v>4767.40576171875</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46098</v>
+        <v>46114</v>
       </c>
       <c r="B200" t="n">
-        <v>4828.181605693067</v>
+        <v>4558.332392085946</v>
       </c>
       <c r="C200" t="n">
-        <v>4657.680091966286</v>
+        <v>4385.520431887721</v>
       </c>
       <c r="D200" t="n">
-        <v>5005.42558309345</v>
+        <v>4740.11939318571</v>
       </c>
       <c r="E200" t="n">
-        <v>4994.1279296875</v>
+        <v>4668.07666015625</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46099</v>
+        <v>46115</v>
       </c>
       <c r="B201" t="n">
-        <v>4794.162963281434</v>
+        <v>4570.047252401626</v>
       </c>
       <c r="C201" t="n">
-        <v>4617.060232247413</v>
+        <v>4402.477938775845</v>
       </c>
       <c r="D201" t="n">
-        <v>4965.721727254263</v>
+        <v>4746.996484183692</v>
       </c>
       <c r="E201" t="n">
-        <v>4827.228515625</v>
+        <v>4648.1611328125</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46100</v>
+        <v>46116</v>
       </c>
       <c r="B202" t="n">
-        <v>4738.85685460783</v>
+        <v>4591.478714291254</v>
       </c>
       <c r="C202" t="n">
-        <v>4563.703442757745</v>
+        <v>4413.41763141889</v>
       </c>
       <c r="D202" t="n">
-        <v>4900.185674571754</v>
+        <v>4763.714853224558</v>
       </c>
       <c r="E202" t="n">
-        <v>4654.67138671875</v>
+        <v>4649.1181640625</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46101</v>
+        <v>46117</v>
       </c>
       <c r="B203" t="n">
-        <v>4692.088835121381</v>
+        <v>4609.521081889357</v>
       </c>
       <c r="C203" t="n">
-        <v>4525.059831567742</v>
+        <v>4441.296216365352</v>
       </c>
       <c r="D203" t="n">
-        <v>4871.56025264847</v>
+        <v>4798.254670609213</v>
       </c>
       <c r="E203" t="n">
-        <v>4509.33447265625</v>
+        <v>4601.5048828125</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46102</v>
+        <v>46118</v>
       </c>
       <c r="B204" t="n">
-        <v>4658.732786555287</v>
+        <v>4645.242519562832</v>
       </c>
       <c r="C204" t="n">
-        <v>4491.429510925047</v>
+        <v>4467.604342314859</v>
       </c>
       <c r="D204" t="n">
-        <v>4824.369336973035</v>
+        <v>4826.939940864828</v>
       </c>
       <c r="E204" t="n">
-        <v>4504.21630859375</v>
+        <v>4643.5390625</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46103</v>
+        <v>46119</v>
       </c>
       <c r="B205" t="n">
-        <v>4618.686049762964</v>
+        <v>4661.352448186925</v>
       </c>
       <c r="C205" t="n">
-        <v>4461.573335176528</v>
+        <v>4479.95251204442</v>
       </c>
       <c r="D205" t="n">
-        <v>4789.722173035751</v>
+        <v>4827.406488181686</v>
       </c>
       <c r="E205" t="n">
-        <v>4471.259765625</v>
+        <v>4794.943359375</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46104</v>
+        <v>46120</v>
       </c>
       <c r="B206" t="n">
-        <v>4599.103916184698</v>
+        <v>4697.752881512455</v>
       </c>
       <c r="C206" t="n">
-        <v>4420.0441822741</v>
+        <v>4534.259240038484</v>
       </c>
       <c r="D206" t="n">
-        <v>4763.370909787761</v>
+        <v>4865.963349185252</v>
       </c>
       <c r="E206" t="n">
-        <v>4444.1826171875</v>
+        <v>4700.63037109375</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46105</v>
+        <v>46121</v>
       </c>
       <c r="B207" t="n">
-        <v>4574.193752196463</v>
+        <v>4707.522881374967</v>
       </c>
       <c r="C207" t="n">
-        <v>4392.877589080216</v>
+        <v>4542.615500366786</v>
       </c>
       <c r="D207" t="n">
-        <v>4749.693710136487</v>
+        <v>4879.635002929502</v>
       </c>
       <c r="E207" t="n">
-        <v>4548.10546875</v>
+        <v>4747.31787109375</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46106</v>
+        <v>46122</v>
       </c>
       <c r="B208" t="n">
-        <v>4563.58987247168</v>
+        <v>4721.810571887455</v>
       </c>
       <c r="C208" t="n">
-        <v>4382.762369496015</v>
+        <v>4546.844316216768</v>
       </c>
       <c r="D208" t="n">
-        <v>4729.556695201481</v>
+        <v>4897.447580651111</v>
       </c>
       <c r="E208" t="n">
-        <v>4499.9892578125</v>
+        <v>4735.64111328125</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46107</v>
+        <v>46123</v>
       </c>
       <c r="B209" t="n">
-        <v>4534.935593175855</v>
+        <v>4741.735772259615</v>
       </c>
       <c r="C209" t="n">
-        <v>4369.724314934539</v>
+        <v>4571.483677410516</v>
       </c>
       <c r="D209" t="n">
-        <v>4717.02315093306</v>
+        <v>4909.757386913921</v>
       </c>
       <c r="E209" t="n">
-        <v>4406.93994140625</v>
+        <v>4733.71923828125</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46108</v>
+        <v>46124</v>
       </c>
       <c r="B210" t="n">
-        <v>4517.475198526358</v>
+        <v>4754.384101256001</v>
       </c>
       <c r="C210" t="n">
-        <v>4352.659363326343</v>
+        <v>4585.224289396162</v>
       </c>
       <c r="D210" t="n">
-        <v>4681.02673332622</v>
+        <v>4931.864720704542</v>
       </c>
       <c r="E210" t="n">
-        <v>4499.17333984375</v>
+        <v>4652.7919921875</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46109</v>
+        <v>46125</v>
       </c>
       <c r="B211" t="n">
-        <v>4515.445148611992</v>
+        <v>4781.103526118912</v>
       </c>
       <c r="C211" t="n">
-        <v>4355.247785640227</v>
+        <v>4636.358278989372</v>
       </c>
       <c r="D211" t="n">
-        <v>4677.247024102919</v>
+        <v>4948.891223881405</v>
       </c>
       <c r="E211" t="n">
-        <v>4497.9765625</v>
+        <v>4742.3955078125</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B212" t="n">
-        <v>4508.064796011754</v>
+        <v>4784.96290940506</v>
       </c>
       <c r="C212" t="n">
-        <v>4343.656203948848</v>
+        <v>4605.302911158356</v>
       </c>
       <c r="D212" t="n">
-        <v>4690.133845375677</v>
+        <v>4958.025239167818</v>
       </c>
       <c r="E212" t="n">
-        <v>4452.71044921875</v>
+        <v>4828.4228515625</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B213" t="n">
-        <v>4521.787409936685</v>
+        <v>4806.292595074972</v>
       </c>
       <c r="C213" t="n">
-        <v>4349.532863073194</v>
+        <v>4629.174380128204</v>
       </c>
       <c r="D213" t="n">
-        <v>4692.532820251288</v>
+        <v>4977.011353490322</v>
       </c>
       <c r="E213" t="n">
-        <v>4507.97314453125</v>
+        <v>4812.73828125</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B214" t="n">
-        <v>4530.111350766781</v>
+        <v>4798.656520269463</v>
       </c>
       <c r="C214" t="n">
-        <v>4353.027189040887</v>
+        <v>4633.582143098645</v>
       </c>
       <c r="D214" t="n">
-        <v>4705.52179485041</v>
+        <v>4961.921697367188</v>
       </c>
       <c r="E214" t="n">
-        <v>4683.30615234375</v>
+        <v>4777.44384765625</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B215" t="n">
-        <v>4551.972071817479</v>
+        <v>4793.730637553814</v>
       </c>
       <c r="C215" t="n">
-        <v>4394.896583223463</v>
+        <v>4630.758963860814</v>
       </c>
       <c r="D215" t="n">
-        <v>4724.598590291012</v>
+        <v>4959.911936858222</v>
       </c>
       <c r="E215" t="n">
-        <v>4767.40576171875</v>
+        <v>4821.47607421875</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46114</v>
+        <v>46130</v>
       </c>
       <c r="B216" t="n">
-        <v>4554.340936402674</v>
+        <v>4793.191083542119</v>
       </c>
       <c r="C216" t="n">
-        <v>4382.994918852008</v>
+        <v>4631.142749201915</v>
       </c>
       <c r="D216" t="n">
-        <v>4726.302557312909</v>
+        <v>4982.003366635642</v>
       </c>
       <c r="E216" t="n">
-        <v>4668.07666015625</v>
+        <v>4777.1845703125</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46115</v>
+        <v>46131</v>
       </c>
       <c r="B217" t="n">
-        <v>4565.833153731679</v>
+        <v>4784.693339985245</v>
       </c>
       <c r="C217" t="n">
-        <v>4397.020062084737</v>
+        <v>4625.752305236362</v>
       </c>
       <c r="D217" t="n">
-        <v>4744.124823496523</v>
+        <v>4948.887839660135</v>
       </c>
       <c r="E217" t="n">
-        <v>4648.1611328125</v>
+        <v>4738.798828125</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46116</v>
+        <v>46132</v>
       </c>
       <c r="B218" t="n">
-        <v>4590.113754269892</v>
+        <v>4790.153761824093</v>
       </c>
       <c r="C218" t="n">
-        <v>4410.975367207753</v>
+        <v>4625.051665155976</v>
       </c>
       <c r="D218" t="n">
-        <v>4764.877440013142</v>
+        <v>4963.404917340203</v>
       </c>
       <c r="E218" t="n">
-        <v>4649.1181640625</v>
+        <v>4807.7041015625</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46117</v>
+        <v>46133</v>
       </c>
       <c r="B219" t="n">
-        <v>4605.901498776865</v>
+        <v>4773.19342410327</v>
       </c>
       <c r="C219" t="n">
-        <v>4434.707230019842</v>
+        <v>4610.983002112018</v>
       </c>
       <c r="D219" t="n">
-        <v>4768.614213381894</v>
+        <v>4949.721140725738</v>
       </c>
       <c r="E219" t="n">
-        <v>4601.5048828125</v>
+        <v>4729.26611328125</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46118</v>
+        <v>46134</v>
       </c>
       <c r="B220" t="n">
-        <v>4639.231188712299</v>
+        <v>4774.664713803499</v>
       </c>
       <c r="C220" t="n">
-        <v>4473.092384380263</v>
+        <v>4609.916541813002</v>
       </c>
       <c r="D220" t="n">
-        <v>4815.644551246784</v>
+        <v>4959.242439022961</v>
       </c>
       <c r="E220" t="n">
-        <v>4643.5390625</v>
+        <v>4714.892578125</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46119</v>
+        <v>46135</v>
       </c>
       <c r="B221" t="n">
-        <v>4663.273945183055</v>
+        <v>4748.610512870096</v>
       </c>
       <c r="C221" t="n">
-        <v>4483.915886226525</v>
+        <v>4581.148540602867</v>
       </c>
       <c r="D221" t="n">
-        <v>4846.622515521576</v>
+        <v>4916.996010585466</v>
       </c>
       <c r="E221" t="n">
-        <v>4794.943359375</v>
+        <v>4687.91357421875</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46120</v>
+        <v>46136</v>
       </c>
       <c r="B222" t="n">
-        <v>4696.735912684925</v>
+        <v>4727.131085327828</v>
       </c>
       <c r="C222" t="n">
-        <v>4514.238820270659</v>
+        <v>4557.02625404261</v>
       </c>
       <c r="D222" t="n">
-        <v>4857.504275727777</v>
+        <v>4891.35916409561</v>
       </c>
       <c r="E222" t="n">
-        <v>4700.63037109375</v>
+        <v>4697.42529296875</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46121</v>
+        <v>46137</v>
       </c>
       <c r="B223" t="n">
-        <v>4706.461223105455</v>
+        <v>4712.262387898668</v>
       </c>
       <c r="C223" t="n">
-        <v>4528.295845836524</v>
+        <v>4539.941763179321</v>
       </c>
       <c r="D223" t="n">
-        <v>4896.962381469137</v>
+        <v>4881.620464681912</v>
       </c>
       <c r="E223" t="n">
-        <v>4747.31787109375</v>
+        <v>4692.419921875</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46122</v>
+        <v>46138</v>
       </c>
       <c r="B224" t="n">
-        <v>4721.04143846501</v>
+        <v>4691.947286321362</v>
       </c>
       <c r="C224" t="n">
-        <v>4552.707457546995</v>
+        <v>4516.156401499535</v>
       </c>
       <c r="D224" t="n">
-        <v>4892.368330506535</v>
+        <v>4865.152705826817</v>
       </c>
       <c r="E224" t="n">
-        <v>4735.64111328125</v>
+        <v>4675.0712890625</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46123</v>
+        <v>46139</v>
       </c>
       <c r="B225" t="n">
-        <v>4744.220378093203</v>
+        <v>4688.311231875351</v>
       </c>
       <c r="C225" t="n">
-        <v>4568.408427426868</v>
+        <v>4515.629458984047</v>
       </c>
       <c r="D225" t="n">
-        <v>4913.920068950212</v>
+        <v>4858.898871535708</v>
       </c>
       <c r="E225" t="n">
-        <v>4733.71923828125</v>
+        <v>4684.798828125</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46124</v>
+        <v>46140</v>
       </c>
       <c r="B226" t="n">
-        <v>4754.89428061225</v>
+        <v>4665.102471445883</v>
       </c>
       <c r="C226" t="n">
-        <v>4581.682370560007</v>
+        <v>4506.035684235008</v>
       </c>
       <c r="D226" t="n">
-        <v>4929.428973834466</v>
+        <v>4836.473119673798</v>
       </c>
       <c r="E226" t="n">
-        <v>4652.7919921875</v>
+        <v>4586.419921875</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46125</v>
+        <v>46141</v>
       </c>
       <c r="B227" t="n">
-        <v>4779.36789245484</v>
+        <v>4663.217275957238</v>
       </c>
       <c r="C227" t="n">
-        <v>4613.008210986294</v>
+        <v>4492.183287669944</v>
       </c>
       <c r="D227" t="n">
-        <v>4954.273952346368</v>
+        <v>4840.474834707082</v>
       </c>
       <c r="E227" t="n">
-        <v>4742.3955078125</v>
+        <v>4551.4296875</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46126</v>
+        <v>46142</v>
       </c>
       <c r="B228" t="n">
-        <v>4791.166238922194</v>
+        <v>4636.660030218686</v>
       </c>
       <c r="C228" t="n">
-        <v>4608.98615952054</v>
+        <v>4461.807388319154</v>
       </c>
       <c r="D228" t="n">
-        <v>4962.167040033509</v>
+        <v>4820.033263966431</v>
       </c>
       <c r="E228" t="n">
-        <v>4828.4228515625</v>
+        <v>4618.77001953125</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46127</v>
+        <v>46143</v>
       </c>
       <c r="B229" t="n">
-        <v>4809.422781869313</v>
+        <v>4617.413231911665</v>
       </c>
       <c r="C229" t="n">
-        <v>4643.29735521783</v>
+        <v>4446.944526474666</v>
       </c>
       <c r="D229" t="n">
-        <v>4971.407683848573</v>
+        <v>4791.393843052741</v>
       </c>
       <c r="E229" t="n">
-        <v>4812.73828125</v>
+        <v>4604.0791015625</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46128</v>
+        <v>46144</v>
       </c>
       <c r="B230" t="n">
-        <v>4801.470099258266</v>
+        <v>4607.320994981063</v>
       </c>
       <c r="C230" t="n">
-        <v>4634.322888008513</v>
+        <v>4449.701980183373</v>
       </c>
       <c r="D230" t="n">
-        <v>4968.915726099101</v>
+        <v>4784.194463344244</v>
       </c>
       <c r="E230" t="n">
-        <v>4777.44384765625</v>
+        <v>4597.361328125</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46129</v>
+        <v>46145</v>
       </c>
       <c r="B231" t="n">
-        <v>4796.435648042114</v>
+        <v>4594.067360639533</v>
       </c>
       <c r="C231" t="n">
-        <v>4627.325342104667</v>
+        <v>4429.485828070595</v>
       </c>
       <c r="D231" t="n">
-        <v>4979.324408814735</v>
+        <v>4768.206677501727</v>
       </c>
       <c r="E231" t="n">
-        <v>4821.47607421875</v>
+        <v>4607.44873046875</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46130</v>
+        <v>46146</v>
       </c>
       <c r="B232" t="n">
-        <v>4798.631893398217</v>
+        <v>4599.460742664338</v>
       </c>
       <c r="C232" t="n">
-        <v>4624.426971398801</v>
+        <v>4424.605612273656</v>
       </c>
       <c r="D232" t="n">
-        <v>4961.5283482389</v>
+        <v>4774.594426393938</v>
       </c>
       <c r="E232" t="n">
-        <v>4777.1845703125</v>
+        <v>4515.73046875</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46131</v>
+        <v>46147</v>
       </c>
       <c r="B233" t="n">
-        <v>4787.541154644815</v>
+        <v>4586.884309785508</v>
       </c>
       <c r="C233" t="n">
-        <v>4617.435526812186</v>
+        <v>4411.83870723349</v>
       </c>
       <c r="D233" t="n">
-        <v>4951.37216697508</v>
+        <v>4757.344736467888</v>
       </c>
       <c r="E233" t="n">
-        <v>4738.798828125</v>
+        <v>4583.22998046875</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46132</v>
+        <v>46148</v>
       </c>
       <c r="B234" t="n">
-        <v>4790.056172381511</v>
+        <v>4596.832486270021</v>
       </c>
       <c r="C234" t="n">
-        <v>4628.541423210822</v>
+        <v>4427.357830251143</v>
       </c>
       <c r="D234" t="n">
-        <v>4968.649361110305</v>
+        <v>4761.759524742186</v>
       </c>
       <c r="E234" t="n">
-        <v>4807.7041015625</v>
+        <v>4685.2685546875</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46133</v>
+        <v>46149</v>
       </c>
       <c r="B235" t="n">
-        <v>4780.276566660244</v>
+        <v>4582.883084295003</v>
       </c>
       <c r="C235" t="n">
-        <v>4616.12147679401</v>
+        <v>4417.328096625253</v>
       </c>
       <c r="D235" t="n">
-        <v>4943.819394002017</v>
+        <v>4749.70458890904</v>
       </c>
       <c r="E235" t="n">
-        <v>4729.26611328125</v>
+        <v>4695.97412109375</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46134</v>
+        <v>46150</v>
       </c>
       <c r="B236" t="n">
-        <v>4777.882293032763</v>
+        <v>4576.579770942037</v>
       </c>
       <c r="C236" t="n">
-        <v>4595.632661006494</v>
+        <v>4420.8659909193</v>
       </c>
       <c r="D236" t="n">
-        <v>4952.608915484288</v>
+        <v>4741.266112071354</v>
       </c>
       <c r="E236" t="n">
-        <v>4714.892578125</v>
+        <v>4706.30517578125</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46135</v>
+        <v>46151</v>
       </c>
       <c r="B237" t="n">
-        <v>4750.710615749859</v>
+        <v>4579.328114797704</v>
       </c>
       <c r="C237" t="n">
-        <v>4579.064824998048</v>
+        <v>4397.671014489381</v>
       </c>
       <c r="D237" t="n">
-        <v>4942.886636140912</v>
+        <v>4755.523400706164</v>
       </c>
       <c r="E237" t="n">
-        <v>4687.91357421875</v>
+        <v>4711.15576171875</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46136</v>
+        <v>46152</v>
       </c>
       <c r="B238" t="n">
-        <v>4728.339509379798</v>
+        <v>4578.386167899166</v>
       </c>
       <c r="C238" t="n">
-        <v>4557.470742895402</v>
+        <v>4411.970740508464</v>
       </c>
       <c r="D238" t="n">
-        <v>4905.171867471195</v>
+        <v>4748.589636025018</v>
       </c>
       <c r="E238" t="n">
-        <v>4697.42529296875</v>
+        <v>4689.40771484375</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46137</v>
+        <v>46153</v>
       </c>
       <c r="B239" t="n">
-        <v>4715.467083534648</v>
+        <v>4595.16057740577</v>
       </c>
       <c r="C239" t="n">
-        <v>4534.80297995631</v>
+        <v>4428.653741532594</v>
       </c>
       <c r="D239" t="n">
-        <v>4889.114213935155</v>
+        <v>4759.775034870815</v>
       </c>
       <c r="E239" t="n">
-        <v>4692.419921875</v>
+        <v>4754.81640625</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46138</v>
+        <v>46154</v>
       </c>
       <c r="B240" t="n">
-        <v>4691.88764333465</v>
+        <v>4592.667718933466</v>
       </c>
       <c r="C240" t="n">
-        <v>4526.621151441511</v>
+        <v>4427.329542839072</v>
       </c>
       <c r="D240" t="n">
-        <v>4859.884235996775</v>
+        <v>4759.455360530093</v>
       </c>
       <c r="E240" t="n">
-        <v>4675.0712890625</v>
+        <v>4711.0009765625</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46139</v>
+        <v>46155</v>
       </c>
       <c r="B241" t="n">
-        <v>4684.725597493444</v>
+        <v>4611.079753199437</v>
       </c>
       <c r="C241" t="n">
-        <v>4507.635849777031</v>
+        <v>4447.644013941306</v>
       </c>
       <c r="D241" t="n">
-        <v>4859.078814781333</v>
+        <v>4794.09615180763</v>
       </c>
       <c r="E241" t="n">
-        <v>4684.798828125</v>
+        <v>4685.81005859375</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46140</v>
+        <v>46156</v>
       </c>
       <c r="B242" t="n">
-        <v>4668.227530861278</v>
+        <v>4603.70487825814</v>
       </c>
       <c r="C242" t="n">
-        <v>4499.700192814601</v>
+        <v>4433.703164046736</v>
       </c>
       <c r="D242" t="n">
-        <v>4848.336871794149</v>
+        <v>4774.356675277552</v>
       </c>
       <c r="E242" t="n">
-        <v>4586.419921875</v>
+        <v>4647.783203125</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46141</v>
+        <v>46157</v>
       </c>
       <c r="B243" t="n">
-        <v>4662.133632684965</v>
+        <v>4601.876283277381</v>
       </c>
       <c r="C243" t="n">
-        <v>4491.157023307001</v>
+        <v>4437.154573749934</v>
       </c>
       <c r="D243" t="n">
-        <v>4827.007437379963</v>
+        <v>4776.153173145655</v>
       </c>
       <c r="E243" t="n">
-        <v>4551.4296875</v>
+        <v>4540.41552734375</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46142</v>
+        <v>46158</v>
       </c>
       <c r="B244" t="n">
-        <v>4634.255016890338</v>
+        <v>4606.852900604185</v>
       </c>
       <c r="C244" t="n">
-        <v>4455.705688471242</v>
+        <v>4428.775323417804</v>
       </c>
       <c r="D244" t="n">
-        <v>4817.511262917185</v>
+        <v>4781.032497971003</v>
       </c>
       <c r="E244" t="n">
-        <v>4618.77001953125</v>
+        <v>4535.490234375</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46143</v>
+        <v>46159</v>
       </c>
       <c r="B245" t="n">
-        <v>4614.059800856197</v>
+        <v>4605.812817271183</v>
       </c>
       <c r="C245" t="n">
-        <v>4446.883329559991</v>
+        <v>4429.133865441727</v>
       </c>
       <c r="D245" t="n">
-        <v>4785.27269279144</v>
+        <v>4767.917829468844</v>
       </c>
       <c r="E245" t="n">
-        <v>4604.0791015625</v>
+        <v>4534.8125</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46144</v>
+        <v>46160</v>
       </c>
       <c r="B246" t="n">
-        <v>4606.057427441227</v>
+        <v>4620.150298382708</v>
       </c>
       <c r="C246" t="n">
-        <v>4430.917109466252</v>
+        <v>4439.128033888111</v>
       </c>
       <c r="D246" t="n">
-        <v>4780.230777920367</v>
+        <v>4793.305656939016</v>
       </c>
       <c r="E246" t="n">
-        <v>4597.361328125</v>
+        <v>4574.75048828125</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46145</v>
+        <v>46161</v>
       </c>
       <c r="B247" t="n">
-        <v>4589.781674755765</v>
+        <v>4612.935927967132</v>
       </c>
       <c r="C247" t="n">
-        <v>4413.291502545307</v>
+        <v>4447.354111023702</v>
       </c>
       <c r="D247" t="n">
-        <v>4760.969615950883</v>
+        <v>4806.356669795621</v>
       </c>
       <c r="E247" t="n">
-        <v>4607.44873046875</v>
+        <v>4491.31494140625</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46146</v>
+        <v>46162</v>
       </c>
       <c r="B248" t="n">
-        <v>4592.033343557421</v>
+        <v>4624.459835751843</v>
       </c>
       <c r="C248" t="n">
-        <v>4413.043027142761</v>
+        <v>4458.117369408981</v>
       </c>
       <c r="D248" t="n">
-        <v>4767.00612332248</v>
+        <v>4806.040513588571</v>
       </c>
       <c r="E248" t="n">
-        <v>4515.73046875</v>
+        <v>4535.93505859375</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46147</v>
+        <v>46163</v>
       </c>
       <c r="B249" t="n">
-        <v>4586.682669940525</v>
+        <v>4608.207398177543</v>
       </c>
       <c r="C249" t="n">
-        <v>4414.606997935752</v>
+        <v>4430.239913324553</v>
       </c>
       <c r="D249" t="n">
-        <v>4752.811246723384</v>
+        <v>4786.076535459561</v>
       </c>
       <c r="E249" t="n">
-        <v>4583.22998046875</v>
+        <v>4524.57861328125</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46148</v>
+        <v>46164</v>
       </c>
       <c r="B250" t="n">
-        <v>4593.052346601718</v>
+        <v>4595.742083418777</v>
       </c>
       <c r="C250" t="n">
-        <v>4417.794341658467</v>
+        <v>4431.829516036944</v>
       </c>
       <c r="D250" t="n">
-        <v>4758.989499770682</v>
+        <v>4766.888406749724</v>
       </c>
       <c r="E250" t="n">
-        <v>4685.2685546875</v>
+        <v>4494.931640625</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46149</v>
+        <v>46165</v>
       </c>
       <c r="B251" t="n">
-        <v>4578.507350837691</v>
+        <v>4588.598740502625</v>
       </c>
       <c r="C251" t="n">
-        <v>4405.26647836894</v>
+        <v>4416.853583713299</v>
       </c>
       <c r="D251" t="n">
-        <v>4735.786665095289</v>
+        <v>4770.060142346718</v>
       </c>
       <c r="E251" t="n">
-        <v>4695.97412109375</v>
+        <v>4522.34521484375</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46150</v>
+        <v>46166</v>
       </c>
       <c r="B252" t="n">
-        <v>4572.054087364801</v>
+        <v>4574.268431727717</v>
       </c>
       <c r="C252" t="n">
-        <v>4400.149868911938</v>
+        <v>4404.20120714261</v>
       </c>
       <c r="D252" t="n">
-        <v>4740.645712310789</v>
+        <v>4737.106814788587</v>
       </c>
       <c r="E252" t="n">
-        <v>4706.30517578125</v>
+        <v>4562.1640625</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
-        <v>46151</v>
+        <v>46167</v>
       </c>
       <c r="B253" t="n">
-        <v>4577.737962221024</v>
+        <v>4574.486025653905</v>
       </c>
       <c r="C253" t="n">
-        <v>4404.26756296936</v>
+        <v>4401.757810182156</v>
       </c>
       <c r="D253" t="n">
-        <v>4750.205664053291</v>
+        <v>4736.984764226874</v>
       </c>
       <c r="E253" t="n">
-        <v>4711.15576171875</v>
+        <v>4548.4677734375</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
-        <v>46152</v>
+        <v>46168</v>
       </c>
       <c r="B254" t="n">
-        <v>4574.63946398629</v>
+        <v>4552.680339985391</v>
       </c>
       <c r="C254" t="n">
-        <v>4405.188773483665</v>
+        <v>4378.853396817986</v>
       </c>
       <c r="D254" t="n">
-        <v>4737.609559957374</v>
+        <v>4720.987496738354</v>
       </c>
       <c r="E254" t="n">
-        <v>4689.40771484375</v>
+        <v>4515.7841796875</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
-        <v>46153</v>
+        <v>46169</v>
       </c>
       <c r="B255" t="n">
-        <v>4589.129384344516</v>
+        <v>4549.507096465145</v>
       </c>
       <c r="C255" t="n">
-        <v>4407.675844216848</v>
+        <v>4371.794813760662</v>
       </c>
       <c r="D255" t="n">
-        <v>4756.626053516572</v>
+        <v>4723.660853110782</v>
       </c>
       <c r="E255" t="n">
-        <v>4754.81640625</v>
+        <v>4443.1279296875</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
-        <v>46154</v>
+        <v>46170</v>
       </c>
       <c r="B256" t="n">
-        <v>4594.682888211719</v>
+        <v>4518.814372791</v>
       </c>
       <c r="C256" t="n">
-        <v>4419.250632606346</v>
+        <v>4358.586201222575</v>
       </c>
       <c r="D256" t="n">
-        <v>4764.728949882378</v>
+        <v>4680.452390463968</v>
       </c>
       <c r="E256" t="n">
-        <v>4711.0009765625</v>
+        <v>4480.20751953125</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
-        <v>46155</v>
+        <v>46171</v>
       </c>
       <c r="B257" t="n">
-        <v>4610.273008461028</v>
+        <v>4492.515509728613</v>
       </c>
       <c r="C257" t="n">
-        <v>4434.826719444158</v>
+        <v>4312.946434716424</v>
       </c>
       <c r="D257" t="n">
-        <v>4776.590897917255</v>
+        <v>4670.580316582461</v>
       </c>
       <c r="E257" t="n">
-        <v>4685.81005859375</v>
+        <v>4529.62451171875</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
-        <v>46156</v>
+        <v>46172</v>
       </c>
       <c r="B258" t="n">
-        <v>4602.969492734604</v>
+        <v>4472.473048314153</v>
       </c>
       <c r="C258" t="n">
-        <v>4440.239934229972</v>
+        <v>4298.363937012819</v>
       </c>
       <c r="D258" t="n">
-        <v>4772.720095899868</v>
+        <v>4649.454919473784</v>
       </c>
       <c r="E258" t="n">
-        <v>4647.783203125</v>
+        <v>4517.13134765625</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
-        <v>46157</v>
+        <v>46173</v>
       </c>
       <c r="B259" t="n">
-        <v>4601.545285184324</v>
+        <v>4446.475048400186</v>
       </c>
       <c r="C259" t="n">
-        <v>4425.30558460328</v>
+        <v>4272.890133673224</v>
       </c>
       <c r="D259" t="n">
-        <v>4771.227768007813</v>
+        <v>4610.902709430044</v>
       </c>
       <c r="E259" t="n">
-        <v>4540.41552734375</v>
+        <v>4530.79296875</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
-        <v>46158</v>
+        <v>46174</v>
       </c>
       <c r="B260" t="n">
-        <v>4609.879582336762</v>
+        <v>4436.515227868944</v>
       </c>
       <c r="C260" t="n">
-        <v>4440.401885898677</v>
+        <v>4277.752661992758</v>
       </c>
       <c r="D260" t="n">
-        <v>4774.59556734001</v>
+        <v>4600.520218339514</v>
       </c>
       <c r="E260" t="n">
-        <v>4535.490234375</v>
+        <v>4475.79248046875</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
-        <v>46159</v>
+        <v>46175</v>
       </c>
       <c r="B261" t="n">
-        <v>4606.957419648162</v>
+        <v>4406.236900991892</v>
       </c>
       <c r="C261" t="n">
-        <v>4426.584718159139</v>
+        <v>4235.179578435012</v>
       </c>
       <c r="D261" t="n">
-        <v>4783.626541737849</v>
+        <v>4583.388992814257</v>
       </c>
       <c r="E261" t="n">
-        <v>4534.8125</v>
+        <v>4463.0302734375</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
-        <v>46160</v>
+        <v>46176</v>
       </c>
       <c r="B262" t="n">
-        <v>4619.126356111379</v>
+        <v>4396.461124545807</v>
       </c>
       <c r="C262" t="n">
-        <v>4444.840976130965</v>
+        <v>4221.544138271702</v>
       </c>
       <c r="D262" t="n">
-        <v>4800.238798595212</v>
+        <v>4563.012557194626</v>
       </c>
       <c r="E262" t="n">
-        <v>4574.75048828125</v>
+        <v>4448.11572265625</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
-        <v>46161</v>
+        <v>46177</v>
       </c>
       <c r="B263" t="n">
-        <v>4619.909961482859</v>
+        <v>4361.148842080403</v>
       </c>
       <c r="C263" t="n">
-        <v>4448.158413122905</v>
+        <v>4194.474853020055</v>
       </c>
       <c r="D263" t="n">
-        <v>4786.77348367517</v>
+        <v>4531.227639542165</v>
       </c>
       <c r="E263" t="n">
-        <v>4491.31494140625</v>
+        <v>4453.0693359375</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
-        <v>46162</v>
+        <v>46178</v>
       </c>
       <c r="B264" t="n">
-        <v>4628.398732824469</v>
+        <v>4332.272043594116</v>
       </c>
       <c r="C264" t="n">
-        <v>4452.790057034339</v>
+        <v>4157.799086353457</v>
       </c>
       <c r="D264" t="n">
-        <v>4789.24222104927</v>
+        <v>4501.34242778295</v>
       </c>
       <c r="E264" t="n">
-        <v>4535.93505859375</v>
+        <v>4320.01220703125</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
-        <v>46163</v>
+        <v>46179</v>
       </c>
       <c r="B265" t="n">
-        <v>4611.844474846176</v>
+        <v>4311.697528495696</v>
       </c>
       <c r="C265" t="n">
-        <v>4447.369847075416</v>
+        <v>4128.26923189429</v>
       </c>
       <c r="D265" t="n">
-        <v>4780.045987493472</v>
+        <v>4495.794739625759</v>
       </c>
       <c r="E265" t="n">
-        <v>4524.57861328125</v>
+        <v>4296.80859375</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
-        <v>46164</v>
+        <v>46180</v>
       </c>
       <c r="B266" t="n">
-        <v>4599.260584394542</v>
+        <v>4287.164590264916</v>
       </c>
       <c r="C266" t="n">
-        <v>4428.122220636875</v>
+        <v>4111.555256668803</v>
       </c>
       <c r="D266" t="n">
-        <v>4780.681840129804</v>
+        <v>4460.00181688773</v>
       </c>
       <c r="E266" t="n">
-        <v>4494.931640625</v>
+        <v>4334.697265625</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
-        <v>46165</v>
+        <v>46181</v>
       </c>
       <c r="B267" t="n">
-        <v>4594.817384079945</v>
+        <v>4280.567986358534</v>
       </c>
       <c r="C267" t="n">
-        <v>4440.541228188726</v>
+        <v>4112.745397677522</v>
       </c>
       <c r="D267" t="n">
-        <v>4766.195003196046</v>
+        <v>4451.54148881627</v>
       </c>
       <c r="E267" t="n">
-        <v>4522.34521484375</v>
+        <v>4308.56982421875</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
-        <v>46166</v>
+        <v>46182</v>
       </c>
       <c r="B268" t="n">
-        <v>4577.832704226135</v>
+        <v>4255.406053240794</v>
       </c>
       <c r="C268" t="n">
-        <v>4403.124445036838</v>
+        <v>4083.105667775443</v>
       </c>
       <c r="D268" t="n">
-        <v>4758.468713141743</v>
+        <v>4426.88800574162</v>
       </c>
       <c r="E268" t="n">
-        <v>4562.1640625</v>
+        <v>4215.26708984375</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
-        <v>46167</v>
+        <v>46183</v>
       </c>
       <c r="B269" t="n">
-        <v>4575.018557459419</v>
+        <v>4252.314223022331</v>
       </c>
       <c r="C269" t="n">
-        <v>4396.827239523801</v>
+        <v>4091.284341632921</v>
       </c>
       <c r="D269" t="n">
-        <v>4752.515401663944</v>
+        <v>4418.440723385414</v>
       </c>
       <c r="E269" t="n">
-        <v>4548.4677734375</v>
+        <v>4049.58642578125</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
-        <v>46168</v>
+        <v>46184</v>
       </c>
       <c r="B270" t="n">
-        <v>4560.283910590049</v>
+        <v>4225.03354667688</v>
       </c>
       <c r="C270" t="n">
-        <v>4392.325800248936</v>
+        <v>4053.98105687276</v>
       </c>
       <c r="D270" t="n">
-        <v>4738.394012707587</v>
+        <v>4377.354735070697</v>
       </c>
       <c r="E270" t="n">
-        <v>4515.7841796875</v>
+        <v>4211.1201171875</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>46169</v>
+        <v>46185</v>
       </c>
       <c r="B271" t="n">
-        <v>4553.114494966058</v>
+        <v>4205.289031506813</v>
       </c>
       <c r="C271" t="n">
-        <v>4379.491466809434</v>
+        <v>4022.499758000664</v>
       </c>
       <c r="D271" t="n">
-        <v>4725.699078247448</v>
+        <v>4372.355654532419</v>
       </c>
       <c r="E271" t="n">
-        <v>4443.1279296875</v>
+        <v>4209.83251953125</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>46170</v>
+        <v>46186</v>
       </c>
       <c r="B272" t="n">
-        <v>4521.156011911756</v>
+        <v>4194.681152375119</v>
       </c>
       <c r="C272" t="n">
-        <v>4350.802351077119</v>
+        <v>4016.093619840134</v>
       </c>
       <c r="D272" t="n">
-        <v>4694.4138116644</v>
+        <v>4367.991042972667</v>
       </c>
       <c r="E272" t="n">
-        <v>4480.20751953125</v>
+        <v>4220.650390625</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>46171</v>
+        <v>46187</v>
       </c>
       <c r="B273" t="n">
-        <v>4493.803489850305</v>
+        <v>4180.671616160986</v>
       </c>
       <c r="C273" t="n">
-        <v>4332.559221732947</v>
+        <v>4010.078501064342</v>
       </c>
       <c r="D273" t="n">
-        <v>4668.636992348125</v>
+        <v>4364.081452871638</v>
       </c>
       <c r="E273" t="n">
-        <v>4529.62451171875</v>
+        <v>4286.2568359375</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>46172</v>
+        <v>46188</v>
       </c>
       <c r="B274" t="n">
-        <v>4475.586243776932</v>
+        <v>4184.874499221144</v>
       </c>
       <c r="C274" t="n">
-        <v>4301.823937338308</v>
+        <v>4021.880682779329</v>
       </c>
       <c r="D274" t="n">
-        <v>4656.890479135491</v>
+        <v>4369.419212679159</v>
       </c>
       <c r="E274" t="n">
-        <v>4517.13134765625</v>
+        <v>4306.87744140625</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>46173</v>
+        <v>46189</v>
       </c>
       <c r="B275" t="n">
-        <v>4446.148920269172</v>
+        <v>4170.512377971468</v>
       </c>
       <c r="C275" t="n">
-        <v>4273.907409646643</v>
+        <v>3999.645598523428</v>
       </c>
       <c r="D275" t="n">
-        <v>4618.434085989366</v>
+        <v>4351.467503724839</v>
       </c>
       <c r="E275" t="n">
-        <v>4530.79296875</v>
+        <v>4319.31689453125</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>46174</v>
+        <v>46190</v>
       </c>
       <c r="B276" t="n">
-        <v>4432.489727743554</v>
+        <v>4177.957479452448</v>
       </c>
       <c r="C276" t="n">
-        <v>4251.294530854604</v>
+        <v>4006.880419878994</v>
       </c>
       <c r="D276" t="n">
-        <v>4610.630229672652</v>
+        <v>4341.837549007002</v>
       </c>
       <c r="E276" t="n">
-        <v>4475.79248046875</v>
+        <v>4265.73486328125</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>46175</v>
+        <v>46191</v>
       </c>
       <c r="B277" t="n">
-        <v>4408.756076293279</v>
+        <v>4160.707244261179</v>
       </c>
       <c r="C277" t="n">
-        <v>4240.947098832864</v>
+        <v>3977.55794640093</v>
       </c>
       <c r="D277" t="n">
-        <v>4581.876183953024</v>
+        <v>4331.392677467764</v>
       </c>
       <c r="E277" t="n">
-        <v>4463.0302734375</v>
+        <v>4180.39892578125</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>46176</v>
+        <v>46192</v>
       </c>
       <c r="B278" t="n">
-        <v>4394.618747368167</v>
+        <v>4150.268919852988</v>
       </c>
       <c r="C278" t="n">
-        <v>4231.822895395977</v>
+        <v>3977.762831221805</v>
       </c>
       <c r="D278" t="n">
-        <v>4575.634950301437</v>
+        <v>4317.976247477695</v>
       </c>
       <c r="E278" t="n">
-        <v>4448.11572265625</v>
+        <v>4151.90771484375</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>46177</v>
+        <v>46193</v>
       </c>
       <c r="B279" t="n">
-        <v>4357.851081363066</v>
+        <v>4148.056382429872</v>
       </c>
       <c r="C279" t="n">
-        <v>4168.021554236262</v>
+        <v>3990.445379226034</v>
       </c>
       <c r="D279" t="n">
-        <v>4524.055616380295</v>
+        <v>4327.727086310918</v>
       </c>
       <c r="E279" t="n">
-        <v>4453.0693359375</v>
+        <v>4149.44677734375</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>46178</v>
+        <v>46194</v>
       </c>
       <c r="B280" t="n">
-        <v>4327.916024736372</v>
+        <v>4141.380137241195</v>
       </c>
       <c r="C280" t="n">
-        <v>4147.54018408404</v>
+        <v>3982.640255208643</v>
       </c>
       <c r="D280" t="n">
-        <v>4506.870246788513</v>
+        <v>4324.941500830478</v>
       </c>
       <c r="E280" t="n">
-        <v>4320.01220703125</v>
+        <v>4134.23193359375</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>46179</v>
+        <v>46195</v>
       </c>
       <c r="B281" t="n">
-        <v>4309.350519991821</v>
+        <v>4151.741523773451</v>
       </c>
       <c r="C281" t="n">
-        <v>4127.785616798601</v>
+        <v>3976.834142051447</v>
       </c>
       <c r="D281" t="n">
-        <v>4481.160586636227</v>
+        <v>4318.330177027078</v>
       </c>
       <c r="E281" t="n">
-        <v>4296.80859375</v>
+        <v>4179.84033203125</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>46180</v>
+        <v>46196</v>
       </c>
       <c r="B282" t="n">
-        <v>4281.74770458098</v>
+        <v>4142.290689569278</v>
       </c>
       <c r="C282" t="n">
-        <v>4108.752423524287</v>
+        <v>3986.280427751941</v>
       </c>
       <c r="D282" t="n">
-        <v>4460.005343555153</v>
+        <v>4318.268540766511</v>
       </c>
       <c r="E282" t="n">
-        <v>4334.697265625</v>
+        <v>4091.5751953125</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>46181</v>
+        <v>46197</v>
       </c>
       <c r="B283" t="n">
-        <v>4271.997951594154</v>
+        <v>4153.368341075643</v>
       </c>
       <c r="C283" t="n">
-        <v>4101.803444693413</v>
+        <v>3976.406794063015</v>
       </c>
       <c r="D283" t="n">
-        <v>4449.896986474983</v>
+        <v>4323.528266928207</v>
       </c>
       <c r="E283" t="n">
-        <v>4308.56982421875</v>
+        <v>4007.2138671875</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>46182</v>
+        <v>46198</v>
       </c>
       <c r="B284" t="n">
-        <v>4254.088863525278</v>
+        <v>4138.480684984735</v>
       </c>
       <c r="C284" t="n">
-        <v>4071.978571164278</v>
+        <v>3968.796628648023</v>
       </c>
       <c r="D284" t="n">
-        <v>4422.214696437177</v>
+        <v>4293.567530383509</v>
       </c>
       <c r="E284" t="n">
-        <v>4215.26708984375</v>
+        <v>4008.37060546875</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>46183</v>
+        <v>46199</v>
       </c>
       <c r="B285" t="n">
-        <v>4247.485183525473</v>
+        <v>4129.182233420003</v>
       </c>
       <c r="C285" t="n">
-        <v>4078.723784977748</v>
+        <v>3974.590173544963</v>
       </c>
       <c r="D285" t="n">
-        <v>4408.776313227903</v>
+        <v>4295.384052127225</v>
       </c>
       <c r="E285" t="n">
-        <v>4049.58642578125</v>
+        <v>4076.42822265625</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>46184</v>
+        <v>46200</v>
       </c>
       <c r="B286" t="n">
-        <v>4219.714919176315</v>
+        <v>4126.969762036529</v>
       </c>
       <c r="C286" t="n">
-        <v>4053.616978128443</v>
+        <v>3952.622605210051</v>
       </c>
       <c r="D286" t="n">
-        <v>4392.788469756637</v>
+        <v>4299.614220628535</v>
       </c>
       <c r="E286" t="n">
-        <v>4211.1201171875</v>
+        <v>4069.586181640625</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>46185</v>
+        <v>46201</v>
       </c>
       <c r="B287" t="n">
-        <v>4199.964296293896</v>
+        <v>4119.268491337004</v>
       </c>
       <c r="C287" t="n">
-        <v>4023.4566126663</v>
+        <v>3937.101774868373</v>
       </c>
       <c r="D287" t="n">
-        <v>4367.742242332242</v>
+        <v>4286.614036700857</v>
       </c>
       <c r="E287" t="n">
-        <v>4209.83251953125</v>
+        <v>4053.93408203125</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>46186</v>
+        <v>46202</v>
       </c>
       <c r="B288" t="n">
-        <v>4192.47077798998</v>
+        <v>4127.721664120709</v>
       </c>
       <c r="C288" t="n">
-        <v>4022.148993574549</v>
+        <v>3948.162620072355</v>
       </c>
       <c r="D288" t="n">
-        <v>4362.161575099114</v>
+        <v>4289.431720555938</v>
       </c>
       <c r="E288" t="n">
-        <v>4220.650390625</v>
+        <v>4007.720947265625</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>46187</v>
+        <v>46203</v>
       </c>
       <c r="B289" t="n">
-        <v>4176.514350461393</v>
+        <v>4115.643249831795</v>
       </c>
       <c r="C289" t="n">
-        <v>3999.368957439076</v>
+        <v>3941.880077099138</v>
       </c>
       <c r="D289" t="n">
-        <v>4347.564530800648</v>
+        <v>4280.156538594924</v>
       </c>
       <c r="E289" t="n">
-        <v>4286.2568359375</v>
+        <v>3999.095458984375</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>46188</v>
+        <v>46204</v>
       </c>
       <c r="B290" t="n">
-        <v>4178.667835704487</v>
+        <v>4123.553966903162</v>
       </c>
       <c r="C290" t="n">
-        <v>4005.868777107668</v>
+        <v>3957.904640673172</v>
       </c>
       <c r="D290" t="n">
-        <v>4342.739685763856</v>
+        <v>4292.373622716846</v>
       </c>
       <c r="E290" t="n">
-        <v>4306.87744140625</v>
+        <v>4029.442138671875</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>46189</v>
+        <v>46205</v>
       </c>
       <c r="B291" t="n">
-        <v>4172.606069162181</v>
+        <v>4105.150226593501</v>
       </c>
       <c r="C291" t="n">
-        <v>4005.163358818377</v>
+        <v>3928.677207044278</v>
       </c>
       <c r="D291" t="n">
-        <v>4346.349491237076</v>
+        <v>4279.365998511539</v>
       </c>
       <c r="E291" t="n">
-        <v>4319.31689453125</v>
+        <v>4120.0087890625</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>46190</v>
+        <v>46206</v>
       </c>
       <c r="B292" t="n">
-        <v>4177.49464149936</v>
+        <v>4092.180866660992</v>
       </c>
       <c r="C292" t="n">
-        <v>3997.780166634795</v>
+        <v>3927.539313430686</v>
       </c>
       <c r="D292" t="n">
-        <v>4338.973826128813</v>
+        <v>4254.036662162904</v>
       </c>
       <c r="E292" t="n">
-        <v>4265.73486328125</v>
+        <v>4166.45947265625</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>46191</v>
+        <v>46207</v>
       </c>
       <c r="B293" t="n">
-        <v>4160.584249444841</v>
+        <v>4086.335153909864</v>
       </c>
       <c r="C293" t="n">
-        <v>3985.784744413995</v>
+        <v>3907.744801099596</v>
       </c>
       <c r="D293" t="n">
-        <v>4334.408743658748</v>
+        <v>4243.158803618645</v>
       </c>
       <c r="E293" t="n">
-        <v>4180.39892578125</v>
+        <v>4164.49365234375</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>46192</v>
+        <v>46208</v>
       </c>
       <c r="B294" t="n">
-        <v>4150.81304682914</v>
+        <v>4075.223307267979</v>
       </c>
       <c r="C294" t="n">
-        <v>3975.700961964699</v>
+        <v>3910.590597917546</v>
       </c>
       <c r="D294" t="n">
-        <v>4332.698162962715</v>
+        <v>4238.820866363472</v>
       </c>
       <c r="E294" t="n">
-        <v>4151.90771484375</v>
+        <v>4175.6865234375</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
-        <v>46193</v>
+        <v>46209</v>
       </c>
       <c r="B295" t="n">
-        <v>4152.206030575464</v>
+        <v>4080.660880391948</v>
       </c>
       <c r="C295" t="n">
-        <v>3972.514779745021</v>
+        <v>3907.972552290135</v>
       </c>
       <c r="D295" t="n">
-        <v>4314.147348082876</v>
+        <v>4258.787504848201</v>
       </c>
       <c r="E295" t="n">
-        <v>4149.44677734375</v>
+        <v>4152.48388671875</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
-        <v>46194</v>
+        <v>46210</v>
       </c>
       <c r="B296" t="n">
-        <v>4143.871500735831</v>
+        <v>4066.11688167189</v>
       </c>
       <c r="C296" t="n">
-        <v>3978.741447808189</v>
+        <v>3894.856352572693</v>
       </c>
       <c r="D296" t="n">
-        <v>4328.108271788599</v>
+        <v>4226.104969942156</v>
       </c>
       <c r="E296" t="n">
-        <v>4134.23193359375</v>
+        <v>4092.410888671875</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
-        <v>46195</v>
+        <v>46211</v>
       </c>
       <c r="B297" t="n">
-        <v>4152.255227923817</v>
+        <v>4072.245944754969</v>
       </c>
       <c r="C297" t="n">
-        <v>3992.520114862361</v>
+        <v>3901.561532349312</v>
       </c>
       <c r="D297" t="n">
-        <v>4313.908548691116</v>
+        <v>4240.834736450184</v>
       </c>
       <c r="E297" t="n">
-        <v>4179.84033203125</v>
+        <v>4069.62353515625</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
-        <v>46196</v>
+        <v>46212</v>
       </c>
       <c r="B298" t="n">
-        <v>4150.952081991213</v>
+        <v>4052.854248545395</v>
       </c>
       <c r="C298" t="n">
-        <v>3977.618009951143</v>
+        <v>3883.732506733079</v>
       </c>
       <c r="D298" t="n">
-        <v>4315.864995496138</v>
+        <v>4221.685894686285</v>
       </c>
       <c r="E298" t="n">
-        <v>4091.5751953125</v>
+        <v>4114.41064453125</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
-        <v>46197</v>
+        <v>46213</v>
       </c>
       <c r="B299" t="n">
-        <v>4159.09578007858</v>
+        <v>4039.774120363844</v>
       </c>
       <c r="C299" t="n">
-        <v>3992.197366749555</v>
+        <v>3874.896861246832</v>
       </c>
       <c r="D299" t="n">
-        <v>4334.645483379985</v>
+        <v>4215.60069229216</v>
       </c>
       <c r="E299" t="n">
-        <v>4007.2138671875</v>
+        <v>4110.74462890625</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
-        <v>46198</v>
+        <v>46214</v>
       </c>
       <c r="B300" t="n">
-        <v>4143.952801846842</v>
+        <v>4034.75083547477</v>
       </c>
       <c r="C300" t="n">
-        <v>3959.712546973644</v>
+        <v>3854.805001762888</v>
       </c>
       <c r="D300" t="n">
-        <v>4321.547257016226</v>
+        <v>4216.756722377227</v>
       </c>
       <c r="E300" t="n">
-        <v>4008.37060546875</v>
+        <v>4100.0029296875</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
-        <v>46199</v>
+        <v>46215</v>
       </c>
       <c r="B301" t="n">
-        <v>4134.522907610781</v>
+        <v>4025.422867156149</v>
       </c>
       <c r="C301" t="n">
-        <v>3959.434389615694</v>
+        <v>3860.056763457294</v>
       </c>
       <c r="D301" t="n">
-        <v>4297.631779920301</v>
+        <v>4196.687474458978</v>
       </c>
       <c r="E301" t="n">
-        <v>4076.42822265625</v>
+        <v>4074.627685546875</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
-        <v>46200</v>
+        <v>46216</v>
       </c>
       <c r="B302" t="n">
-        <v>4134.935382400694</v>
+        <v>4033.606898190587</v>
       </c>
       <c r="C302" t="n">
-        <v>3967.297920687902</v>
+        <v>3871.304877999024</v>
       </c>
       <c r="D302" t="n">
-        <v>4309.751694786113</v>
+        <v>4209.342965720401</v>
       </c>
       <c r="E302" t="n">
-        <v>4069.586181640625</v>
+        <v>3992.321533203125</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
-        <v>46201</v>
+        <v>46217</v>
       </c>
       <c r="B303" t="n">
-        <v>4124.441166866377</v>
+        <v>4022.747413420845</v>
       </c>
       <c r="C303" t="n">
-        <v>3962.350305670586</v>
+        <v>3870.973612628276</v>
       </c>
       <c r="D303" t="n">
-        <v>4300.10824894404</v>
+        <v>4191.710330891164</v>
       </c>
       <c r="E303" t="n">
-        <v>4053.93408203125</v>
+        <v>4046.171875</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
-        <v>46202</v>
+        <v>46218</v>
       </c>
       <c r="B304" t="n">
-        <v>4129.661666176207</v>
+        <v>4033.451102608178</v>
       </c>
       <c r="C304" t="n">
-        <v>3957.317259410656</v>
+        <v>3856.080434567285</v>
       </c>
       <c r="D304" t="n">
-        <v>4304.32502961241</v>
+        <v>4198.588732823016</v>
       </c>
       <c r="E304" t="n">
-        <v>4007.720947265625</v>
+        <v>4048.7763671875</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
-        <v>46203</v>
+        <v>46219</v>
       </c>
       <c r="B305" t="n">
-        <v>4124.394175134233</v>
+        <v>4019.455664556267</v>
       </c>
       <c r="C305" t="n">
-        <v>3959.83915621679</v>
+        <v>3852.999331279684</v>
       </c>
       <c r="D305" t="n">
-        <v>4282.75995626182</v>
+        <v>4200.505707557052</v>
       </c>
       <c r="E305" t="n">
-        <v>3999.095458984375</v>
+        <v>3977.87548828125</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
-        <v>46204</v>
+        <v>46220</v>
       </c>
       <c r="B306" t="n">
-        <v>4127.994783891106</v>
+        <v>4012.507819332034</v>
       </c>
       <c r="C306" t="n">
-        <v>3944.677513890104</v>
+        <v>3830.071868317162</v>
       </c>
       <c r="D306" t="n">
-        <v>4294.045156583159</v>
+        <v>4168.247876456215</v>
       </c>
       <c r="E306" t="n">
-        <v>4029.442138671875</v>
+        <v>4003.6015625</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
-        <v>46205</v>
+        <v>46221</v>
       </c>
       <c r="B307" t="n">
-        <v>4107.965033352311</v>
+        <v>4014.253900416981</v>
       </c>
       <c r="C307" t="n">
-        <v>3939.057940826471</v>
+        <v>3839.343632044862</v>
       </c>
       <c r="D307" t="n">
-        <v>4293.519164629064</v>
+        <v>4191.103081327149</v>
       </c>
       <c r="E307" t="n">
-        <v>4120.0087890625</v>
+        <v>4008.41796875</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
-        <v>46206</v>
+        <v>46222</v>
       </c>
       <c r="B308" t="n">
-        <v>4093.544985364908</v>
+        <v>4012.224130227083</v>
       </c>
       <c r="C308" t="n">
-        <v>3920.927909144182</v>
+        <v>3857.409144521838</v>
       </c>
       <c r="D308" t="n">
-        <v>4267.691516548732</v>
+        <v>4170.540172692288</v>
       </c>
       <c r="E308" t="n">
-        <v>4166.45947265625</v>
+        <v>3989.054931640625</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
-        <v>46207</v>
+        <v>46223</v>
       </c>
       <c r="B309" t="n">
-        <v>4089.102061020049</v>
+        <v>4028.121735148202</v>
       </c>
       <c r="C309" t="n">
-        <v>3922.521959390411</v>
+        <v>3852.338182195378</v>
       </c>
       <c r="D309" t="n">
-        <v>4267.032463020249</v>
+        <v>4183.638162225594</v>
       </c>
       <c r="E309" t="n">
-        <v>4164.49365234375</v>
+        <v>4002.884765625</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
-        <v>46208</v>
+        <v>46224</v>
       </c>
       <c r="B310" t="n">
-        <v>4074.116032207412</v>
+        <v>4025.276566409641</v>
       </c>
       <c r="C310" t="n">
-        <v>3896.603940218929</v>
+        <v>3854.564774858171</v>
       </c>
       <c r="D310" t="n">
-        <v>4250.554842917782</v>
+        <v>4199.301342016064</v>
       </c>
       <c r="E310" t="n">
-        <v>4175.6865234375</v>
+        <v>4072.03076171875</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
-        <v>46209</v>
+        <v>46225</v>
       </c>
       <c r="B311" t="n">
-        <v>4075.421168963618</v>
+        <v>4044.183309433638</v>
       </c>
       <c r="C311" t="n">
-        <v>3903.7134733803</v>
+        <v>3873.830805279074</v>
       </c>
       <c r="D311" t="n">
-        <v>4249.962261336228</v>
+        <v>4212.546833715549</v>
       </c>
       <c r="E311" t="n">
-        <v>4152.48388671875</v>
+        <v>4123.4501953125</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="n">
-        <v>46210</v>
+        <v>46226</v>
       </c>
       <c r="B312" t="n">
-        <v>4067.00567314808</v>
+        <v>4038.473737747174</v>
       </c>
       <c r="C312" t="n">
-        <v>3905.410737556036</v>
+        <v>3863.320447424799</v>
       </c>
       <c r="D312" t="n">
-        <v>4230.558962149075</v>
+        <v>4211.605021501937</v>
       </c>
       <c r="E312" t="n">
-        <v>4092.410888671875</v>
+        <v>4043.264404296875</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="n">
-        <v>46211</v>
+        <v>46227</v>
       </c>
       <c r="B313" t="n">
-        <v>4068.389430480892</v>
+        <v>4039.797699694024</v>
       </c>
       <c r="C313" t="n">
-        <v>3876.399794776607</v>
+        <v>3873.283671946293</v>
       </c>
       <c r="D313" t="n">
-        <v>4242.862492873875</v>
+        <v>4217.863922872049</v>
       </c>
       <c r="E313" t="n">
-        <v>4069.62353515625</v>
+        <v>4050.573486328125</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="n">
-        <v>46212</v>
+        <v>46228</v>
       </c>
       <c r="B314" t="n">
-        <v>4047.206488325504</v>
+        <v>4049.716111421533</v>
       </c>
       <c r="C314" t="n">
-        <v>3879.019566580022</v>
+        <v>3882.960467700426</v>
       </c>
       <c r="D314" t="n">
-        <v>4216.758023891622</v>
+        <v>4221.94644543771</v>
       </c>
       <c r="E314" t="n">
-        <v>4114.41064453125</v>
+        <v>4052.02490234375</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="n">
-        <v>46213</v>
+        <v>46229</v>
       </c>
       <c r="B315" t="n">
-        <v>4032.795029442748</v>
+        <v>4055.686984683188</v>
       </c>
       <c r="C315" t="n">
-        <v>3853.240754774171</v>
+        <v>3868.208163927672</v>
       </c>
       <c r="D315" t="n">
-        <v>4210.345456140409</v>
+        <v>4219.647272869707</v>
       </c>
       <c r="E315" t="n">
-        <v>4110.74462890625</v>
+        <v>4083.52392578125</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="n">
-        <v>46214</v>
+        <v>46230</v>
       </c>
       <c r="B316" t="n">
-        <v>4029.584264386235</v>
+        <v>4079.355596562928</v>
       </c>
       <c r="C316" t="n">
-        <v>3848.018522713468</v>
+        <v>3907.180482506671</v>
       </c>
       <c r="D316" t="n">
-        <v>4194.411842433686</v>
+        <v>4242.302534159202</v>
       </c>
       <c r="E316" t="n">
-        <v>4100.0029296875</v>
+        <v>4062.4287109375</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
-        <v>46215</v>
+        <v>46231</v>
       </c>
       <c r="B317" t="n">
-        <v>4017.078659664346</v>
+        <v>4084.008445748451</v>
       </c>
       <c r="C317" t="n">
-        <v>3838.307946638767</v>
+        <v>3910.071919375889</v>
       </c>
       <c r="D317" t="n">
-        <v>4183.145286093169</v>
+        <v>4264.666108932985</v>
       </c>
       <c r="E317" t="n">
-        <v>4074.627685546875</v>
+        <v>4017.01123046875</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
-        <v>46216</v>
+        <v>46232</v>
       </c>
       <c r="B318" t="n">
-        <v>4022.100498502344</v>
+        <v>4110.111084178782</v>
       </c>
       <c r="C318" t="n">
-        <v>3837.71744007579</v>
+        <v>3933.801332733546</v>
       </c>
       <c r="D318" t="n">
-        <v>4184.397985398808</v>
+        <v>4286.573459814397</v>
       </c>
       <c r="E318" t="n">
-        <v>3992.321533203125</v>
+        <v>4078.895751953125</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
-        <v>46217</v>
+        <v>46233</v>
       </c>
       <c r="B319" t="n">
-        <v>4018.590862157307</v>
+        <v>4111.279313797994</v>
       </c>
       <c r="C319" t="n">
-        <v>3860.865011412493</v>
+        <v>3931.457109882744</v>
       </c>
       <c r="D319" t="n">
-        <v>4180.934605754866</v>
+        <v>4287.266794205574</v>
       </c>
       <c r="E319" t="n">
-        <v>4046.171875</v>
+        <v>4098.5625</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
-        <v>46218</v>
+        <v>46234</v>
       </c>
       <c r="B320" t="n">
-        <v>4025.989986323443</v>
+        <v>4119.158496378395</v>
       </c>
       <c r="C320" t="n">
-        <v>3854.511335584244</v>
+        <v>3936.508003327736</v>
       </c>
       <c r="D320" t="n">
-        <v>4184.238731419649</v>
+        <v>4296.987687313127</v>
       </c>
       <c r="E320" t="n">
-        <v>4048.7763671875</v>
+        <v>4043.583740234375</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
-        <v>46219</v>
+        <v>46235</v>
       </c>
       <c r="B321" t="n">
-        <v>4011.823290620426</v>
+        <v>4135.314333421739</v>
       </c>
       <c r="C321" t="n">
-        <v>3833.58258264236</v>
+        <v>3971.590561038641</v>
       </c>
       <c r="D321" t="n">
-        <v>4196.474918819538</v>
+        <v>4312.297830800379</v>
       </c>
       <c r="E321" t="n">
-        <v>3977.87548828125</v>
+        <v>4044.826904296875</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
-        <v>46220</v>
+        <v>46236</v>
       </c>
       <c r="B322" t="n">
-        <v>4005.2957140838</v>
+        <v>4147.216248927</v>
       </c>
       <c r="C322" t="n">
-        <v>3826.080852925455</v>
+        <v>3976.293638781052</v>
       </c>
       <c r="D322" t="n">
-        <v>4163.102526406357</v>
+        <v>4321.268041418725</v>
       </c>
       <c r="E322" t="n">
-        <v>4003.6015625</v>
+        <v>4066.402587890625</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
-        <v>46221</v>
+        <v>46237</v>
       </c>
       <c r="B323" t="n">
-        <v>4010.683618902946</v>
+        <v>4176.524603277014</v>
       </c>
       <c r="C323" t="n">
-        <v>3816.294408108089</v>
+        <v>3999.523589016395</v>
       </c>
       <c r="D323" t="n">
-        <v>4174.064529326285</v>
+        <v>4352.144275474468</v>
       </c>
       <c r="E323" t="n">
-        <v>4008.41796875</v>
+        <v>4047.6044921875</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
-        <v>46222</v>
+        <v>46238</v>
       </c>
       <c r="B324" t="n">
-        <v>4007.324501447986</v>
+        <v>4186.541516517658</v>
       </c>
       <c r="C324" t="n">
-        <v>3820.407653852886</v>
+        <v>4004.836678386458</v>
       </c>
       <c r="D324" t="n">
-        <v>4168.696107481565</v>
+        <v>4359.36464490448</v>
       </c>
       <c r="E324" t="n">
-        <v>3989.054931640625</v>
+        <v>4064.322265625</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
-        <v>46223</v>
+        <v>46239</v>
       </c>
       <c r="B325" t="n">
-        <v>4021.865317630125</v>
+        <v>4217.745531156415</v>
       </c>
       <c r="C325" t="n">
-        <v>3846.677356012395</v>
+        <v>4059.598468226731</v>
       </c>
       <c r="D325" t="n">
-        <v>4187.515438868266</v>
+        <v>4378.632296208859</v>
       </c>
       <c r="E325" t="n">
-        <v>4002.884765625</v>
+        <v>4265.63232421875</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
-        <v>46224</v>
+        <v>46240</v>
       </c>
       <c r="B326" t="n">
-        <v>4028.069315288947</v>
+        <v>4223.759748044929</v>
       </c>
       <c r="C326" t="n">
-        <v>3858.501889994364</v>
+        <v>4055.847727267645</v>
       </c>
       <c r="D326" t="n">
-        <v>4214.949695914071</v>
+        <v>4380.329449124471</v>
       </c>
       <c r="E326" t="n">
-        <v>4072.03076171875</v>
+        <v>4244.072265625</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
-        <v>46225</v>
+        <v>46241</v>
       </c>
       <c r="B327" t="n">
-        <v>4045.202133757805</v>
+        <v>4236.228324441834</v>
       </c>
       <c r="C327" t="n">
-        <v>3868.271654630117</v>
+        <v>4068.111987825312</v>
       </c>
       <c r="D327" t="n">
-        <v>4212.15873538024</v>
+        <v>4396.495495703453</v>
       </c>
       <c r="E327" t="n">
-        <v>4123.4501953125</v>
+        <v>4340.7705078125</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
-        <v>46226</v>
+        <v>46242</v>
       </c>
       <c r="B328" t="n">
-        <v>4040.62328131972</v>
+        <v>4256.704824525812</v>
       </c>
       <c r="C328" t="n">
-        <v>3860.736800317345</v>
+        <v>4091.043180506888</v>
       </c>
       <c r="D328" t="n">
-        <v>4214.433196317842</v>
+        <v>4432.956181151764</v>
       </c>
       <c r="E328" t="n">
-        <v>4043.264404296875</v>
+        <v>4343.48876953125</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
-        <v>46227</v>
+        <v>46243</v>
       </c>
       <c r="B329" t="n">
-        <v>4043.385449236129</v>
+        <v>4272.633675614445</v>
       </c>
       <c r="C329" t="n">
-        <v>3879.941335171182</v>
+        <v>4091.704471302878</v>
       </c>
       <c r="D329" t="n">
-        <v>4215.090446481264</v>
+        <v>4434.285149560321</v>
       </c>
       <c r="E329" t="n">
-        <v>4050.573486328125</v>
+        <v>4331.46240234375</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
-        <v>46228</v>
+        <v>46244</v>
       </c>
       <c r="B330" t="n">
-        <v>4057.630768855496</v>
+        <v>4305.636061482157</v>
       </c>
       <c r="C330" t="n">
-        <v>3882.720390202088</v>
+        <v>4131.347093041373</v>
       </c>
       <c r="D330" t="n">
-        <v>4218.120144710575</v>
+        <v>4467.080956794259</v>
       </c>
       <c r="E330" t="n">
-        <v>4052.02490234375</v>
+        <v>4390.552734375</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
-        <v>46229</v>
+        <v>46245</v>
       </c>
       <c r="B331" t="n">
-        <v>4062.584118408834</v>
+        <v>4318.96011290735</v>
       </c>
       <c r="C331" t="n">
-        <v>3892.15638669934</v>
+        <v>4157.671962383776</v>
       </c>
       <c r="D331" t="n">
-        <v>4246.051730894142</v>
+        <v>4482.281216923341</v>
       </c>
       <c r="E331" t="n">
-        <v>4083.52392578125</v>
+        <v>4364.71484375</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
-        <v>46230</v>
+        <v>46246</v>
       </c>
       <c r="B332" t="n">
-        <v>4084.804181417036</v>
+        <v>4353.015682867643</v>
       </c>
       <c r="C332" t="n">
-        <v>3909.565462303651</v>
+        <v>4174.345990146095</v>
       </c>
       <c r="D332" t="n">
-        <v>4270.563487376776</v>
+        <v>4519.989606947833</v>
       </c>
       <c r="E332" t="n">
-        <v>4062.4287109375</v>
+        <v>4401.5400390625</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
-        <v>46231</v>
+        <v>46247</v>
       </c>
       <c r="B333" t="n">
-        <v>4097.992074692829</v>
+        <v>4361.343370215861</v>
       </c>
       <c r="C333" t="n">
-        <v>3925.559169453541</v>
+        <v>4184.248694897563</v>
       </c>
       <c r="D333" t="n">
-        <v>4276.490350336971</v>
+        <v>4519.122800619494</v>
       </c>
       <c r="E333" t="n">
-        <v>4017.01123046875</v>
+        <v>4353.865234375</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
-        <v>46232</v>
+        <v>46248</v>
       </c>
       <c r="B334" t="n">
-        <v>4121.378263877297</v>
+        <v>4375.492682603455</v>
       </c>
       <c r="C334" t="n">
-        <v>3959.321614988487</v>
+        <v>4194.45077060628</v>
       </c>
       <c r="D334" t="n">
-        <v>4303.096992877317</v>
+        <v>4553.323980331217</v>
       </c>
       <c r="E334" t="n">
-        <v>4078.895751953125</v>
+        <v>4374.42626953125</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
-        <v>46233</v>
+        <v>46249</v>
       </c>
       <c r="B335" t="n">
-        <v>4122.313868536721</v>
+        <v>4396.912801381557</v>
       </c>
       <c r="C335" t="n">
-        <v>3958.207196347434</v>
+        <v>4231.872740860173</v>
       </c>
       <c r="D335" t="n">
-        <v>4308.64807443505</v>
+        <v>4565.852027576745</v>
       </c>
       <c r="E335" t="n">
-        <v>4098.5625</v>
+        <v>4374.23486328125</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
-        <v>46234</v>
+        <v>46250</v>
       </c>
       <c r="B336" t="n">
-        <v>4129.868840275108</v>
+        <v>4412.937145354274</v>
       </c>
       <c r="C336" t="n">
-        <v>3956.556619642983</v>
+        <v>4245.72181831847</v>
       </c>
       <c r="D336" t="n">
-        <v>4300.103724493886</v>
+        <v>4585.787303942941</v>
       </c>
       <c r="E336" t="n">
-        <v>4043.583740234375</v>
+        <v>4364.1181640625</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
-        <v>46235</v>
+        <v>46251</v>
       </c>
       <c r="B337" t="n">
-        <v>4148.2261774603</v>
+        <v>4445.072980906863</v>
       </c>
       <c r="C337" t="n">
-        <v>3976.045362972862</v>
+        <v>4264.144879841438</v>
       </c>
       <c r="D337" t="n">
-        <v>4319.194185785267</v>
+        <v>4612.088098037413</v>
       </c>
       <c r="E337" t="n">
-        <v>4044.826904296875</v>
+        <v>4413.7080078125</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
-        <v>46236</v>
+        <v>46252</v>
       </c>
       <c r="B338" t="n">
-        <v>4156.672370401401</v>
+        <v>4456.455829575914</v>
       </c>
       <c r="C338" t="n">
-        <v>3985.559565663506</v>
+        <v>4277.873879910354</v>
       </c>
       <c r="D338" t="n">
-        <v>4333.626373822466</v>
+        <v>4644.894680547914</v>
       </c>
       <c r="E338" t="n">
-        <v>4066.402587890625</v>
+        <v>4332.75439453125</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
-        <v>46237</v>
+        <v>46253</v>
       </c>
       <c r="B339" t="n">
-        <v>4181.844893131315</v>
+        <v>4487.388829407844</v>
       </c>
       <c r="C339" t="n">
-        <v>4016.384118058938</v>
+        <v>4324.93248599772</v>
       </c>
       <c r="D339" t="n">
-        <v>4363.078087695897</v>
+        <v>4671.052121459961</v>
       </c>
       <c r="E339" t="n">
-        <v>4047.6044921875</v>
+        <v>4496.87548828125</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
-        <v>46238</v>
+        <v>46254</v>
       </c>
       <c r="B340" t="n">
-        <v>4197.536697013312</v>
+        <v>4491.316564821441</v>
       </c>
       <c r="C340" t="n">
-        <v>4022.575184456827</v>
+        <v>4331.795842773588</v>
       </c>
       <c r="D340" t="n">
-        <v>4371.334893849402</v>
+        <v>4658.764643363756</v>
       </c>
       <c r="E340" t="n">
-        <v>4064.322265625</v>
+        <v>4513.38232421875</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
-        <v>46239</v>
+        <v>46255</v>
       </c>
       <c r="B341" t="n">
-        <v>4223.078579636615</v>
+        <v>4499.708093218055</v>
       </c>
       <c r="C341" t="n">
-        <v>4037.730280360464</v>
+        <v>4334.893998925705</v>
       </c>
       <c r="D341" t="n">
-        <v>4393.298750464879</v>
+        <v>4663.02442972373</v>
       </c>
       <c r="E341" t="n">
-        <v>4265.63232421875</v>
+        <v>4598.94677734375</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
-        <v>46240</v>
+        <v>46256</v>
       </c>
       <c r="B342" t="n">
-        <v>4225.925699555378</v>
+        <v>4513.95246030531</v>
       </c>
       <c r="C342" t="n">
-        <v>4067.646301309712</v>
+        <v>4347.335369072631</v>
       </c>
       <c r="D342" t="n">
-        <v>4407.89307828032</v>
+        <v>4684.999887159718</v>
       </c>
       <c r="E342" t="n">
-        <v>4244.072265625</v>
+        <v>4586.66064453125</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
-        <v>46241</v>
+        <v>46257</v>
       </c>
       <c r="B343" t="n">
-        <v>4235.250896177383</v>
+        <v>4521.347727521553</v>
       </c>
       <c r="C343" t="n">
-        <v>4070.330906587459</v>
+        <v>4345.429112930397</v>
       </c>
       <c r="D343" t="n">
-        <v>4396.478903873989</v>
+        <v>4704.288597126954</v>
       </c>
       <c r="E343" t="n">
-        <v>4340.7705078125</v>
+        <v>4611.45068359375</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
-        <v>46242</v>
+        <v>46258</v>
       </c>
       <c r="B344" t="n">
-        <v>4255.334155671463</v>
+        <v>4543.394588603361</v>
       </c>
       <c r="C344" t="n">
-        <v>4085.397009867746</v>
+        <v>4375.756914926986</v>
       </c>
       <c r="D344" t="n">
-        <v>4427.696828134233</v>
+        <v>4714.443459353639</v>
       </c>
       <c r="E344" t="n">
-        <v>4343.48876953125</v>
+        <v>4671.80908203125</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
-        <v>46243</v>
+        <v>46259</v>
       </c>
       <c r="B345" t="n">
-        <v>4265.548589506874</v>
+        <v>4543.254164605757</v>
       </c>
       <c r="C345" t="n">
-        <v>4090.264353437833</v>
+        <v>4376.533830441891</v>
       </c>
       <c r="D345" t="n">
-        <v>4446.092984263383</v>
+        <v>4713.315901850211</v>
       </c>
       <c r="E345" t="n">
-        <v>4331.46240234375</v>
+        <v>4648.12109375</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
-        <v>46244</v>
+        <v>46260</v>
       </c>
       <c r="B346" t="n">
-        <v>4292.603904290714</v>
+        <v>4561.28998624868</v>
       </c>
       <c r="C346" t="n">
-        <v>4110.050680238594</v>
+        <v>4387.691033456206</v>
       </c>
       <c r="D346" t="n">
-        <v>4452.533219826485</v>
+        <v>4738.0541532259</v>
       </c>
       <c r="E346" t="n">
-        <v>4390.552734375</v>
+        <v>4616.73388671875</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
-        <v>46245</v>
+        <v>46261</v>
       </c>
       <c r="B347" t="n">
-        <v>4310.347464969344</v>
+        <v>4551.043550314837</v>
       </c>
       <c r="C347" t="n">
-        <v>4138.180402910759</v>
+        <v>4380.126311046817</v>
       </c>
       <c r="D347" t="n">
-        <v>4474.271458426625</v>
+        <v>4718.317359032593</v>
       </c>
       <c r="E347" t="n">
-        <v>4364.71484375</v>
+        <v>4588.3125</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
-        <v>46246</v>
+        <v>46262</v>
       </c>
       <c r="B348" t="n">
-        <v>4338.143951141709</v>
+        <v>4544.118074509114</v>
       </c>
       <c r="C348" t="n">
-        <v>4168.956114470973</v>
+        <v>4376.624685353178</v>
       </c>
       <c r="D348" t="n">
-        <v>4505.614525739928</v>
+        <v>4714.044031213346</v>
       </c>
       <c r="E348" t="n">
-        <v>4401.5400390625</v>
+        <v>4462.6953125</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
-        <v>46247</v>
+        <v>46263</v>
       </c>
       <c r="B349" t="n">
-        <v>4343.459978548907</v>
+        <v>4542.073667065142</v>
       </c>
       <c r="C349" t="n">
-        <v>4164.190990548566</v>
+        <v>4374.084736324652</v>
       </c>
       <c r="D349" t="n">
-        <v>4526.977876492833</v>
+        <v>4715.196632771416</v>
       </c>
       <c r="E349" t="n">
-        <v>4353.865234375</v>
+        <v>4464.5947265625</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
-        <v>46248</v>
+        <v>46264</v>
       </c>
       <c r="B350" t="n">
-        <v>4355.456418372271</v>
+        <v>4532.414890140863</v>
       </c>
       <c r="C350" t="n">
-        <v>4185.852574293297</v>
+        <v>4376.366608866166</v>
       </c>
       <c r="D350" t="n">
-        <v>4515.54044076185</v>
+        <v>4720.255918539502</v>
       </c>
       <c r="E350" t="n">
-        <v>4374.42626953125</v>
+        <v>4447.748046875</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
-        <v>46249</v>
+        <v>46265</v>
       </c>
       <c r="B351" t="n">
-        <v>4378.377797866468</v>
+        <v>4536.881783280534</v>
       </c>
       <c r="C351" t="n">
-        <v>4200.662060662495</v>
+        <v>4358.993526579914</v>
       </c>
       <c r="D351" t="n">
-        <v>4549.832067807279</v>
+        <v>4702.847485531868</v>
       </c>
       <c r="E351" t="n">
-        <v>4374.23486328125</v>
+        <v>4447.16064453125</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
-        <v>46250</v>
+        <v>46266</v>
       </c>
       <c r="B352" t="n">
-        <v>4391.53915943542</v>
+        <v>4518.903960313193</v>
       </c>
       <c r="C352" t="n">
-        <v>4220.208656911638</v>
+        <v>4361.16270650802</v>
       </c>
       <c r="D352" t="n">
-        <v>4556.022071254965</v>
+        <v>4704.432676867425</v>
       </c>
       <c r="E352" t="n">
-        <v>4364.1181640625</v>
+        <v>4339.46044921875</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="n">
-        <v>46251</v>
+        <v>46267</v>
       </c>
       <c r="B353" t="n">
-        <v>4421.57133470344</v>
+        <v>4519.137847613928</v>
       </c>
       <c r="C353" t="n">
-        <v>4243.860121996189</v>
+        <v>4351.86920442147</v>
       </c>
       <c r="D353" t="n">
-        <v>4579.499089905333</v>
+        <v>4691.447826082721</v>
       </c>
       <c r="E353" t="n">
-        <v>4413.7080078125</v>
+        <v>4393.13720703125</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
-        <v>46252</v>
+        <v>46268</v>
       </c>
       <c r="B354" t="n">
-        <v>4442.224681535527</v>
+        <v>4491.436543583772</v>
       </c>
       <c r="C354" t="n">
-        <v>4271.268683066875</v>
+        <v>4317.58265623579</v>
       </c>
       <c r="D354" t="n">
-        <v>4632.566303843591</v>
+        <v>4662.646283170956</v>
       </c>
       <c r="E354" t="n">
-        <v>4332.75439453125</v>
+        <v>4479.80419921875</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
-        <v>46253</v>
+        <v>46269</v>
       </c>
       <c r="B355" t="n">
-        <v>4472.752199298182</v>
+        <v>4467.727048979804</v>
       </c>
       <c r="C355" t="n">
-        <v>4300.193970083071</v>
+        <v>4302.315296603789</v>
       </c>
       <c r="D355" t="n">
-        <v>4647.219477090847</v>
+        <v>4633.113918587128</v>
       </c>
       <c r="E355" t="n">
-        <v>4496.87548828125</v>
+        <v>4432.97021484375</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
-        <v>46254</v>
+        <v>46270</v>
       </c>
       <c r="B356" t="n">
-        <v>4480.498282262541</v>
+        <v>4449.898238671136</v>
       </c>
       <c r="C356" t="n">
-        <v>4313.967859204938</v>
+        <v>4280.84425910451</v>
       </c>
       <c r="D356" t="n">
-        <v>4645.221205230849</v>
+        <v>4615.278046751862</v>
       </c>
       <c r="E356" t="n">
-        <v>4513.38232421875</v>
+        <v>4432.44287109375</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
-        <v>46255</v>
+        <v>46271</v>
       </c>
       <c r="B357" t="n">
-        <v>4494.495707460501</v>
+        <v>4425.780733250973</v>
       </c>
       <c r="C357" t="n">
-        <v>4322.576075971091</v>
+        <v>4249.737727722972</v>
       </c>
       <c r="D357" t="n">
-        <v>4671.614793411384</v>
+        <v>4589.803955008905</v>
       </c>
       <c r="E357" t="n">
-        <v>4598.94677734375</v>
+        <v>4420.9033203125</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
-        <v>46256</v>
+        <v>46272</v>
       </c>
       <c r="B358" t="n">
-        <v>4518.860084385644</v>
+        <v>4417.429936458208</v>
       </c>
       <c r="C358" t="n">
-        <v>4354.731764119143</v>
+        <v>4238.041258329063</v>
       </c>
       <c r="D358" t="n">
-        <v>4692.188464749017</v>
+        <v>4575.922958603126</v>
       </c>
       <c r="E358" t="n">
-        <v>4586.66064453125</v>
+        <v>4421.685546875</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
-        <v>46257</v>
+        <v>46273</v>
       </c>
       <c r="B359" t="n">
-        <v>4532.781972690904</v>
+        <v>4388.572066220111</v>
       </c>
       <c r="C359" t="n">
-        <v>4355.407969978867</v>
+        <v>4223.919727170995</v>
       </c>
       <c r="D359" t="n">
-        <v>4701.809194747925</v>
+        <v>4555.850290352464</v>
       </c>
       <c r="E359" t="n">
-        <v>4611.45068359375</v>
+        <v>4355.5458984375</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
-        <v>46258</v>
+        <v>46274</v>
       </c>
       <c r="B360" t="n">
-        <v>4562.777444171665</v>
+        <v>4380.133470379593</v>
       </c>
       <c r="C360" t="n">
-        <v>4391.895779645298</v>
+        <v>4215.462616163056</v>
       </c>
       <c r="D360" t="n">
-        <v>4724.274332596564</v>
+        <v>4553.077515093383</v>
       </c>
       <c r="E360" t="n">
-        <v>4671.80908203125</v>
+        <v>4393.83203125</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
-        <v>46259</v>
+        <v>46275</v>
       </c>
       <c r="B361" t="n">
-        <v>4582.496953236648</v>
+        <v>4346.202932355749</v>
       </c>
       <c r="C361" t="n">
-        <v>4400.620344822575</v>
+        <v>4179.784430974398</v>
       </c>
       <c r="D361" t="n">
-        <v>4757.300596065099</v>
+        <v>4520.092612178031</v>
       </c>
       <c r="E361" t="n">
-        <v>4648.12109375</v>
+        <v>4319.04443359375</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
-        <v>46260</v>
+        <v>46276</v>
       </c>
       <c r="B362" t="n">
-        <v>4611.113249901532</v>
+        <v>4318.901937393771</v>
       </c>
       <c r="C362" t="n">
-        <v>4445.259180224924</v>
+        <v>4152.949839731677</v>
       </c>
       <c r="D362" t="n">
-        <v>4783.656154593186</v>
+        <v>4494.845623532009</v>
       </c>
       <c r="E362" t="n">
-        <v>4616.73388671875</v>
+        <v>4354.66845703125</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
-        <v>46261</v>
+        <v>46277</v>
       </c>
       <c r="B363" t="n">
-        <v>4615.914422374554</v>
+        <v>4300.266480026568</v>
       </c>
       <c r="C363" t="n">
-        <v>4438.03679421105</v>
+        <v>4136.580191297728</v>
       </c>
       <c r="D363" t="n">
-        <v>4799.518321363118</v>
+        <v>4456.869323544933</v>
       </c>
       <c r="E363" t="n">
-        <v>4588.3125</v>
+        <v>4354.5498046875</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
-        <v>46262</v>
+        <v>46278</v>
       </c>
       <c r="B364" t="n">
-        <v>4625.904506836647</v>
+        <v>4278.221763860216</v>
       </c>
       <c r="C364" t="n">
-        <v>4460.217884509028</v>
+        <v>4114.115758367911</v>
       </c>
       <c r="D364" t="n">
-        <v>4795.842693049098</v>
+        <v>4438.83612017717</v>
       </c>
       <c r="E364" t="n">
-        <v>4462.6953125</v>
+        <v>4336.236328125</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
-        <v>46265</v>
+        <v>46279</v>
       </c>
       <c r="B365" t="n">
-        <v>4675.968293085014</v>
+        <v>4274.861228969214</v>
       </c>
       <c r="C365" t="n">
-        <v>4487.574106077641</v>
+        <v>4099.159015676522</v>
       </c>
       <c r="D365" t="n">
-        <v>4836.768699876524</v>
+        <v>4452.005377616013</v>
       </c>
       <c r="E365" t="n">
-        <v>4443.39990234375</v>
+        <v>4294.3330078125</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
-        <v>46266</v>
+        <v>46280</v>
       </c>
       <c r="B366" t="n">
-        <v>4687.773239351347</v>
+        <v>4253.889875309868</v>
       </c>
       <c r="C366" t="n">
-        <v>4514.36913384777</v>
+        <v>4079.842356526417</v>
       </c>
       <c r="D366" t="n">
-        <v>4860.918715571097</v>
-      </c>
-      <c r="E366" t="inlineStr"/>
+        <v>4433.607345759039</v>
+      </c>
+      <c r="E366" t="n">
+        <v>4284.474609375</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
-        <v>46267</v>
+        <v>46281</v>
       </c>
       <c r="B367" t="n">
-        <v>4707.746986108915</v>
+        <v>4256.152280460574</v>
       </c>
       <c r="C367" t="n">
-        <v>4534.561810788086</v>
+        <v>4102.824333573173</v>
       </c>
       <c r="D367" t="n">
-        <v>4885.0962105194</v>
-      </c>
-      <c r="E367" t="inlineStr"/>
+        <v>4430.535494838807</v>
+      </c>
+      <c r="E367" t="n">
+        <v>4330.77001953125</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
-        <v>46268</v>
+        <v>46282</v>
       </c>
       <c r="B368" t="n">
-        <v>4703.33875570295</v>
+        <v>4235.595087114642</v>
       </c>
       <c r="C368" t="n">
-        <v>4537.424041536517</v>
+        <v>4055.272795763664</v>
       </c>
       <c r="D368" t="n">
-        <v>4893.490115831116</v>
+        <v>4409.792858244292</v>
       </c>
       <c r="E368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
-        <v>46269</v>
+        <v>46283</v>
       </c>
       <c r="B369" t="n">
-        <v>4703.739717277193</v>
+        <v>4224.138961420169</v>
       </c>
       <c r="C369" t="n">
-        <v>4537.485528860905</v>
+        <v>4047.839476645354</v>
       </c>
       <c r="D369" t="n">
-        <v>4882.323168220306</v>
+        <v>4384.226875606212</v>
       </c>
       <c r="E369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B370" t="n">
-        <v>4713.275932070437</v>
+        <v>4223.563591933389</v>
       </c>
       <c r="C370" t="n">
-        <v>4543.606948938175</v>
+        <v>4049.960361888883</v>
       </c>
       <c r="D370" t="n">
-        <v>4872.505877996977</v>
+        <v>4391.76262998272</v>
       </c>
       <c r="E370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
-        <v>46271</v>
+        <v>46285</v>
       </c>
       <c r="B371" t="n">
-        <v>4711.397207581753</v>
+        <v>4221.487027784839</v>
       </c>
       <c r="C371" t="n">
-        <v>4543.410635013222</v>
+        <v>4044.830882477185</v>
       </c>
       <c r="D371" t="n">
-        <v>4886.104038339226</v>
+        <v>4389.162871004505</v>
       </c>
       <c r="E371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
-        <v>46272</v>
+        <v>46286</v>
       </c>
       <c r="B372" t="n">
-        <v>4724.922689458849</v>
+        <v>4239.650698010311</v>
       </c>
       <c r="C372" t="n">
-        <v>4560.809101054338</v>
+        <v>4068.450006731092</v>
       </c>
       <c r="D372" t="n">
-        <v>4898.346680489903</v>
+        <v>4411.167622890786</v>
       </c>
       <c r="E372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
-        <v>46273</v>
+        <v>46287</v>
       </c>
       <c r="B373" t="n">
-        <v>4727.84316337782</v>
+        <v>4241.369948343959</v>
       </c>
       <c r="C373" t="n">
-        <v>4549.315718527885</v>
+        <v>4074.530663846954</v>
       </c>
       <c r="D373" t="n">
-        <v>4897.298897791056</v>
+        <v>4416.831713595607</v>
       </c>
       <c r="E373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
-        <v>46274</v>
+        <v>46288</v>
       </c>
       <c r="B374" t="n">
-        <v>4739.70096187035</v>
+        <v>4267.070326077157</v>
       </c>
       <c r="C374" t="n">
-        <v>4561.718216088649</v>
+        <v>4082.572029295077</v>
       </c>
       <c r="D374" t="n">
-        <v>4913.751087613087</v>
+        <v>4435.596388291364</v>
       </c>
       <c r="E374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
-        <v>46275</v>
+        <v>46289</v>
       </c>
       <c r="B375" t="n">
-        <v>4728.173772625902</v>
+        <v>4270.259189369872</v>
       </c>
       <c r="C375" t="n">
-        <v>4548.26184515339</v>
+        <v>4103.324207030192</v>
       </c>
       <c r="D375" t="n">
-        <v>4902.57818380574</v>
+        <v>4434.658245412753</v>
       </c>
       <c r="E375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
-        <v>46276</v>
+        <v>46290</v>
       </c>
       <c r="B376" t="n">
-        <v>4722.665037990268</v>
+        <v>4282.407416938798</v>
       </c>
       <c r="C376" t="n">
-        <v>4543.316979655575</v>
+        <v>4110.513994998728</v>
       </c>
       <c r="D376" t="n">
-        <v>4901.872445943714</v>
+        <v>4463.90376185722</v>
       </c>
       <c r="E376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
-        <v>46277</v>
+        <v>46291</v>
       </c>
       <c r="B377" t="n">
-        <v>4727.690321268497</v>
+        <v>4304.844542617559</v>
       </c>
       <c r="C377" t="n">
-        <v>4553.317261432628</v>
+        <v>4132.762303252405</v>
       </c>
       <c r="D377" t="n">
-        <v>4912.838717724873</v>
+        <v>4474.40313598093</v>
       </c>
       <c r="E377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
-        <v>46278</v>
+        <v>46292</v>
       </c>
       <c r="B378" t="n">
-        <v>4722.860045285393</v>
+        <v>4324.748354663181</v>
       </c>
       <c r="C378" t="n">
-        <v>4541.534526708929</v>
+        <v>4158.886444714862</v>
       </c>
       <c r="D378" t="n">
-        <v>4881.055366037446</v>
+        <v>4486.151972343784</v>
       </c>
       <c r="E378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
-        <v>46279</v>
+        <v>46293</v>
       </c>
       <c r="B379" t="n">
-        <v>4735.119624496778</v>
+        <v>4363.440036709033</v>
       </c>
       <c r="C379" t="n">
-        <v>4557.482656814426</v>
+        <v>4194.910360398864</v>
       </c>
       <c r="D379" t="n">
-        <v>4911.460227787561</v>
+        <v>4539.064679248086</v>
       </c>
       <c r="E379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
-        <v>46280</v>
+        <v>46294</v>
       </c>
       <c r="B380" t="n">
-        <v>4738.547138694878</v>
+        <v>4383.844422636602</v>
       </c>
       <c r="C380" t="n">
-        <v>4575.505378329756</v>
+        <v>4203.75029161467</v>
       </c>
       <c r="D380" t="n">
-        <v>4919.422510430139</v>
+        <v>4555.697841387857</v>
       </c>
       <c r="E380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B381" t="n">
-        <v>4752.729596855808</v>
+        <v>4426.035340375062</v>
       </c>
       <c r="C381" t="n">
-        <v>4583.751459635055</v>
+        <v>4250.963928249726</v>
       </c>
       <c r="D381" t="n">
-        <v>4930.074811388106</v>
+        <v>4607.708210801135</v>
       </c>
       <c r="E381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
-        <v>46282</v>
+        <v>46296</v>
       </c>
       <c r="B382" t="n">
-        <v>4745.34421416177</v>
+        <v>4443.215381070851</v>
       </c>
       <c r="C382" t="n">
-        <v>4564.422518300332</v>
+        <v>4283.090641241415</v>
       </c>
       <c r="D382" t="n">
-        <v>4917.737980520633</v>
+        <v>4606.93952032046</v>
       </c>
       <c r="E382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
-        <v>46283</v>
+        <v>46297</v>
       </c>
       <c r="B383" t="n">
-        <v>4745.747487230148</v>
+        <v>4466.604652086569</v>
       </c>
       <c r="C383" t="n">
-        <v>4594.878873944665</v>
+        <v>4297.128220425019</v>
       </c>
       <c r="D383" t="n">
-        <v>4919.993562920321</v>
+        <v>4641.889798990184</v>
       </c>
       <c r="E383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
-        <v>46284</v>
+        <v>46298</v>
       </c>
       <c r="B384" t="n">
-        <v>4758.361504067012</v>
+        <v>4497.341649579404</v>
       </c>
       <c r="C384" t="n">
-        <v>4574.35122455802</v>
+        <v>4326.09967028554</v>
       </c>
       <c r="D384" t="n">
-        <v>4936.656602573571</v>
+        <v>4664.249976268125</v>
       </c>
       <c r="E384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
-        <v>46285</v>
+        <v>46299</v>
       </c>
       <c r="B385" t="n">
-        <v>4762.657918522693</v>
+        <v>4522.477135970279</v>
       </c>
       <c r="C385" t="n">
-        <v>4589.884420871505</v>
+        <v>4350.390664895551</v>
       </c>
       <c r="D385" t="n">
-        <v>4922.76736240704</v>
+        <v>4685.608984969631</v>
       </c>
       <c r="E385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
-        <v>46286</v>
+        <v>46300</v>
       </c>
       <c r="B386" t="n">
-        <v>4785.400597179533</v>
+        <v>4563.271983343753</v>
       </c>
       <c r="C386" t="n">
-        <v>4622.321471552636</v>
+        <v>4396.865813763931</v>
       </c>
       <c r="D386" t="n">
-        <v>4951.644153121052</v>
+        <v>4737.681761693692</v>
       </c>
       <c r="E386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
-        <v>46287</v>
+        <v>46301</v>
       </c>
       <c r="B387" t="n">
-        <v>4800.44703569471</v>
+        <v>4582.65848133939</v>
       </c>
       <c r="C387" t="n">
-        <v>4633.83283356127</v>
+        <v>4421.861302131683</v>
       </c>
       <c r="D387" t="n">
-        <v>4968.90111152761</v>
+        <v>4754.199467395099</v>
       </c>
       <c r="E387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
-        <v>46288</v>
+        <v>46302</v>
       </c>
       <c r="B388" t="n">
-        <v>4827.129505624357</v>
+        <v>4620.785055242698</v>
       </c>
       <c r="C388" t="n">
-        <v>4658.380885192474</v>
+        <v>4446.068329277313</v>
       </c>
       <c r="D388" t="n">
-        <v>4993.792688142384</v>
+        <v>4785.979625425657</v>
       </c>
       <c r="E388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
-        <v>46289</v>
+        <v>46303</v>
       </c>
       <c r="B389" t="n">
-        <v>4832.842233005881</v>
+        <v>4630.99374683102</v>
       </c>
       <c r="C389" t="n">
-        <v>4649.259476942503</v>
+        <v>4452.576514287175</v>
       </c>
       <c r="D389" t="n">
-        <v>4992.196551057192</v>
+        <v>4802.442658929414</v>
       </c>
       <c r="E389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
-        <v>46290</v>
+        <v>46304</v>
       </c>
       <c r="B390" t="n">
-        <v>4846.637241039536</v>
+        <v>4644.705077678525</v>
       </c>
       <c r="C390" t="n">
-        <v>4672.934795034479</v>
+        <v>4480.23761176474</v>
       </c>
       <c r="D390" t="n">
-        <v>5015.847159715127</v>
+        <v>4812.95084681417</v>
       </c>
       <c r="E390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
-        <v>46291</v>
+        <v>46305</v>
       </c>
       <c r="B391" t="n">
-        <v>4872.618114020807</v>
+        <v>4663.313535469692</v>
       </c>
       <c r="C391" t="n">
-        <v>4694.324841486547</v>
+        <v>4499.995966482547</v>
       </c>
       <c r="D391" t="n">
-        <v>5056.603716014049</v>
+        <v>4827.536725664918</v>
       </c>
       <c r="E391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
-        <v>46292</v>
+        <v>46306</v>
       </c>
       <c r="B392" t="n">
-        <v>4889.931911324493</v>
+        <v>4674.174714167813</v>
       </c>
       <c r="C392" t="n">
-        <v>4714.912303706985</v>
+        <v>4505.104436146971</v>
       </c>
       <c r="D392" t="n">
-        <v>5063.252265434552</v>
+        <v>4853.170675837844</v>
       </c>
       <c r="E392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
-        <v>46293</v>
+        <v>46307</v>
       </c>
       <c r="B393" t="n">
-        <v>4925.020022545306</v>
+        <v>4698.895251344298</v>
       </c>
       <c r="C393" t="n">
-        <v>4753.994845154289</v>
+        <v>4523.313127231032</v>
       </c>
       <c r="D393" t="n">
-        <v>5093.953096633913</v>
+        <v>4859.629182031789</v>
       </c>
       <c r="E393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
-        <v>46294</v>
+        <v>46308</v>
       </c>
       <c r="B394" t="n">
-        <v>4951.427834392931</v>
+        <v>4700.785275182223</v>
       </c>
       <c r="C394" t="n">
-        <v>4780.304872325491</v>
+        <v>4532.231545994007</v>
       </c>
       <c r="D394" t="n">
-        <v>5122.815853320753</v>
+        <v>4871.848201583487</v>
       </c>
       <c r="E394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
-        <v>46295</v>
+        <v>46309</v>
       </c>
       <c r="B395" t="n">
-        <v>4988.193940923049</v>
+        <v>4720.393546512562</v>
       </c>
       <c r="C395" t="n">
-        <v>4826.082828003448</v>
+        <v>4539.489562424717</v>
       </c>
       <c r="D395" t="n">
-        <v>5160.736708036404</v>
+        <v>4889.998987836218</v>
       </c>
       <c r="E395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B396" t="n">
+        <v>4711.474907070758</v>
+      </c>
+      <c r="C396" t="n">
+        <v>4534.147363650503</v>
+      </c>
+      <c r="D396" t="n">
+        <v>4878.181600087742</v>
+      </c>
+      <c r="E396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B397" t="n">
+        <v>4705.864924013026</v>
+      </c>
+      <c r="C397" t="n">
+        <v>4535.701511225338</v>
+      </c>
+      <c r="D397" t="n">
+        <v>4882.432441718302</v>
+      </c>
+      <c r="E397" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/XAUUSD_Predictivo.xlsx
+++ b/XAUUSD_Predictivo.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E397"/>
+  <dimension ref="A1:E396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6675 +449,6658 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45916</v>
+        <v>45921</v>
       </c>
       <c r="B2" t="n">
-        <v>3679.98083328355</v>
+        <v>3634.645969806586</v>
       </c>
       <c r="C2" t="n">
-        <v>3504.158284557758</v>
+        <v>3474.623935146207</v>
       </c>
       <c r="D2" t="n">
-        <v>3845.548265381387</v>
+        <v>3799.51682916316</v>
       </c>
       <c r="E2" t="n">
-        <v>3706.650146484375</v>
+        <v>3693.28857421875</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45917</v>
+        <v>45922</v>
       </c>
       <c r="B3" t="n">
-        <v>3686.017184185088</v>
+        <v>3663.898255793223</v>
       </c>
       <c r="C3" t="n">
-        <v>3530.527270426483</v>
+        <v>3502.753373358569</v>
       </c>
       <c r="D3" t="n">
-        <v>3860.742222606353</v>
+        <v>3829.254454932726</v>
       </c>
       <c r="E3" t="n">
-        <v>3674.03955078125</v>
+        <v>3761.20703125</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45918</v>
+        <v>45923</v>
       </c>
       <c r="B4" t="n">
-        <v>3669.516951580054</v>
+        <v>3674.340029322156</v>
       </c>
       <c r="C4" t="n">
-        <v>3500.862663587928</v>
+        <v>3498.26087965698</v>
       </c>
       <c r="D4" t="n">
-        <v>3841.921362598886</v>
+        <v>3843.710255323629</v>
       </c>
       <c r="E4" t="n">
-        <v>3646.354248046875</v>
+        <v>3774.19580078125</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45919</v>
+        <v>45924</v>
       </c>
       <c r="B5" t="n">
-        <v>3662.327410083399</v>
+        <v>3709.023002861693</v>
       </c>
       <c r="C5" t="n">
-        <v>3489.980836353495</v>
+        <v>3531.845448316127</v>
       </c>
       <c r="D5" t="n">
-        <v>3839.363610979202</v>
+        <v>3874.833215029075</v>
       </c>
       <c r="E5" t="n">
-        <v>3690.746337890625</v>
+        <v>3757.54638671875</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45920</v>
+        <v>45925</v>
       </c>
       <c r="B6" t="n">
-        <v>3666.149500847964</v>
+        <v>3724.156709960403</v>
       </c>
       <c r="C6" t="n">
-        <v>3501.820914968039</v>
+        <v>3557.7592013365</v>
       </c>
       <c r="D6" t="n">
-        <v>3841.17504734113</v>
+        <v>3896.181094620413</v>
       </c>
       <c r="E6" t="n">
-        <v>3688.934326171875</v>
+        <v>3755.103759765625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45921</v>
+        <v>45926</v>
       </c>
       <c r="B7" t="n">
-        <v>3668.518898794471</v>
+        <v>3743.747690757176</v>
       </c>
       <c r="C7" t="n">
-        <v>3492.244451335695</v>
+        <v>3589.007277746244</v>
       </c>
       <c r="D7" t="n">
-        <v>3840.804174300255</v>
+        <v>3919.363724242415</v>
       </c>
       <c r="E7" t="n">
-        <v>3693.28857421875</v>
+        <v>3775.42431640625</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45922</v>
+        <v>45927</v>
       </c>
       <c r="B8" t="n">
-        <v>3691.092875275434</v>
+        <v>3773.027696928548</v>
       </c>
       <c r="C8" t="n">
-        <v>3527.280622450407</v>
+        <v>3602.299218676312</v>
       </c>
       <c r="D8" t="n">
-        <v>3854.303618522702</v>
+        <v>3941.317478906112</v>
       </c>
       <c r="E8" t="n">
-        <v>3761.20703125</v>
+        <v>3776.893310546875</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45923</v>
+        <v>45928</v>
       </c>
       <c r="B9" t="n">
-        <v>3697.102745825419</v>
+        <v>3798.638163525805</v>
       </c>
       <c r="C9" t="n">
-        <v>3542.746299166445</v>
+        <v>3622.222708811287</v>
       </c>
       <c r="D9" t="n">
-        <v>3871.104148597615</v>
+        <v>3969.214818905011</v>
       </c>
       <c r="E9" t="n">
-        <v>3774.19580078125</v>
+        <v>3778.170654296875</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45924</v>
+        <v>45929</v>
       </c>
       <c r="B10" t="n">
-        <v>3726.892084549927</v>
+        <v>3842.727225128657</v>
       </c>
       <c r="C10" t="n">
-        <v>3567.951078819339</v>
+        <v>3656.191123789541</v>
       </c>
       <c r="D10" t="n">
-        <v>3899.047198318294</v>
+        <v>4011.570228426875</v>
       </c>
       <c r="E10" t="n">
-        <v>3757.54638671875</v>
+        <v>3848.826416015625</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45925</v>
+        <v>45930</v>
       </c>
       <c r="B11" t="n">
-        <v>3733.890231437271</v>
+        <v>3865.528602080934</v>
       </c>
       <c r="C11" t="n">
-        <v>3554.097547658839</v>
+        <v>3676.187547297029</v>
       </c>
       <c r="D11" t="n">
-        <v>3899.645348453991</v>
+        <v>4034.404901959507</v>
       </c>
       <c r="E11" t="n">
-        <v>3755.103759765625</v>
+        <v>3875.141357421875</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45926</v>
+        <v>45931</v>
       </c>
       <c r="B12" t="n">
-        <v>3749.495818761786</v>
+        <v>3909.866470486215</v>
       </c>
       <c r="C12" t="n">
-        <v>3568.65979851777</v>
+        <v>3728.461198038498</v>
       </c>
       <c r="D12" t="n">
-        <v>3921.363645353184</v>
+        <v>4083.854578028584</v>
       </c>
       <c r="E12" t="n">
-        <v>3775.42431640625</v>
+        <v>3874.288330078125</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45927</v>
+        <v>45932</v>
       </c>
       <c r="B13" t="n">
-        <v>3774.973593058987</v>
+        <v>3931.77976361326</v>
       </c>
       <c r="C13" t="n">
-        <v>3610.31514695008</v>
+        <v>3752.540449972922</v>
       </c>
       <c r="D13" t="n">
-        <v>3941.963347560436</v>
+        <v>4116.552104775806</v>
       </c>
       <c r="E13" t="n">
-        <v>3776.893310546875</v>
+        <v>3866.750244140625</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45928</v>
+        <v>45933</v>
       </c>
       <c r="B14" t="n">
-        <v>3797.445527639396</v>
+        <v>3955.165296180415</v>
       </c>
       <c r="C14" t="n">
-        <v>3630.608660801517</v>
+        <v>3790.481282947866</v>
       </c>
       <c r="D14" t="n">
-        <v>3961.206249037003</v>
+        <v>4118.997936851244</v>
       </c>
       <c r="E14" t="n">
-        <v>3778.170654296875</v>
+        <v>3886.2197265625</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45929</v>
+        <v>45934</v>
       </c>
       <c r="B15" t="n">
-        <v>3838.187261945236</v>
+        <v>3985.208434026391</v>
       </c>
       <c r="C15" t="n">
-        <v>3660.330588193615</v>
+        <v>3814.51967157012</v>
       </c>
       <c r="D15" t="n">
-        <v>4018.659354507531</v>
+        <v>4144.832146887419</v>
       </c>
       <c r="E15" t="n">
-        <v>3848.826416015625</v>
+        <v>3902.44921875</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45930</v>
+        <v>45935</v>
       </c>
       <c r="B16" t="n">
-        <v>3860.089405422192</v>
+        <v>4008.568486723067</v>
       </c>
       <c r="C16" t="n">
-        <v>3698.743939717142</v>
+        <v>3840.568279699873</v>
       </c>
       <c r="D16" t="n">
-        <v>4045.073155184002</v>
+        <v>4192.880690170495</v>
       </c>
       <c r="E16" t="n">
-        <v>3875.141357421875</v>
+        <v>3915.343017578125</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45931</v>
+        <v>45936</v>
       </c>
       <c r="B17" t="n">
-        <v>3903.203651774035</v>
+        <v>4047.475068169231</v>
       </c>
       <c r="C17" t="n">
-        <v>3738.357354264796</v>
+        <v>3879.172089554301</v>
       </c>
       <c r="D17" t="n">
-        <v>4086.38047529124</v>
+        <v>4215.752604857159</v>
       </c>
       <c r="E17" t="n">
-        <v>3874.288330078125</v>
+        <v>3984.27783203125</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45932</v>
+        <v>45937</v>
       </c>
       <c r="B18" t="n">
-        <v>3920.7230197826</v>
+        <v>4062.304765829645</v>
       </c>
       <c r="C18" t="n">
-        <v>3752.529874158814</v>
+        <v>3899.914527356896</v>
       </c>
       <c r="D18" t="n">
-        <v>4101.158778207985</v>
+        <v>4234.481753171628</v>
       </c>
       <c r="E18" t="n">
-        <v>3866.750244140625</v>
+        <v>4003.220703125</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45933</v>
+        <v>45938</v>
       </c>
       <c r="B19" t="n">
-        <v>3943.870765813413</v>
+        <v>4096.082285740646</v>
       </c>
       <c r="C19" t="n">
-        <v>3775.534513491252</v>
+        <v>3926.352719636622</v>
       </c>
       <c r="D19" t="n">
-        <v>4113.282923596983</v>
+        <v>4253.07356306122</v>
       </c>
       <c r="E19" t="n">
-        <v>3886.2197265625</v>
+        <v>4033.29296875</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45934</v>
+        <v>45939</v>
       </c>
       <c r="B20" t="n">
-        <v>3973.80109928985</v>
+        <v>4105.099616828674</v>
       </c>
       <c r="C20" t="n">
-        <v>3798.488927093038</v>
+        <v>3931.641691832568</v>
       </c>
       <c r="D20" t="n">
-        <v>4144.409050518306</v>
+        <v>4267.06385124389</v>
       </c>
       <c r="E20" t="n">
-        <v>3902.44921875</v>
+        <v>4002.012939453125</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45935</v>
+        <v>45940</v>
       </c>
       <c r="B21" t="n">
-        <v>3997.592590502234</v>
+        <v>4113.552740168073</v>
       </c>
       <c r="C21" t="n">
-        <v>3828.61582828885</v>
+        <v>3946.729905369379</v>
       </c>
       <c r="D21" t="n">
-        <v>4169.059241024563</v>
+        <v>4272.332942763408</v>
       </c>
       <c r="E21" t="n">
-        <v>3915.343017578125</v>
+        <v>3991.026611328125</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45936</v>
+        <v>45941</v>
       </c>
       <c r="B22" t="n">
-        <v>4036.545244356017</v>
+        <v>4126.964775019687</v>
       </c>
       <c r="C22" t="n">
-        <v>3869.01345597101</v>
+        <v>3968.680273580804</v>
       </c>
       <c r="D22" t="n">
-        <v>4219.819222719959</v>
+        <v>4308.76339772611</v>
       </c>
       <c r="E22" t="n">
-        <v>3984.27783203125</v>
+        <v>3996.272216796875</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45937</v>
+        <v>45942</v>
       </c>
       <c r="B23" t="n">
-        <v>4053.640759371051</v>
+        <v>4132.362937400983</v>
       </c>
       <c r="C23" t="n">
-        <v>3881.979892181364</v>
+        <v>3954.417584292612</v>
       </c>
       <c r="D23" t="n">
-        <v>4227.922060024126</v>
+        <v>4282.326726920935</v>
       </c>
       <c r="E23" t="n">
-        <v>4003.220703125</v>
+        <v>4041.53369140625</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45938</v>
+        <v>45943</v>
       </c>
       <c r="B24" t="n">
-        <v>4089.085946012002</v>
+        <v>4152.365782994109</v>
       </c>
       <c r="C24" t="n">
-        <v>3925.66849134036</v>
+        <v>3963.142869513267</v>
       </c>
       <c r="D24" t="n">
-        <v>4256.547988810617</v>
+        <v>4311.885184508037</v>
       </c>
       <c r="E24" t="n">
-        <v>4033.29296875</v>
+        <v>4144.38818359375</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45939</v>
+        <v>45944</v>
       </c>
       <c r="B25" t="n">
-        <v>4096.288692123832</v>
+        <v>4147.750315530799</v>
       </c>
       <c r="C25" t="n">
-        <v>3924.443231215124</v>
+        <v>3977.098015718461</v>
       </c>
       <c r="D25" t="n">
-        <v>4265.5979388037</v>
+        <v>4316.454866882076</v>
       </c>
       <c r="E25" t="n">
-        <v>4002.012939453125</v>
+        <v>4180.63134765625</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45940</v>
+        <v>45945</v>
       </c>
       <c r="B26" t="n">
-        <v>4106.741136148163</v>
+        <v>4161.943383799646</v>
       </c>
       <c r="C26" t="n">
-        <v>3931.599986463362</v>
+        <v>3994.371894254964</v>
       </c>
       <c r="D26" t="n">
-        <v>4280.014196322201</v>
+        <v>4337.989153590423</v>
       </c>
       <c r="E26" t="n">
-        <v>3991.026611328125</v>
+        <v>4241.47607421875</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45941</v>
+        <v>45946</v>
       </c>
       <c r="B27" t="n">
-        <v>4121.91333501499</v>
+        <v>4151.63117037666</v>
       </c>
       <c r="C27" t="n">
-        <v>3949.380927729744</v>
+        <v>3968.402017330239</v>
       </c>
       <c r="D27" t="n">
-        <v>4284.66981690064</v>
+        <v>4331.651189916435</v>
       </c>
       <c r="E27" t="n">
-        <v>3996.272216796875</v>
+        <v>4442.3642578125</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45942</v>
+        <v>45947</v>
       </c>
       <c r="B28" t="n">
-        <v>4129.238505676614</v>
+        <v>4141.386554302906</v>
       </c>
       <c r="C28" t="n">
-        <v>3958.853264489142</v>
+        <v>3975.82321112096</v>
       </c>
       <c r="D28" t="n">
-        <v>4298.207169104555</v>
+        <v>4304.853664583613</v>
       </c>
       <c r="E28" t="n">
-        <v>4041.53369140625</v>
+        <v>4241.09033203125</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45943</v>
+        <v>45948</v>
       </c>
       <c r="B29" t="n">
-        <v>4150.401035957357</v>
+        <v>4137.083487249752</v>
       </c>
       <c r="C29" t="n">
-        <v>3991.099666982571</v>
+        <v>3964.790421277051</v>
       </c>
       <c r="D29" t="n">
-        <v>4325.129842951778</v>
+        <v>4308.990108465946</v>
       </c>
       <c r="E29" t="n">
-        <v>4144.38818359375</v>
+        <v>4244.9248046875</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45944</v>
+        <v>45949</v>
       </c>
       <c r="B30" t="n">
-        <v>4148.78702853277</v>
+        <v>4126.065989197629</v>
       </c>
       <c r="C30" t="n">
-        <v>3977.789855780652</v>
+        <v>3961.69568130018</v>
       </c>
       <c r="D30" t="n">
-        <v>4309.731383617989</v>
+        <v>4300.093151158609</v>
       </c>
       <c r="E30" t="n">
-        <v>4180.63134765625</v>
+        <v>4245.95068359375</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45945</v>
+        <v>45950</v>
       </c>
       <c r="B31" t="n">
-        <v>4165.01761448621</v>
+        <v>4131.228442705669</v>
       </c>
       <c r="C31" t="n">
-        <v>3991.804257396494</v>
+        <v>3960.549880070783</v>
       </c>
       <c r="D31" t="n">
-        <v>4329.587814944636</v>
+        <v>4299.734007058049</v>
       </c>
       <c r="E31" t="n">
-        <v>4241.47607421875</v>
+        <v>4366.8720703125</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45946</v>
+        <v>45951</v>
       </c>
       <c r="B32" t="n">
-        <v>4152.914696292678</v>
+        <v>4113.576945009537</v>
       </c>
       <c r="C32" t="n">
-        <v>3989.685685697978</v>
+        <v>3954.970514739482</v>
       </c>
       <c r="D32" t="n">
-        <v>4318.543028760267</v>
+        <v>4273.327188868078</v>
       </c>
       <c r="E32" t="n">
-        <v>4442.3642578125</v>
+        <v>4106.2548828125</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45947</v>
+        <v>45952</v>
       </c>
       <c r="B33" t="n">
-        <v>4144.374055233611</v>
+        <v>4116.71628508972</v>
       </c>
       <c r="C33" t="n">
-        <v>3961.239174774665</v>
+        <v>3946.194265930188</v>
       </c>
       <c r="D33" t="n">
-        <v>4309.643204887405</v>
+        <v>4290.662504385377</v>
       </c>
       <c r="E33" t="n">
-        <v>4241.09033203125</v>
+        <v>4096.44775390625</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45948</v>
+        <v>45953</v>
       </c>
       <c r="B34" t="n">
-        <v>4141.249378201778</v>
+        <v>4097.456454342577</v>
       </c>
       <c r="C34" t="n">
-        <v>3970.557168357983</v>
+        <v>3933.699222704138</v>
       </c>
       <c r="D34" t="n">
-        <v>4310.937787323826</v>
+        <v>4264.193557468509</v>
       </c>
       <c r="E34" t="n">
-        <v>4244.9248046875</v>
+        <v>4118.24072265625</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45949</v>
+        <v>45954</v>
       </c>
       <c r="B35" t="n">
-        <v>4131.32853938781</v>
+        <v>4080.438538133612</v>
       </c>
       <c r="C35" t="n">
-        <v>3971.097806590483</v>
+        <v>3908.710765072999</v>
       </c>
       <c r="D35" t="n">
-        <v>4303.038503964092</v>
+        <v>4242.058726365361</v>
       </c>
       <c r="E35" t="n">
-        <v>4245.95068359375</v>
+        <v>4112.50732421875</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45950</v>
+        <v>45955</v>
       </c>
       <c r="B36" t="n">
-        <v>4136.613566440396</v>
+        <v>4071.549149040784</v>
       </c>
       <c r="C36" t="n">
-        <v>3959.841276702241</v>
+        <v>3907.618286712646</v>
       </c>
       <c r="D36" t="n">
-        <v>4304.145025207499</v>
+        <v>4250.703559226491</v>
       </c>
       <c r="E36" t="n">
-        <v>4366.8720703125</v>
+        <v>4110.4404296875</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45951</v>
+        <v>45956</v>
       </c>
       <c r="B37" t="n">
-        <v>4120.7642634564</v>
+        <v>4058.090986329203</v>
       </c>
       <c r="C37" t="n">
-        <v>3958.95909793175</v>
+        <v>3892.892895068849</v>
       </c>
       <c r="D37" t="n">
-        <v>4273.883040455215</v>
+        <v>4231.867150435889</v>
       </c>
       <c r="E37" t="n">
-        <v>4106.2548828125</v>
+        <v>4060.7724609375</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45952</v>
+        <v>45957</v>
       </c>
       <c r="B38" t="n">
-        <v>4124.586078716541</v>
+        <v>4062.866136258005</v>
       </c>
       <c r="C38" t="n">
-        <v>3957.333248021819</v>
+        <v>3904.58948699487</v>
       </c>
       <c r="D38" t="n">
-        <v>4295.092663281217</v>
+        <v>4230.079907102109</v>
       </c>
       <c r="E38" t="n">
-        <v>4096.44775390625</v>
+        <v>3990.343994140625</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45953</v>
+        <v>45958</v>
       </c>
       <c r="B39" t="n">
-        <v>4102.111132131103</v>
+        <v>4046.74176763333</v>
       </c>
       <c r="C39" t="n">
-        <v>3924.491844331415</v>
+        <v>3874.895790108932</v>
       </c>
       <c r="D39" t="n">
-        <v>4273.118262831422</v>
+        <v>4218.090502791254</v>
       </c>
       <c r="E39" t="n">
-        <v>4118.24072265625</v>
+        <v>3967.261962890625</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45954</v>
+        <v>45959</v>
       </c>
       <c r="B40" t="n">
-        <v>4085.349197729486</v>
+        <v>4053.142646668246</v>
       </c>
       <c r="C40" t="n">
-        <v>3917.283661401903</v>
+        <v>3886.955145060522</v>
       </c>
       <c r="D40" t="n">
-        <v>4248.024533911571</v>
+        <v>4216.414906738174</v>
       </c>
       <c r="E40" t="n">
-        <v>4112.50732421875</v>
+        <v>3953.506591796875</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45955</v>
+        <v>45960</v>
       </c>
       <c r="B41" t="n">
-        <v>4076.210483340957</v>
+        <v>4038.664204429956</v>
       </c>
       <c r="C41" t="n">
-        <v>3910.68472483911</v>
+        <v>3854.09157439357</v>
       </c>
       <c r="D41" t="n">
-        <v>4249.947621943275</v>
+        <v>4219.429865130852</v>
       </c>
       <c r="E41" t="n">
-        <v>4110.4404296875</v>
+        <v>4038.202392578125</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45956</v>
+        <v>45961</v>
       </c>
       <c r="B42" t="n">
-        <v>4062.482431482849</v>
+        <v>4027.705800042936</v>
       </c>
       <c r="C42" t="n">
-        <v>3881.260212548028</v>
+        <v>3858.902430271133</v>
       </c>
       <c r="D42" t="n">
-        <v>4228.386782676483</v>
+        <v>4199.642251514245</v>
       </c>
       <c r="E42" t="n">
-        <v>4060.7724609375</v>
+        <v>3998.996826171875</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45957</v>
+        <v>45962</v>
       </c>
       <c r="B43" t="n">
-        <v>4066.111755469501</v>
+        <v>4025.893114683161</v>
       </c>
       <c r="C43" t="n">
-        <v>3890.260683458306</v>
+        <v>3859.118441389331</v>
       </c>
       <c r="D43" t="n">
-        <v>4244.51867829717</v>
+        <v>4191.472986644044</v>
       </c>
       <c r="E43" t="n">
-        <v>3990.343994140625</v>
+        <v>4007.91015625</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45958</v>
+        <v>45963</v>
       </c>
       <c r="B44" t="n">
-        <v>4050.651599930293</v>
+        <v>4020.257019807355</v>
       </c>
       <c r="C44" t="n">
-        <v>3886.105393235133</v>
+        <v>3843.112137725438</v>
       </c>
       <c r="D44" t="n">
-        <v>4223.601470178025</v>
+        <v>4183.773354465206</v>
       </c>
       <c r="E44" t="n">
-        <v>3967.261962890625</v>
+        <v>3978.682373046875</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45959</v>
+        <v>45964</v>
       </c>
       <c r="B45" t="n">
-        <v>4056.794112619266</v>
+        <v>4033.325285051904</v>
       </c>
       <c r="C45" t="n">
-        <v>3873.392534459476</v>
+        <v>3856.337965682997</v>
       </c>
       <c r="D45" t="n">
-        <v>4231.424525811029</v>
+        <v>4202.217040766927</v>
       </c>
       <c r="E45" t="n">
-        <v>3953.506591796875</v>
+        <v>3991.654541015625</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45960</v>
+        <v>45965</v>
       </c>
       <c r="B46" t="n">
-        <v>4038.338062592251</v>
+        <v>4025.696530001188</v>
       </c>
       <c r="C46" t="n">
-        <v>3866.560941764771</v>
+        <v>3864.488606710952</v>
       </c>
       <c r="D46" t="n">
-        <v>4200.874381376351</v>
+        <v>4201.075801030426</v>
       </c>
       <c r="E46" t="n">
-        <v>4038.202392578125</v>
+        <v>3929.777099609375</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45961</v>
+        <v>45966</v>
       </c>
       <c r="B47" t="n">
-        <v>4027.066340805009</v>
+        <v>4040.540601055492</v>
       </c>
       <c r="C47" t="n">
-        <v>3854.586061813833</v>
+        <v>3870.622176821408</v>
       </c>
       <c r="D47" t="n">
-        <v>4188.861577367719</v>
+        <v>4208.475857441933</v>
       </c>
       <c r="E47" t="n">
-        <v>3998.996826171875</v>
+        <v>3971.510498046875</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45962</v>
+        <v>45967</v>
       </c>
       <c r="B48" t="n">
-        <v>4024.636728276019</v>
+        <v>4034.218876704882</v>
       </c>
       <c r="C48" t="n">
-        <v>3848.977301826964</v>
+        <v>3851.602763934835</v>
       </c>
       <c r="D48" t="n">
-        <v>4194.088682557625</v>
+        <v>4200.061470466452</v>
       </c>
       <c r="E48" t="n">
-        <v>4007.91015625</v>
+        <v>3984.83203125</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45963</v>
+        <v>45968</v>
       </c>
       <c r="B49" t="n">
-        <v>4018.567031980841</v>
+        <v>4030.923935755143</v>
       </c>
       <c r="C49" t="n">
-        <v>3843.980385694907</v>
+        <v>3870.130392254005</v>
       </c>
       <c r="D49" t="n">
-        <v>4184.631847595447</v>
+        <v>4189.098516239168</v>
       </c>
       <c r="E49" t="n">
-        <v>3978.682373046875</v>
+        <v>3989.748046875</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45964</v>
+        <v>45969</v>
       </c>
       <c r="B50" t="n">
-        <v>4030.525724487632</v>
+        <v>4036.10734126007</v>
       </c>
       <c r="C50" t="n">
-        <v>3852.792093612567</v>
+        <v>3873.416909685568</v>
       </c>
       <c r="D50" t="n">
-        <v>4206.12612521906</v>
+        <v>4217.491717807035</v>
       </c>
       <c r="E50" t="n">
-        <v>3991.654541015625</v>
+        <v>3988.74072265625</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45965</v>
+        <v>45970</v>
       </c>
       <c r="B51" t="n">
-        <v>4023.787716956515</v>
+        <v>4036.66273432503</v>
       </c>
       <c r="C51" t="n">
-        <v>3840.992496753285</v>
+        <v>3861.859381377139</v>
       </c>
       <c r="D51" t="n">
-        <v>4201.975120987146</v>
+        <v>4203.511624007651</v>
       </c>
       <c r="E51" t="n">
-        <v>3929.777099609375</v>
+        <v>4002.193115234375</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45966</v>
+        <v>45971</v>
       </c>
       <c r="B52" t="n">
-        <v>4038.775294984217</v>
+        <v>4055.020488429833</v>
       </c>
       <c r="C52" t="n">
-        <v>3872.50475682435</v>
+        <v>3886.107724579041</v>
       </c>
       <c r="D52" t="n">
-        <v>4209.29747682813</v>
+        <v>4238.150816097136</v>
       </c>
       <c r="E52" t="n">
-        <v>3971.510498046875</v>
+        <v>4111.927734375</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45967</v>
+        <v>45972</v>
       </c>
       <c r="B53" t="n">
-        <v>4029.033605560076</v>
+        <v>4051.723256229493</v>
       </c>
       <c r="C53" t="n">
-        <v>3868.644400961068</v>
+        <v>3866.47606048941</v>
       </c>
       <c r="D53" t="n">
-        <v>4196.411478285037</v>
+        <v>4224.66643368995</v>
       </c>
       <c r="E53" t="n">
-        <v>3984.83203125</v>
+        <v>4127.6044921875</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45968</v>
+        <v>45973</v>
       </c>
       <c r="B54" t="n">
-        <v>4026.115301511744</v>
+        <v>4069.926557733032</v>
       </c>
       <c r="C54" t="n">
-        <v>3851.255225786634</v>
+        <v>3908.19908943044</v>
       </c>
       <c r="D54" t="n">
-        <v>4208.694512818191</v>
+        <v>4237.902841235365</v>
       </c>
       <c r="E54" t="n">
-        <v>3989.748046875</v>
+        <v>4179.14697265625</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45969</v>
+        <v>45974</v>
       </c>
       <c r="B55" t="n">
-        <v>4031.477523297552</v>
+        <v>4066.017924430166</v>
       </c>
       <c r="C55" t="n">
-        <v>3859.84443834714</v>
+        <v>3896.513139257396</v>
       </c>
       <c r="D55" t="n">
-        <v>4202.024715179336</v>
+        <v>4230.257247033561</v>
       </c>
       <c r="E55" t="n">
-        <v>3988.74072265625</v>
+        <v>4172.74658203125</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45970</v>
+        <v>45975</v>
       </c>
       <c r="B56" t="n">
-        <v>4032.472143312809</v>
+        <v>4064.254087395292</v>
       </c>
       <c r="C56" t="n">
-        <v>3861.274593918728</v>
+        <v>3903.966222046346</v>
       </c>
       <c r="D56" t="n">
-        <v>4198.769465651539</v>
+        <v>4226.801895428642</v>
       </c>
       <c r="E56" t="n">
-        <v>4002.193115234375</v>
+        <v>4069.39794921875</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45971</v>
+        <v>45976</v>
       </c>
       <c r="B57" t="n">
-        <v>4050.640269165031</v>
+        <v>4070.185056365263</v>
       </c>
       <c r="C57" t="n">
-        <v>3875.059226729391</v>
+        <v>3891.211771372423</v>
       </c>
       <c r="D57" t="n">
-        <v>4227.972900882432</v>
+        <v>4236.315898939373</v>
       </c>
       <c r="E57" t="n">
-        <v>4111.927734375</v>
+        <v>4091.458740234375</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45972</v>
+        <v>45977</v>
       </c>
       <c r="B58" t="n">
-        <v>4049.170535331076</v>
+        <v>4070.832415070635</v>
       </c>
       <c r="C58" t="n">
-        <v>3886.372697030104</v>
+        <v>3906.47700367478</v>
       </c>
       <c r="D58" t="n">
-        <v>4216.440201712197</v>
+        <v>4241.213114797913</v>
       </c>
       <c r="E58" t="n">
-        <v>4127.6044921875</v>
+        <v>4090.231201171875</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45973</v>
+        <v>45978</v>
       </c>
       <c r="B59" t="n">
-        <v>4068.441155139883</v>
+        <v>4088.778250207787</v>
       </c>
       <c r="C59" t="n">
-        <v>3892.011233160719</v>
+        <v>3914.616065999534</v>
       </c>
       <c r="D59" t="n">
-        <v>4230.80284389538</v>
+        <v>4253.628972099725</v>
       </c>
       <c r="E59" t="n">
-        <v>4179.14697265625</v>
+        <v>4023.780517578125</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45974</v>
+        <v>45979</v>
       </c>
       <c r="B60" t="n">
-        <v>4061.995107250401</v>
+        <v>4084.734238524355</v>
       </c>
       <c r="C60" t="n">
-        <v>3896.262566485404</v>
+        <v>3919.208699157961</v>
       </c>
       <c r="D60" t="n">
-        <v>4222.786821298028</v>
+        <v>4264.414195435294</v>
       </c>
       <c r="E60" t="n">
-        <v>4172.74658203125</v>
+        <v>4065.880126953125</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45975</v>
+        <v>45980</v>
       </c>
       <c r="B61" t="n">
-        <v>4061.423093336321</v>
+        <v>4102.035257844958</v>
       </c>
       <c r="C61" t="n">
-        <v>3886.598112787671</v>
+        <v>3919.834095478</v>
       </c>
       <c r="D61" t="n">
-        <v>4221.55940538202</v>
+        <v>4283.441505773485</v>
       </c>
       <c r="E61" t="n">
-        <v>4069.39794921875</v>
+        <v>4093.896240234375</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45976</v>
+        <v>45981</v>
       </c>
       <c r="B62" t="n">
-        <v>4068.257520402572</v>
+        <v>4097.251269212304</v>
       </c>
       <c r="C62" t="n">
-        <v>3895.732440484211</v>
+        <v>3922.734223260007</v>
       </c>
       <c r="D62" t="n">
-        <v>4244.004433101946</v>
+        <v>4274.16021344098</v>
       </c>
       <c r="E62" t="n">
-        <v>4091.458740234375</v>
+        <v>4068.984375</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45977</v>
+        <v>45982</v>
       </c>
       <c r="B63" t="n">
-        <v>4069.958546286593</v>
+        <v>4094.81719789488</v>
       </c>
       <c r="C63" t="n">
-        <v>3877.942053807123</v>
+        <v>3914.432723244156</v>
       </c>
       <c r="D63" t="n">
-        <v>4240.865877834759</v>
+        <v>4270.77940824386</v>
       </c>
       <c r="E63" t="n">
-        <v>4090.231201171875</v>
+        <v>4062.59423828125</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45978</v>
+        <v>45983</v>
       </c>
       <c r="B64" t="n">
-        <v>4088.203336297971</v>
+        <v>4100.449903390542</v>
       </c>
       <c r="C64" t="n">
-        <v>3919.522000132935</v>
+        <v>3930.03442467279</v>
       </c>
       <c r="D64" t="n">
-        <v>4256.972862828757</v>
+        <v>4268.159974748176</v>
       </c>
       <c r="E64" t="n">
-        <v>4023.780517578125</v>
+        <v>4055.166015625</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45979</v>
+        <v>45984</v>
       </c>
       <c r="B65" t="n">
-        <v>4086.338243295263</v>
+        <v>4101.31979886181</v>
       </c>
       <c r="C65" t="n">
-        <v>3909.365165928529</v>
+        <v>3925.338231457766</v>
       </c>
       <c r="D65" t="n">
-        <v>4255.469227106907</v>
+        <v>4265.731475308639</v>
       </c>
       <c r="E65" t="n">
-        <v>4065.880126953125</v>
+        <v>4064.7265625</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45980</v>
+        <v>45985</v>
       </c>
       <c r="B66" t="n">
-        <v>4104.914092834551</v>
+        <v>4120.133759562044</v>
       </c>
       <c r="C66" t="n">
-        <v>3937.533332828321</v>
+        <v>3941.993953233698</v>
       </c>
       <c r="D66" t="n">
-        <v>4283.766956162192</v>
+        <v>4282.609603903348</v>
       </c>
       <c r="E66" t="n">
-        <v>4093.896240234375</v>
+        <v>4139.75537109375</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45981</v>
+        <v>45986</v>
       </c>
       <c r="B67" t="n">
-        <v>4097.654177115735</v>
+        <v>4117.699046185423</v>
       </c>
       <c r="C67" t="n">
-        <v>3930.057717443474</v>
+        <v>3953.798197493326</v>
       </c>
       <c r="D67" t="n">
-        <v>4278.412459237645</v>
+        <v>4273.485033693481</v>
       </c>
       <c r="E67" t="n">
-        <v>4068.984375</v>
+        <v>4124.7265625</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>45982</v>
+        <v>45987</v>
       </c>
       <c r="B68" t="n">
-        <v>4096.329836780767</v>
+        <v>4137.412783605666</v>
       </c>
       <c r="C68" t="n">
-        <v>3926.493855262593</v>
+        <v>3971.649159470261</v>
       </c>
       <c r="D68" t="n">
-        <v>4267.145369320202</v>
+        <v>4305.083684329013</v>
       </c>
       <c r="E68" t="n">
-        <v>4062.59423828125</v>
+        <v>4166.796875</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>45983</v>
+        <v>45988</v>
       </c>
       <c r="B69" t="n">
-        <v>4102.647131168213</v>
+        <v>4135.870883674752</v>
       </c>
       <c r="C69" t="n">
-        <v>3937.325896494297</v>
+        <v>3972.381361867476</v>
       </c>
       <c r="D69" t="n">
-        <v>4272.563564582486</v>
+        <v>4304.280758263883</v>
       </c>
       <c r="E69" t="n">
-        <v>4055.166015625</v>
+        <v>4160.1474609375</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>45984</v>
+        <v>45989</v>
       </c>
       <c r="B70" t="n">
-        <v>4104.225881020062</v>
+        <v>4137.496245940943</v>
       </c>
       <c r="C70" t="n">
-        <v>3939.173059976891</v>
+        <v>3969.452844762323</v>
       </c>
       <c r="D70" t="n">
-        <v>4283.32781853832</v>
+        <v>4318.819682014904</v>
       </c>
       <c r="E70" t="n">
-        <v>4064.7265625</v>
+        <v>4231.93359375</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>45985</v>
+        <v>45990</v>
       </c>
       <c r="B71" t="n">
-        <v>4122.882465676184</v>
+        <v>4147.955389811292</v>
       </c>
       <c r="C71" t="n">
-        <v>3956.747962591118</v>
+        <v>3987.73890925941</v>
       </c>
       <c r="D71" t="n">
-        <v>4305.471462809241</v>
+        <v>4326.437504856741</v>
       </c>
       <c r="E71" t="n">
-        <v>4139.75537109375</v>
+        <v>4250.109375</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>45986</v>
+        <v>45991</v>
       </c>
       <c r="B72" t="n">
-        <v>4122.076304358305</v>
+        <v>4154.331100914766</v>
       </c>
       <c r="C72" t="n">
-        <v>3944.432634135541</v>
+        <v>3986.466352140943</v>
       </c>
       <c r="D72" t="n">
-        <v>4287.916386491131</v>
+        <v>4313.236906190806</v>
       </c>
       <c r="E72" t="n">
-        <v>4124.7265625</v>
+        <v>4240.22265625</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="B73" t="n">
-        <v>4142.440395536507</v>
+        <v>4179.207709077872</v>
       </c>
       <c r="C73" t="n">
-        <v>3968.048409406009</v>
+        <v>4005.834210956481</v>
       </c>
       <c r="D73" t="n">
-        <v>4311.040044298414</v>
+        <v>4351.521073380955</v>
       </c>
       <c r="E73" t="n">
-        <v>4166.796875</v>
+        <v>4246.2890625</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>45988</v>
+        <v>45993</v>
       </c>
       <c r="B74" t="n">
-        <v>4137.745680849137</v>
+        <v>4183.238659362197</v>
       </c>
       <c r="C74" t="n">
-        <v>3975.377114505161</v>
+        <v>4016.877127328218</v>
       </c>
       <c r="D74" t="n">
-        <v>4308.242656068154</v>
+        <v>4357.007003953843</v>
       </c>
       <c r="E74" t="n">
-        <v>4160.1474609375</v>
+        <v>4215.837890625</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>45989</v>
+        <v>45994</v>
       </c>
       <c r="B75" t="n">
-        <v>4139.774237367299</v>
+        <v>4209.64080856598</v>
       </c>
       <c r="C75" t="n">
-        <v>3972.887524221773</v>
+        <v>4039.150226630768</v>
       </c>
       <c r="D75" t="n">
-        <v>4307.156068834139</v>
+        <v>4387.258065942043</v>
       </c>
       <c r="E75" t="n">
-        <v>4231.93359375</v>
+        <v>4215.3046875</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>45990</v>
+        <v>45995</v>
       </c>
       <c r="B76" t="n">
-        <v>4150.204886699297</v>
+        <v>4214.809192002542</v>
       </c>
       <c r="C76" t="n">
-        <v>3976.671606229506</v>
+        <v>4045.797376158856</v>
       </c>
       <c r="D76" t="n">
-        <v>4325.292903130395</v>
+        <v>4375.850494972387</v>
       </c>
       <c r="E76" t="n">
-        <v>4250.109375</v>
+        <v>4213.90283203125</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>45991</v>
+        <v>45996</v>
       </c>
       <c r="B77" t="n">
-        <v>4156.592547834725</v>
+        <v>4222.95191421178</v>
       </c>
       <c r="C77" t="n">
-        <v>3997.654166676367</v>
+        <v>4061.430183178924</v>
       </c>
       <c r="D77" t="n">
-        <v>4326.426714054623</v>
+        <v>4386.589173771771</v>
       </c>
       <c r="E77" t="n">
-        <v>4240.22265625</v>
+        <v>4211.54150390625</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>45992</v>
+        <v>45997</v>
       </c>
       <c r="B78" t="n">
-        <v>4180.65271526003</v>
+        <v>4239.51410874372</v>
       </c>
       <c r="C78" t="n">
-        <v>3999.174962434759</v>
+        <v>4076.770174952104</v>
       </c>
       <c r="D78" t="n">
-        <v>4355.403055238859</v>
+        <v>4409.494322806999</v>
       </c>
       <c r="E78" t="n">
-        <v>4246.2890625</v>
+        <v>4215.07421875</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>45993</v>
+        <v>45998</v>
       </c>
       <c r="B79" t="n">
-        <v>4185.710946779891</v>
+        <v>4251.358318476877</v>
       </c>
       <c r="C79" t="n">
-        <v>4002.631328696591</v>
+        <v>4088.185262994489</v>
       </c>
       <c r="D79" t="n">
-        <v>4356.973267020708</v>
+        <v>4413.29180584595</v>
       </c>
       <c r="E79" t="n">
-        <v>4215.837890625</v>
+        <v>4214.52880859375</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>45994</v>
+        <v>45999</v>
       </c>
       <c r="B80" t="n">
-        <v>4212.237646664912</v>
+        <v>4280.85766693076</v>
       </c>
       <c r="C80" t="n">
-        <v>4045.543904520634</v>
+        <v>4118.536330618005</v>
       </c>
       <c r="D80" t="n">
-        <v>4373.305993421724</v>
+        <v>4456.643834928355</v>
       </c>
       <c r="E80" t="n">
-        <v>4215.3046875</v>
+        <v>4203.466796875</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="B81" t="n">
-        <v>4213.817780487472</v>
+        <v>4288.471225982405</v>
       </c>
       <c r="C81" t="n">
-        <v>4036.083863771838</v>
+        <v>4124.364521241214</v>
       </c>
       <c r="D81" t="n">
-        <v>4382.665024823003</v>
+        <v>4460.059804192432</v>
       </c>
       <c r="E81" t="n">
-        <v>4213.90283203125</v>
+        <v>4215.78662109375</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>45996</v>
+        <v>46001</v>
       </c>
       <c r="B82" t="n">
-        <v>4222.03036053188</v>
+        <v>4317.245757951439</v>
       </c>
       <c r="C82" t="n">
-        <v>4049.598396542247</v>
+        <v>4150.503256903566</v>
       </c>
       <c r="D82" t="n">
-        <v>4382.364350680275</v>
+        <v>4466.557133869653</v>
       </c>
       <c r="E82" t="n">
-        <v>4211.54150390625</v>
+        <v>4240.0341796875</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>45997</v>
+        <v>46002</v>
       </c>
       <c r="B83" t="n">
-        <v>4238.341090279037</v>
+        <v>4323.437327196679</v>
       </c>
       <c r="C83" t="n">
-        <v>4082.02544086709</v>
+        <v>4168.453011209964</v>
       </c>
       <c r="D83" t="n">
-        <v>4407.136906080794</v>
+        <v>4501.279239696862</v>
       </c>
       <c r="E83" t="n">
-        <v>4215.07421875</v>
+        <v>4286.09228515625</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>45998</v>
+        <v>46003</v>
       </c>
       <c r="B84" t="n">
-        <v>4250.089270997601</v>
+        <v>4331.152202678647</v>
       </c>
       <c r="C84" t="n">
-        <v>4080.226418949735</v>
+        <v>4153.252126562063</v>
       </c>
       <c r="D84" t="n">
-        <v>4416.204256430809</v>
+        <v>4506.346622928534</v>
       </c>
       <c r="E84" t="n">
-        <v>4214.52880859375</v>
+        <v>4309.79052734375</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>45999</v>
+        <v>46004</v>
       </c>
       <c r="B85" t="n">
-        <v>4278.780108095391</v>
+        <v>4345.77578522578</v>
       </c>
       <c r="C85" t="n">
-        <v>4102.003433070071</v>
+        <v>4174.180657430271</v>
       </c>
       <c r="D85" t="n">
-        <v>4447.096953825467</v>
+        <v>4520.021262473397</v>
       </c>
       <c r="E85" t="n">
-        <v>4203.466796875</v>
+        <v>4318.52587890625</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46000</v>
+        <v>46005</v>
       </c>
       <c r="B86" t="n">
-        <v>4287.542045765228</v>
+        <v>4354.156731643199</v>
       </c>
       <c r="C86" t="n">
-        <v>4116.513540642393</v>
+        <v>4181.339418108869</v>
       </c>
       <c r="D86" t="n">
-        <v>4454.498596446073</v>
+        <v>4521.80857643765</v>
       </c>
       <c r="E86" t="n">
-        <v>4215.78662109375</v>
+        <v>4319.2890625</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46001</v>
+        <v>46006</v>
       </c>
       <c r="B87" t="n">
-        <v>4316.669156289901</v>
+        <v>4378.702498754839</v>
       </c>
       <c r="C87" t="n">
-        <v>4143.665699673745</v>
+        <v>4208.540084313313</v>
       </c>
       <c r="D87" t="n">
-        <v>4494.026386885651</v>
+        <v>4554.08588954001</v>
       </c>
       <c r="E87" t="n">
-        <v>4240.0341796875</v>
+        <v>4316.8115234375</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="B88" t="n">
-        <v>4319.597964933631</v>
+        <v>4379.955608226119</v>
       </c>
       <c r="C88" t="n">
-        <v>4149.602152179915</v>
+        <v>4196.26000655579</v>
       </c>
       <c r="D88" t="n">
-        <v>4497.161893063881</v>
+        <v>4553.448467943091</v>
       </c>
       <c r="E88" t="n">
-        <v>4286.09228515625</v>
+        <v>4322.4453125</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="B89" t="n">
-        <v>4327.793306276973</v>
+        <v>4401.094748588418</v>
       </c>
       <c r="C89" t="n">
-        <v>4175.239275753636</v>
+        <v>4232.479809688641</v>
       </c>
       <c r="D89" t="n">
-        <v>4494.415226317838</v>
+        <v>4555.440510115599</v>
       </c>
       <c r="E89" t="n">
-        <v>4309.79052734375</v>
+        <v>4359.79248046875</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46004</v>
+        <v>46009</v>
       </c>
       <c r="B90" t="n">
-        <v>4342.646377405978</v>
+        <v>4398.554194733334</v>
       </c>
       <c r="C90" t="n">
-        <v>4166.494084117518</v>
+        <v>4226.379244457613</v>
       </c>
       <c r="D90" t="n">
-        <v>4505.588396103951</v>
+        <v>4578.363783928104</v>
       </c>
       <c r="E90" t="n">
-        <v>4318.52587890625</v>
+        <v>4345.7919921875</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46005</v>
+        <v>46010</v>
       </c>
       <c r="B91" t="n">
-        <v>4351.465895090539</v>
+        <v>4396.660998884284</v>
       </c>
       <c r="C91" t="n">
-        <v>4183.281216409249</v>
+        <v>4231.309508692245</v>
       </c>
       <c r="D91" t="n">
-        <v>4507.019560135985</v>
+        <v>4570.229995218954</v>
       </c>
       <c r="E91" t="n">
-        <v>4319.2890625</v>
+        <v>4349.39208984375</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46006</v>
+        <v>46011</v>
       </c>
       <c r="B92" t="n">
-        <v>4375.773332126081</v>
+        <v>4401.05876761598</v>
       </c>
       <c r="C92" t="n">
-        <v>4213.964827345787</v>
+        <v>4224.108094922639</v>
       </c>
       <c r="D92" t="n">
-        <v>4546.515922431883</v>
+        <v>4574.74479996209</v>
       </c>
       <c r="E92" t="n">
-        <v>4316.8115234375</v>
+        <v>4350.67431640625</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46007</v>
+        <v>46012</v>
       </c>
       <c r="B93" t="n">
-        <v>4378.761738326404</v>
+        <v>4398.885320862815</v>
       </c>
       <c r="C93" t="n">
-        <v>4208.437600686695</v>
+        <v>4221.381332147764</v>
       </c>
       <c r="D93" t="n">
-        <v>4555.812875113013</v>
+        <v>4555.148329757501</v>
       </c>
       <c r="E93" t="n">
-        <v>4322.4453125</v>
+        <v>4364.52685546875</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46008</v>
+        <v>46013</v>
       </c>
       <c r="B94" t="n">
-        <v>4400.838092321217</v>
+        <v>4412.860625553217</v>
       </c>
       <c r="C94" t="n">
-        <v>4235.576568649813</v>
+        <v>4246.575981255406</v>
       </c>
       <c r="D94" t="n">
-        <v>4585.711637741809</v>
+        <v>4586.328513134086</v>
       </c>
       <c r="E94" t="n">
-        <v>4359.79248046875</v>
+        <v>4481.84814453125</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46009</v>
+        <v>46014</v>
       </c>
       <c r="B95" t="n">
-        <v>4395.598531661879</v>
+        <v>4403.854509629624</v>
       </c>
       <c r="C95" t="n">
-        <v>4210.771612192776</v>
+        <v>4237.466596115657</v>
       </c>
       <c r="D95" t="n">
-        <v>4578.004975194413</v>
+        <v>4570.360343034026</v>
       </c>
       <c r="E95" t="n">
-        <v>4345.7919921875</v>
+        <v>4530.59375</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46010</v>
+        <v>46015</v>
       </c>
       <c r="B96" t="n">
-        <v>4394.711071600616</v>
+        <v>4415.378510919232</v>
       </c>
       <c r="C96" t="n">
-        <v>4224.56731063591</v>
+        <v>4235.494833032808</v>
       </c>
       <c r="D96" t="n">
-        <v>4555.54238525123</v>
+        <v>4579.790691548049</v>
       </c>
       <c r="E96" t="n">
-        <v>4349.39208984375</v>
+        <v>4493.84716796875</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46011</v>
+        <v>46016</v>
       </c>
       <c r="B97" t="n">
-        <v>4399.809040562117</v>
+        <v>4404.195605445966</v>
       </c>
       <c r="C97" t="n">
-        <v>4225.188750019611</v>
+        <v>4234.309709187529</v>
       </c>
       <c r="D97" t="n">
-        <v>4567.33093979678</v>
+        <v>4576.080384024963</v>
       </c>
       <c r="E97" t="n">
-        <v>4350.67431640625</v>
+        <v>4513.3798828125</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46012</v>
+        <v>46017</v>
       </c>
       <c r="B98" t="n">
-        <v>4398.476249550194</v>
+        <v>4394.947549401802</v>
       </c>
       <c r="C98" t="n">
-        <v>4227.996691537754</v>
+        <v>4218.248964217493</v>
       </c>
       <c r="D98" t="n">
-        <v>4575.93939397342</v>
+        <v>4562.702927794786</v>
       </c>
       <c r="E98" t="n">
-        <v>4364.52685546875</v>
+        <v>4553.92822265625</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46013</v>
+        <v>46018</v>
       </c>
       <c r="B99" t="n">
-        <v>4412.535024447312</v>
+        <v>4393.568942352221</v>
       </c>
       <c r="C99" t="n">
-        <v>4236.395543960552</v>
+        <v>4221.587419823469</v>
       </c>
       <c r="D99" t="n">
-        <v>4594.321266767024</v>
+        <v>4570.577830034437</v>
       </c>
       <c r="E99" t="n">
-        <v>4481.84814453125</v>
+        <v>4567.81787109375</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46014</v>
+        <v>46019</v>
       </c>
       <c r="B100" t="n">
-        <v>4405.496801216519</v>
+        <v>4387.455599803072</v>
       </c>
       <c r="C100" t="n">
-        <v>4223.038602259031</v>
+        <v>4216.450169340765</v>
       </c>
       <c r="D100" t="n">
-        <v>4575.421052823316</v>
+        <v>4562.906246209021</v>
       </c>
       <c r="E100" t="n">
-        <v>4530.59375</v>
+        <v>4548.640625</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B101" t="n">
-        <v>4418.095459409892</v>
+        <v>4399.543913469343</v>
       </c>
       <c r="C101" t="n">
-        <v>4241.53330972717</v>
+        <v>4231.055909874472</v>
       </c>
       <c r="D101" t="n">
-        <v>4581.912630419843</v>
+        <v>4561.441765704596</v>
       </c>
       <c r="E101" t="n">
-        <v>4493.84716796875</v>
+        <v>4357.6005859375</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46016</v>
+        <v>46021</v>
       </c>
       <c r="B102" t="n">
-        <v>4404.252999240022</v>
+        <v>4390.870974629013</v>
       </c>
       <c r="C102" t="n">
-        <v>4233.160841452145</v>
+        <v>4222.557813881667</v>
       </c>
       <c r="D102" t="n">
-        <v>4578.187230304836</v>
+        <v>4571.215611592821</v>
       </c>
       <c r="E102" t="n">
-        <v>4513.3798828125</v>
+        <v>4355.40380859375</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46017</v>
+        <v>46022</v>
       </c>
       <c r="B103" t="n">
-        <v>4395.952451384594</v>
+        <v>4405.060060626978</v>
       </c>
       <c r="C103" t="n">
-        <v>4227.391873060053</v>
+        <v>4236.427552941626</v>
       </c>
       <c r="D103" t="n">
-        <v>4557.183969332498</v>
+        <v>4564.410381970515</v>
       </c>
       <c r="E103" t="n">
-        <v>4553.92822265625</v>
+        <v>4330.3779296875</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46018</v>
+        <v>46023</v>
       </c>
       <c r="B104" t="n">
-        <v>4395.121539517026</v>
+        <v>4398.925442070147</v>
       </c>
       <c r="C104" t="n">
-        <v>4225.872608037533</v>
+        <v>4222.131541096935</v>
       </c>
       <c r="D104" t="n">
-        <v>4564.493353614807</v>
+        <v>4572.936122422233</v>
       </c>
       <c r="E104" t="n">
-        <v>4567.81787109375</v>
+        <v>4356.462890625</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46019</v>
+        <v>46024</v>
       </c>
       <c r="B105" t="n">
-        <v>4389.608408665712</v>
+        <v>4397.096421489314</v>
       </c>
       <c r="C105" t="n">
-        <v>4224.531614662536</v>
+        <v>4219.967503297265</v>
       </c>
       <c r="D105" t="n">
-        <v>4573.855768360176</v>
+        <v>4568.416111038806</v>
       </c>
       <c r="E105" t="n">
-        <v>4548.640625</v>
+        <v>4341.74072265625</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46020</v>
+        <v>46025</v>
       </c>
       <c r="B106" t="n">
-        <v>4401.460840403241</v>
+        <v>4405.429840417014</v>
       </c>
       <c r="C106" t="n">
-        <v>4242.243632217984</v>
+        <v>4237.175912940252</v>
       </c>
       <c r="D106" t="n">
-        <v>4562.437543868713</v>
+        <v>4581.155424869608</v>
       </c>
       <c r="E106" t="n">
-        <v>4357.6005859375</v>
+        <v>4353.5283203125</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46021</v>
+        <v>46026</v>
       </c>
       <c r="B107" t="n">
-        <v>4394.368933152747</v>
+        <v>4411.178725757152</v>
       </c>
       <c r="C107" t="n">
-        <v>4217.441748816957</v>
+        <v>4237.343023654237</v>
       </c>
       <c r="D107" t="n">
-        <v>4556.238808318609</v>
+        <v>4580.817624908792</v>
       </c>
       <c r="E107" t="n">
-        <v>4355.40380859375</v>
+        <v>4383.18310546875</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="B108" t="n">
-        <v>4409.19167975584</v>
+        <v>4437.073783682259</v>
       </c>
       <c r="C108" t="n">
-        <v>4235.420863433837</v>
+        <v>4270.265140933167</v>
       </c>
       <c r="D108" t="n">
-        <v>4583.568749510269</v>
+        <v>4603.643014503278</v>
       </c>
       <c r="E108" t="n">
-        <v>4330.3779296875</v>
+        <v>4445.12109375</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46023</v>
+        <v>46028</v>
       </c>
       <c r="B109" t="n">
-        <v>4399.91727398007</v>
+        <v>4443.887493289039</v>
       </c>
       <c r="C109" t="n">
-        <v>4227.99479093967</v>
+        <v>4266.787606107798</v>
       </c>
       <c r="D109" t="n">
-        <v>4584.95492872417</v>
+        <v>4617.45420834911</v>
       </c>
       <c r="E109" t="n">
-        <v>4356.462890625</v>
+        <v>4509.8115234375</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46024</v>
+        <v>46029</v>
       </c>
       <c r="B110" t="n">
-        <v>4398.532225770298</v>
+        <v>4474.925322278454</v>
       </c>
       <c r="C110" t="n">
-        <v>4235.390487366489</v>
+        <v>4299.348865634434</v>
       </c>
       <c r="D110" t="n">
-        <v>4576.474922245006</v>
+        <v>4632.383505580262</v>
       </c>
       <c r="E110" t="n">
-        <v>4341.74072265625</v>
+        <v>4472.72314453125</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46025</v>
+        <v>46030</v>
       </c>
       <c r="B111" t="n">
-        <v>4406.90295104133</v>
+        <v>4486.637893460421</v>
       </c>
       <c r="C111" t="n">
-        <v>4232.968498940666</v>
+        <v>4320.596928598264</v>
       </c>
       <c r="D111" t="n">
-        <v>4585.292099529777</v>
+        <v>4644.182651660871</v>
       </c>
       <c r="E111" t="n">
-        <v>4353.5283203125</v>
+        <v>4478.43115234375</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46026</v>
+        <v>46031</v>
       </c>
       <c r="B112" t="n">
-        <v>4412.751247931885</v>
+        <v>4503.253833913007</v>
       </c>
       <c r="C112" t="n">
-        <v>4243.93203598864</v>
+        <v>4338.068448829645</v>
       </c>
       <c r="D112" t="n">
-        <v>4584.18070567848</v>
+        <v>4667.010794797129</v>
       </c>
       <c r="E112" t="n">
-        <v>4383.18310546875</v>
+        <v>4503.35595703125</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46027</v>
+        <v>46032</v>
       </c>
       <c r="B113" t="n">
-        <v>4437.935127010409</v>
+        <v>4530.202320408672</v>
       </c>
       <c r="C113" t="n">
-        <v>4258.613750801009</v>
+        <v>4371.950007273667</v>
       </c>
       <c r="D113" t="n">
-        <v>4608.3734944217</v>
+        <v>4709.713285096312</v>
       </c>
       <c r="E113" t="n">
-        <v>4445.12109375</v>
+        <v>4516.80322265625</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46028</v>
+        <v>46033</v>
       </c>
       <c r="B114" t="n">
-        <v>4445.894966285233</v>
+        <v>4554.29272961131</v>
       </c>
       <c r="C114" t="n">
-        <v>4279.206602364949</v>
+        <v>4380.823647551358</v>
       </c>
       <c r="D114" t="n">
-        <v>4628.96693801865</v>
+        <v>4714.365360156204</v>
       </c>
       <c r="E114" t="n">
-        <v>4509.8115234375</v>
+        <v>4538.0986328125</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46029</v>
+        <v>46034</v>
       </c>
       <c r="B115" t="n">
-        <v>4477.185361053229</v>
+        <v>4597.807807012912</v>
       </c>
       <c r="C115" t="n">
-        <v>4318.800218030116</v>
+        <v>4438.389268634885</v>
       </c>
       <c r="D115" t="n">
-        <v>4654.766093936721</v>
+        <v>4774.952253423371</v>
       </c>
       <c r="E115" t="n">
-        <v>4472.72314453125</v>
+        <v>4605.93798828125</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46030</v>
+        <v>46035</v>
       </c>
       <c r="B116" t="n">
-        <v>4485.442385044565</v>
+        <v>4621.079788247041</v>
       </c>
       <c r="C116" t="n">
-        <v>4316.999541762024</v>
+        <v>4455.634372913295</v>
       </c>
       <c r="D116" t="n">
-        <v>4649.691847132833</v>
+        <v>4781.763629272383</v>
       </c>
       <c r="E116" t="n">
-        <v>4478.43115234375</v>
+        <v>4601.09033203125</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46031</v>
+        <v>46036</v>
       </c>
       <c r="B117" t="n">
-        <v>4502.261175214153</v>
+        <v>4666.993662277889</v>
       </c>
       <c r="C117" t="n">
-        <v>4331.98946664482</v>
+        <v>4491.470296125656</v>
       </c>
       <c r="D117" t="n">
-        <v>4683.205894122827</v>
+        <v>4830.460555149066</v>
       </c>
       <c r="E117" t="n">
-        <v>4503.35595703125</v>
+        <v>4627.44287109375</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46032</v>
+        <v>46037</v>
       </c>
       <c r="B118" t="n">
-        <v>4529.087293246559</v>
+        <v>4691.61106542241</v>
       </c>
       <c r="C118" t="n">
-        <v>4361.612983746247</v>
+        <v>4524.186485234526</v>
       </c>
       <c r="D118" t="n">
-        <v>4691.360986469832</v>
+        <v>4853.749230783212</v>
       </c>
       <c r="E118" t="n">
-        <v>4516.80322265625</v>
+        <v>4621.1728515625</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46033</v>
+        <v>46038</v>
       </c>
       <c r="B119" t="n">
-        <v>4553.203020360659</v>
+        <v>4718.814202886357</v>
       </c>
       <c r="C119" t="n">
-        <v>4375.701718158091</v>
+        <v>4548.907067108334</v>
       </c>
       <c r="D119" t="n">
-        <v>4731.265875970312</v>
+        <v>4906.907180352612</v>
       </c>
       <c r="E119" t="n">
-        <v>4538.0986328125</v>
+        <v>4601.5517578125</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46034</v>
+        <v>46039</v>
       </c>
       <c r="B120" t="n">
-        <v>4596.019763544189</v>
+        <v>4753.73848998973</v>
       </c>
       <c r="C120" t="n">
-        <v>4418.50172919032</v>
+        <v>4576.403946715234</v>
       </c>
       <c r="D120" t="n">
-        <v>4776.057325829493</v>
+        <v>4922.815375173182</v>
       </c>
       <c r="E120" t="n">
-        <v>4605.93798828125</v>
+        <v>4609.82177734375</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46035</v>
+        <v>46040</v>
       </c>
       <c r="B121" t="n">
-        <v>4620.536227823192</v>
+        <v>4782.961021437125</v>
       </c>
       <c r="C121" t="n">
-        <v>4460.375951098629</v>
+        <v>4614.948146709908</v>
       </c>
       <c r="D121" t="n">
-        <v>4789.800118976399</v>
+        <v>4947.621532527135</v>
       </c>
       <c r="E121" t="n">
-        <v>4601.09033203125</v>
+        <v>4686.02978515625</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46036</v>
+        <v>46041</v>
       </c>
       <c r="B122" t="n">
-        <v>4666.882390627512</v>
+        <v>4828.601016210294</v>
       </c>
       <c r="C122" t="n">
-        <v>4498.050603989465</v>
+        <v>4659.912405654767</v>
       </c>
       <c r="D122" t="n">
-        <v>4829.209501310938</v>
+        <v>5006.6757638593</v>
       </c>
       <c r="E122" t="n">
-        <v>4627.44287109375</v>
+        <v>4681.861328125</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="B123" t="n">
-        <v>4688.298652094956</v>
+        <v>4850.901443367789</v>
       </c>
       <c r="C123" t="n">
-        <v>4531.362866067643</v>
+        <v>4675.738142665046</v>
       </c>
       <c r="D123" t="n">
-        <v>4870.038215569027</v>
+        <v>5025.266307801373</v>
       </c>
       <c r="E123" t="n">
-        <v>4621.1728515625</v>
+        <v>4802.517578125</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46038</v>
+        <v>46043</v>
       </c>
       <c r="B124" t="n">
-        <v>4716.024732351225</v>
+        <v>4892.735837148739</v>
       </c>
       <c r="C124" t="n">
-        <v>4543.265549753465</v>
+        <v>4714.991459807238</v>
       </c>
       <c r="D124" t="n">
-        <v>4879.009549928642</v>
+        <v>5063.642589073476</v>
       </c>
       <c r="E124" t="n">
-        <v>4601.5517578125</v>
+        <v>4807.76416015625</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46039</v>
+        <v>46044</v>
       </c>
       <c r="B125" t="n">
-        <v>4751.20143859398</v>
+        <v>4910.233661457509</v>
       </c>
       <c r="C125" t="n">
-        <v>4602.643680808054</v>
+        <v>4748.832220332376</v>
       </c>
       <c r="D125" t="n">
-        <v>4920.99860064998</v>
+        <v>5073.649295027071</v>
       </c>
       <c r="E125" t="n">
-        <v>4609.82177734375</v>
+        <v>4974.0048828125</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46040</v>
+        <v>46045</v>
       </c>
       <c r="B126" t="n">
-        <v>4780.866149059434</v>
+        <v>4927.423548264893</v>
       </c>
       <c r="C126" t="n">
-        <v>4608.32601131926</v>
+        <v>4763.538989016013</v>
       </c>
       <c r="D126" t="n">
-        <v>4955.244729703289</v>
+        <v>5096.751525306561</v>
       </c>
       <c r="E126" t="n">
-        <v>4686.02978515625</v>
+        <v>5001.9541015625</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46041</v>
+        <v>46046</v>
       </c>
       <c r="B127" t="n">
-        <v>4826.252912318194</v>
+        <v>4949.663088685369</v>
       </c>
       <c r="C127" t="n">
-        <v>4656.873020406229</v>
+        <v>4783.498654900412</v>
       </c>
       <c r="D127" t="n">
-        <v>4999.508802877783</v>
+        <v>5130.821783408368</v>
       </c>
       <c r="E127" t="n">
-        <v>4681.861328125</v>
+        <v>5075.52392578125</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46042</v>
+        <v>46047</v>
       </c>
       <c r="B128" t="n">
-        <v>4850.256575231139</v>
+        <v>4963.822333716196</v>
       </c>
       <c r="C128" t="n">
-        <v>4685.026317649916</v>
+        <v>4790.111181462435</v>
       </c>
       <c r="D128" t="n">
-        <v>5025.502964744303</v>
+        <v>5140.308723940267</v>
       </c>
       <c r="E128" t="n">
-        <v>4802.517578125</v>
+        <v>5063.904296875</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46043</v>
+        <v>46048</v>
       </c>
       <c r="B129" t="n">
-        <v>4892.980779856387</v>
+        <v>4992.377258559014</v>
       </c>
       <c r="C129" t="n">
-        <v>4717.293973146627</v>
+        <v>4826.915860621454</v>
       </c>
       <c r="D129" t="n">
-        <v>5050.020457100441</v>
+        <v>5152.614679520919</v>
       </c>
       <c r="E129" t="n">
-        <v>4807.76416015625</v>
+        <v>5057.650390625</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="B130" t="n">
-        <v>4907.719059372949</v>
+        <v>4995.98256127675</v>
       </c>
       <c r="C130" t="n">
-        <v>4745.423684881164</v>
+        <v>4819.741417041825</v>
       </c>
       <c r="D130" t="n">
-        <v>5072.024033198537</v>
+        <v>5156.17017958814</v>
       </c>
       <c r="E130" t="n">
-        <v>4974.0048828125</v>
+        <v>5187.36669921875</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46045</v>
+        <v>46050</v>
       </c>
       <c r="B131" t="n">
-        <v>4925.843516840465</v>
+        <v>5017.967867044229</v>
       </c>
       <c r="C131" t="n">
-        <v>4760.731917171539</v>
+        <v>4848.743808124726</v>
       </c>
       <c r="D131" t="n">
-        <v>5091.081195155939</v>
+        <v>5200.4803872948</v>
       </c>
       <c r="E131" t="n">
-        <v>5001.9541015625</v>
+        <v>5536.52734375</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46046</v>
+        <v>46051</v>
       </c>
       <c r="B132" t="n">
-        <v>4948.704182312458</v>
+        <v>5014.951742341493</v>
       </c>
       <c r="C132" t="n">
-        <v>4781.599753922397</v>
+        <v>4841.06173365414</v>
       </c>
       <c r="D132" t="n">
-        <v>5121.134611384064</v>
+        <v>5182.136186330578</v>
       </c>
       <c r="E132" t="n">
-        <v>5075.52392578125</v>
+        <v>5467.4462890625</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46047</v>
+        <v>46052</v>
       </c>
       <c r="B133" t="n">
-        <v>4963.619929254116</v>
+        <v>5011.471595951743</v>
       </c>
       <c r="C133" t="n">
-        <v>4784.852448543853</v>
+        <v>4832.224922024381</v>
       </c>
       <c r="D133" t="n">
-        <v>5144.399577962139</v>
+        <v>5182.824396742442</v>
       </c>
       <c r="E133" t="n">
-        <v>5063.904296875</v>
+        <v>4912.69970703125</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="B134" t="n">
-        <v>4992.171943974606</v>
+        <v>5013.400041658147</v>
       </c>
       <c r="C134" t="n">
-        <v>4830.7072923361</v>
+        <v>4851.568078942358</v>
       </c>
       <c r="D134" t="n">
-        <v>5162.727766286954</v>
+        <v>5170.55133191414</v>
       </c>
       <c r="E134" t="n">
-        <v>5057.650390625</v>
+        <v>4834.16162109375</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46049</v>
+        <v>46054</v>
       </c>
       <c r="B135" t="n">
-        <v>4997.659315713945</v>
+        <v>5008.114466528639</v>
       </c>
       <c r="C135" t="n">
-        <v>4815.593864012533</v>
+        <v>4849.007647306314</v>
       </c>
       <c r="D135" t="n">
-        <v>5171.653174778126</v>
+        <v>5182.699228572707</v>
       </c>
       <c r="E135" t="n">
-        <v>5187.36669921875</v>
+        <v>4760.32666015625</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46050</v>
+        <v>46055</v>
       </c>
       <c r="B136" t="n">
-        <v>5020.636797629644</v>
+        <v>5018.57659282125</v>
       </c>
       <c r="C136" t="n">
-        <v>4849.621904176636</v>
+        <v>4847.834376564699</v>
       </c>
       <c r="D136" t="n">
-        <v>5196.512145676096</v>
+        <v>5187.010815203356</v>
       </c>
       <c r="E136" t="n">
-        <v>5536.52734375</v>
+        <v>4785.6171875</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46051</v>
+        <v>46056</v>
       </c>
       <c r="B137" t="n">
-        <v>5014.884229012263</v>
+        <v>5005.891786417961</v>
       </c>
       <c r="C137" t="n">
-        <v>4841.837706687272</v>
+        <v>4842.134477622432</v>
       </c>
       <c r="D137" t="n">
-        <v>5190.22357458344</v>
+        <v>5177.157852163029</v>
       </c>
       <c r="E137" t="n">
-        <v>5467.4462890625</v>
+        <v>4956.98681640625</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46052</v>
+        <v>46057</v>
       </c>
       <c r="B138" t="n">
-        <v>5012.282406406678</v>
+        <v>5013.79271374315</v>
       </c>
       <c r="C138" t="n">
-        <v>4839.875154801764</v>
+        <v>4848.102622282493</v>
       </c>
       <c r="D138" t="n">
-        <v>5185.776255499069</v>
+        <v>5176.91856943591</v>
       </c>
       <c r="E138" t="n">
-        <v>4912.69970703125</v>
+        <v>5023.80615234375</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46053</v>
+        <v>46058</v>
       </c>
       <c r="B139" t="n">
-        <v>5014.698838494355</v>
+        <v>4999.241331499815</v>
       </c>
       <c r="C139" t="n">
-        <v>4843.688561855582</v>
+        <v>4826.171655409255</v>
       </c>
       <c r="D139" t="n">
-        <v>5198.13222506133</v>
+        <v>5174.773135139755</v>
       </c>
       <c r="E139" t="n">
-        <v>4834.16162109375</v>
+        <v>4695.63037109375</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46054</v>
+        <v>46059</v>
       </c>
       <c r="B140" t="n">
-        <v>5009.964631621449</v>
+        <v>4987.049171604661</v>
       </c>
       <c r="C140" t="n">
-        <v>4836.03930810257</v>
+        <v>4827.559992849246</v>
       </c>
       <c r="D140" t="n">
-        <v>5166.310278187486</v>
+        <v>5164.728692435071</v>
       </c>
       <c r="E140" t="n">
-        <v>4760.32666015625</v>
+        <v>4940.42236328125</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46055</v>
+        <v>46060</v>
       </c>
       <c r="B141" t="n">
-        <v>5020.153881855362</v>
+        <v>4983.285233974691</v>
       </c>
       <c r="C141" t="n">
-        <v>4836.826248418905</v>
+        <v>4811.984198740798</v>
       </c>
       <c r="D141" t="n">
-        <v>5184.085091610219</v>
+        <v>5147.649898149818</v>
       </c>
       <c r="E141" t="n">
-        <v>4785.6171875</v>
+        <v>4989.26904296875</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46056</v>
+        <v>46061</v>
       </c>
       <c r="B142" t="n">
-        <v>5009.025529507306</v>
+        <v>4975.439256488422</v>
       </c>
       <c r="C142" t="n">
-        <v>4853.481994058684</v>
+        <v>4802.455588575673</v>
       </c>
       <c r="D142" t="n">
-        <v>5178.290421917505</v>
+        <v>5142.5123334026</v>
       </c>
       <c r="E142" t="n">
-        <v>4956.98681640625</v>
+        <v>5042.5322265625</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46057</v>
+        <v>46062</v>
       </c>
       <c r="B143" t="n">
-        <v>5017.548109512907</v>
+        <v>4986.497189615811</v>
       </c>
       <c r="C143" t="n">
-        <v>4846.607394808568</v>
+        <v>4806.107917956424</v>
       </c>
       <c r="D143" t="n">
-        <v>5190.999448876049</v>
+        <v>5154.150091311583</v>
       </c>
       <c r="E143" t="n">
-        <v>5023.80615234375</v>
+        <v>5035.80712890625</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46058</v>
+        <v>46063</v>
       </c>
       <c r="B144" t="n">
-        <v>4999.857257037736</v>
+        <v>4977.498765359258</v>
       </c>
       <c r="C144" t="n">
-        <v>4824.180423685173</v>
+        <v>4814.807902739114</v>
       </c>
       <c r="D144" t="n">
-        <v>5161.664739432748</v>
+        <v>5152.35005350696</v>
       </c>
       <c r="E144" t="n">
-        <v>4695.63037109375</v>
+        <v>5041.4326171875</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46059</v>
+        <v>46064</v>
       </c>
       <c r="B145" t="n">
-        <v>4988.121095358596</v>
+        <v>4992.021835666611</v>
       </c>
       <c r="C145" t="n">
-        <v>4824.45715731221</v>
+        <v>4821.11876145051</v>
       </c>
       <c r="D145" t="n">
-        <v>5153.59053134142</v>
+        <v>5178.03268673353</v>
       </c>
       <c r="E145" t="n">
-        <v>4940.42236328125</v>
+        <v>5075.75927734375</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46060</v>
+        <v>46065</v>
       </c>
       <c r="B146" t="n">
-        <v>4984.417249352306</v>
+        <v>4986.787473377351</v>
       </c>
       <c r="C146" t="n">
-        <v>4804.833309229332</v>
+        <v>4812.80638173773</v>
       </c>
       <c r="D146" t="n">
-        <v>5164.694909649383</v>
+        <v>5165.000168578456</v>
       </c>
       <c r="E146" t="n">
-        <v>4989.26904296875</v>
+        <v>4920.12548828125</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46061</v>
+        <v>46066</v>
       </c>
       <c r="B147" t="n">
-        <v>4976.702991645579</v>
+        <v>4986.285739915756</v>
       </c>
       <c r="C147" t="n">
-        <v>4806.970464335334</v>
+        <v>4828.709555267948</v>
       </c>
       <c r="D147" t="n">
-        <v>5147.553129619774</v>
+        <v>5156.147510648073</v>
       </c>
       <c r="E147" t="n">
-        <v>5042.5322265625</v>
+        <v>5043.77783203125</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46062</v>
+        <v>46067</v>
       </c>
       <c r="B148" t="n">
-        <v>4987.0901065998</v>
+        <v>4996.191309335194</v>
       </c>
       <c r="C148" t="n">
-        <v>4807.660347531133</v>
+        <v>4824.894194733228</v>
       </c>
       <c r="D148" t="n">
-        <v>5154.043035907172</v>
+        <v>5174.509162889283</v>
       </c>
       <c r="E148" t="n">
-        <v>5035.80712890625</v>
+        <v>5021.64599609375</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46063</v>
+        <v>46068</v>
       </c>
       <c r="B149" t="n">
-        <v>4979.284578472212</v>
+        <v>5003.536532623165</v>
       </c>
       <c r="C149" t="n">
-        <v>4805.012687153277</v>
+        <v>4829.902343640009</v>
       </c>
       <c r="D149" t="n">
-        <v>5152.852960001039</v>
+        <v>5174.117191939599</v>
       </c>
       <c r="E149" t="n">
-        <v>5041.4326171875</v>
+        <v>5022.30224609375</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46064</v>
+        <v>46069</v>
       </c>
       <c r="B150" t="n">
-        <v>4994.111624438245</v>
+        <v>5030.798526651924</v>
       </c>
       <c r="C150" t="n">
-        <v>4814.603689857313</v>
+        <v>4851.571641208171</v>
       </c>
       <c r="D150" t="n">
-        <v>5151.314464013124</v>
+        <v>5209.590147856515</v>
       </c>
       <c r="E150" t="n">
-        <v>5075.75927734375</v>
+        <v>4996.603515625</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="B151" t="n">
-        <v>4985.475951311962</v>
+        <v>5038.469882490003</v>
       </c>
       <c r="C151" t="n">
-        <v>4813.608658586528</v>
+        <v>4864.598398557168</v>
       </c>
       <c r="D151" t="n">
-        <v>5158.043353577128</v>
+        <v>5196.601323071653</v>
       </c>
       <c r="E151" t="n">
-        <v>4920.12548828125</v>
+        <v>4864.6728515625</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46066</v>
+        <v>46071</v>
       </c>
       <c r="B152" t="n">
-        <v>4985.232318630234</v>
+        <v>5069.557330127232</v>
       </c>
       <c r="C152" t="n">
-        <v>4806.573068066156</v>
+        <v>4882.182440172657</v>
       </c>
       <c r="D152" t="n">
-        <v>5149.333654290877</v>
+        <v>5244.874922125709</v>
       </c>
       <c r="E152" t="n">
-        <v>5043.77783203125</v>
+        <v>4977.79296875</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46067</v>
+        <v>46072</v>
       </c>
       <c r="B153" t="n">
-        <v>4995.0700353334</v>
+        <v>5080.20197866238</v>
       </c>
       <c r="C153" t="n">
-        <v>4830.691195428444</v>
+        <v>4907.038070085476</v>
       </c>
       <c r="D153" t="n">
-        <v>5171.595949174343</v>
+        <v>5249.263384902625</v>
       </c>
       <c r="E153" t="n">
-        <v>5021.64599609375</v>
+        <v>4998.19921875</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46068</v>
+        <v>46073</v>
       </c>
       <c r="B154" t="n">
-        <v>5002.492720664041</v>
+        <v>5094.320637894867</v>
       </c>
       <c r="C154" t="n">
-        <v>4829.904610276092</v>
+        <v>4931.007280647185</v>
       </c>
       <c r="D154" t="n">
-        <v>5178.334116341261</v>
+        <v>5272.527531122983</v>
       </c>
       <c r="E154" t="n">
-        <v>5022.30224609375</v>
+        <v>5113.32421875</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46069</v>
+        <v>46074</v>
       </c>
       <c r="B155" t="n">
-        <v>5029.104674999034</v>
+        <v>5117.03699753702</v>
       </c>
       <c r="C155" t="n">
-        <v>4859.503960552755</v>
+        <v>4951.346278384572</v>
       </c>
       <c r="D155" t="n">
-        <v>5199.687706241644</v>
+        <v>5276.800366682414</v>
       </c>
       <c r="E155" t="n">
-        <v>4996.603515625</v>
+        <v>5140.05224609375</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46070</v>
+        <v>46075</v>
       </c>
       <c r="B156" t="n">
-        <v>5038.063677979701</v>
+        <v>5134.869832540539</v>
       </c>
       <c r="C156" t="n">
-        <v>4872.520670850408</v>
+        <v>4970.8989422058</v>
       </c>
       <c r="D156" t="n">
-        <v>5207.755274773753</v>
+        <v>5308.116669064169</v>
       </c>
       <c r="E156" t="n">
-        <v>4864.6728515625</v>
+        <v>5187.380859375</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46071</v>
+        <v>46076</v>
       </c>
       <c r="B157" t="n">
-        <v>5069.620393877576</v>
+        <v>5169.834409989267</v>
       </c>
       <c r="C157" t="n">
-        <v>4901.505630517239</v>
+        <v>4997.705180171795</v>
       </c>
       <c r="D157" t="n">
-        <v>5240.906506672187</v>
+        <v>5353.701947004023</v>
       </c>
       <c r="E157" t="n">
-        <v>4977.79296875</v>
+        <v>5255.55078125</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46072</v>
+        <v>46077</v>
       </c>
       <c r="B158" t="n">
-        <v>5077.093889005126</v>
+        <v>5182.026303655935</v>
       </c>
       <c r="C158" t="n">
-        <v>4902.809293429342</v>
+        <v>5005.296876961932</v>
       </c>
       <c r="D158" t="n">
-        <v>5231.159742791514</v>
+        <v>5364.742075082777</v>
       </c>
       <c r="E158" t="n">
-        <v>4998.19921875</v>
+        <v>5168.69970703125</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46073</v>
+        <v>46078</v>
       </c>
       <c r="B159" t="n">
-        <v>5091.757940777432</v>
+        <v>5214.131593991988</v>
       </c>
       <c r="C159" t="n">
-        <v>4926.129223462964</v>
+        <v>5050.748054707647</v>
       </c>
       <c r="D159" t="n">
-        <v>5266.288990154475</v>
+        <v>5391.356028439639</v>
       </c>
       <c r="E159" t="n">
-        <v>5113.32421875</v>
+        <v>5179.78759765625</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46074</v>
+        <v>46079</v>
       </c>
       <c r="B160" t="n">
-        <v>5114.741346297295</v>
+        <v>5222.056753078135</v>
       </c>
       <c r="C160" t="n">
-        <v>4934.888154092763</v>
+        <v>5052.838598537306</v>
       </c>
       <c r="D160" t="n">
-        <v>5281.085672745211</v>
+        <v>5400.049136679713</v>
       </c>
       <c r="E160" t="n">
-        <v>5140.05224609375</v>
+        <v>5196.6904296875</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46075</v>
+        <v>46080</v>
       </c>
       <c r="B161" t="n">
-        <v>5133.023136212798</v>
+        <v>5229.577449410124</v>
       </c>
       <c r="C161" t="n">
-        <v>4966.498939900103</v>
+        <v>5052.232344279923</v>
       </c>
       <c r="D161" t="n">
-        <v>5304.048152269485</v>
+        <v>5404.966153785336</v>
       </c>
       <c r="E161" t="n">
-        <v>5187.380859375</v>
+        <v>5291.09228515625</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46076</v>
+        <v>46081</v>
       </c>
       <c r="B162" t="n">
-        <v>5167.733622647159</v>
+        <v>5241.774834230773</v>
       </c>
       <c r="C162" t="n">
-        <v>5007.972374415309</v>
+        <v>5066.122659883613</v>
       </c>
       <c r="D162" t="n">
-        <v>5345.562827914383</v>
+        <v>5407.657357368063</v>
       </c>
       <c r="E162" t="n">
-        <v>5255.55078125</v>
+        <v>5372.89599609375</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46077</v>
+        <v>46082</v>
       </c>
       <c r="B163" t="n">
-        <v>5181.620695292757</v>
+        <v>5245.2263243908</v>
       </c>
       <c r="C163" t="n">
-        <v>5031.062818781224</v>
+        <v>5092.629743492432</v>
       </c>
       <c r="D163" t="n">
-        <v>5352.497963113022</v>
+        <v>5419.360237761106</v>
       </c>
       <c r="E163" t="n">
-        <v>5168.69970703125</v>
+        <v>5435.98974609375</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46078</v>
+        <v>46083</v>
       </c>
       <c r="B164" t="n">
-        <v>5214.601176576673</v>
+        <v>5262.106971795694</v>
       </c>
       <c r="C164" t="n">
-        <v>5052.372328324819</v>
+        <v>5093.912912573765</v>
       </c>
       <c r="D164" t="n">
-        <v>5385.541298819861</v>
+        <v>5438.483228055649</v>
       </c>
       <c r="E164" t="n">
-        <v>5179.78759765625</v>
+        <v>5357.2265625</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="B165" t="n">
-        <v>5219.746406620298</v>
+        <v>5252.770608140479</v>
       </c>
       <c r="C165" t="n">
-        <v>5062.828989949597</v>
+        <v>5084.559419866293</v>
       </c>
       <c r="D165" t="n">
-        <v>5381.062596431814</v>
+        <v>5419.486224284858</v>
       </c>
       <c r="E165" t="n">
-        <v>5196.6904296875</v>
+        <v>5144.81201171875</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46080</v>
+        <v>46085</v>
       </c>
       <c r="B166" t="n">
-        <v>5228.176453396662</v>
+        <v>5260.254795651321</v>
       </c>
       <c r="C166" t="n">
-        <v>5040.502831557616</v>
+        <v>5084.313165014072</v>
       </c>
       <c r="D166" t="n">
-        <v>5399.137401642704</v>
+        <v>5422.499876399183</v>
       </c>
       <c r="E166" t="n">
-        <v>5291.09228515625</v>
+        <v>5176.455078125</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46081</v>
+        <v>46086</v>
       </c>
       <c r="B167" t="n">
-        <v>5240.965928210644</v>
+        <v>5240.90300510009</v>
       </c>
       <c r="C167" t="n">
-        <v>5086.729003540501</v>
+        <v>5068.83709337963</v>
       </c>
       <c r="D167" t="n">
-        <v>5416.14302286124</v>
+        <v>5410.599506290767</v>
       </c>
       <c r="E167" t="n">
-        <v>5372.89599609375</v>
+        <v>5102.1650390625</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46082</v>
+        <v>46087</v>
       </c>
       <c r="B168" t="n">
-        <v>5245.14214620344</v>
+        <v>5219.003443106269</v>
       </c>
       <c r="C168" t="n">
-        <v>5079.203877123245</v>
+        <v>5064.76971611137</v>
       </c>
       <c r="D168" t="n">
-        <v>5418.36889986171</v>
+        <v>5391.63360605645</v>
       </c>
       <c r="E168" t="n">
-        <v>5435.98974609375</v>
+        <v>5180.2177734375</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46083</v>
+        <v>46088</v>
       </c>
       <c r="B169" t="n">
-        <v>5261.986463641984</v>
+        <v>5200.2133388937</v>
       </c>
       <c r="C169" t="n">
-        <v>5083.821342430119</v>
+        <v>5046.388252783252</v>
       </c>
       <c r="D169" t="n">
-        <v>5430.639109763146</v>
+        <v>5370.944756924364</v>
       </c>
       <c r="E169" t="n">
-        <v>5357.2265625</v>
+        <v>5174.09228515625</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46084</v>
+        <v>46089</v>
       </c>
       <c r="B170" t="n">
-        <v>5254.498178503613</v>
+        <v>5171.736008052562</v>
       </c>
       <c r="C170" t="n">
-        <v>5082.661684492316</v>
+        <v>4997.712644886216</v>
       </c>
       <c r="D170" t="n">
-        <v>5415.644926616896</v>
+        <v>5343.2339332112</v>
       </c>
       <c r="E170" t="n">
-        <v>5144.81201171875</v>
+        <v>5082.99365234375</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46085</v>
+        <v>46090</v>
       </c>
       <c r="B171" t="n">
-        <v>5262.94084969988</v>
+        <v>5156.40713251977</v>
       </c>
       <c r="C171" t="n">
-        <v>5084.913642609607</v>
+        <v>4996.336049208358</v>
       </c>
       <c r="D171" t="n">
-        <v>5441.867620221787</v>
+        <v>5343.460512850003</v>
       </c>
       <c r="E171" t="n">
-        <v>5176.455078125</v>
+        <v>5146.44091796875</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="B172" t="n">
-        <v>5240.820320717487</v>
+        <v>5115.259831845998</v>
       </c>
       <c r="C172" t="n">
-        <v>5077.803201220724</v>
+        <v>4946.528933662497</v>
       </c>
       <c r="D172" t="n">
-        <v>5406.546813184456</v>
+        <v>5275.489550798638</v>
       </c>
       <c r="E172" t="n">
-        <v>5102.1650390625</v>
+        <v>5195.64208984375</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="B173" t="n">
-        <v>5219.76902607283</v>
+        <v>5092.012969837137</v>
       </c>
       <c r="C173" t="n">
-        <v>5045.340600345266</v>
+        <v>4914.066703996787</v>
       </c>
       <c r="D173" t="n">
-        <v>5389.942120282913</v>
+        <v>5254.407821366389</v>
       </c>
       <c r="E173" t="n">
-        <v>5180.2177734375</v>
+        <v>5144.99365234375</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46088</v>
+        <v>46093</v>
       </c>
       <c r="B174" t="n">
-        <v>5201.439806449669</v>
+        <v>5043.676547068645</v>
       </c>
       <c r="C174" t="n">
-        <v>5022.8469421658</v>
+        <v>4869.505312499875</v>
       </c>
       <c r="D174" t="n">
-        <v>5384.590980957792</v>
+        <v>5234.175609960315</v>
       </c>
       <c r="E174" t="n">
-        <v>5174.09228515625</v>
+        <v>5111.07470703125</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46089</v>
+        <v>46094</v>
       </c>
       <c r="B175" t="n">
-        <v>5173.490275815291</v>
+        <v>4995.174035387676</v>
       </c>
       <c r="C175" t="n">
-        <v>5007.05032952161</v>
+        <v>4837.276912289642</v>
       </c>
       <c r="D175" t="n">
-        <v>5348.261052771883</v>
+        <v>5161.976137101903</v>
       </c>
       <c r="E175" t="n">
-        <v>5082.99365234375</v>
+        <v>5029.34423828125</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46090</v>
+        <v>46095</v>
       </c>
       <c r="B176" t="n">
-        <v>5157.868923227566</v>
+        <v>4952.750891245299</v>
       </c>
       <c r="C176" t="n">
-        <v>4977.421756454161</v>
+        <v>4778.064813647376</v>
       </c>
       <c r="D176" t="n">
-        <v>5324.452975441386</v>
+        <v>5131.30374304987</v>
       </c>
       <c r="E176" t="n">
-        <v>5146.44091796875</v>
+        <v>5021.23486328125</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46091</v>
+        <v>46096</v>
       </c>
       <c r="B177" t="n">
-        <v>5118.262727354587</v>
+        <v>4904.136974007532</v>
       </c>
       <c r="C177" t="n">
-        <v>4947.197638248085</v>
+        <v>4727.734925318061</v>
       </c>
       <c r="D177" t="n">
-        <v>5279.866795600266</v>
+        <v>5066.007314737892</v>
       </c>
       <c r="E177" t="n">
-        <v>5195.64208984375</v>
+        <v>4984.1162109375</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46092</v>
+        <v>46097</v>
       </c>
       <c r="B178" t="n">
-        <v>5095.626559268118</v>
+        <v>4872.619687517147</v>
       </c>
       <c r="C178" t="n">
-        <v>4927.077914269885</v>
+        <v>4694.66048293129</v>
       </c>
       <c r="D178" t="n">
-        <v>5266.023195823162</v>
+        <v>5048.483234309909</v>
       </c>
       <c r="E178" t="n">
-        <v>5144.99365234375</v>
+        <v>5000.9228515625</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46093</v>
+        <v>46098</v>
       </c>
       <c r="B179" t="n">
-        <v>5044.144097067217</v>
+        <v>4819.597760570779</v>
       </c>
       <c r="C179" t="n">
-        <v>4876.847963246971</v>
+        <v>4654.334558357189</v>
       </c>
       <c r="D179" t="n">
-        <v>5207.845744886057</v>
+        <v>4995.003180100562</v>
       </c>
       <c r="E179" t="n">
-        <v>5111.07470703125</v>
+        <v>4994.1279296875</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46094</v>
+        <v>46099</v>
       </c>
       <c r="B180" t="n">
-        <v>4996.095275590428</v>
+        <v>4789.060400390828</v>
       </c>
       <c r="C180" t="n">
-        <v>4821.27445270107</v>
+        <v>4621.199778714173</v>
       </c>
       <c r="D180" t="n">
-        <v>5174.419272059876</v>
+        <v>4951.961832742119</v>
       </c>
       <c r="E180" t="n">
-        <v>5029.34423828125</v>
+        <v>4827.228515625</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46095</v>
+        <v>46100</v>
       </c>
       <c r="B181" t="n">
-        <v>4953.733934962402</v>
+        <v>4738.185906429065</v>
       </c>
       <c r="C181" t="n">
-        <v>4787.463100813634</v>
+        <v>4575.055277191793</v>
       </c>
       <c r="D181" t="n">
-        <v>5126.465624468696</v>
+        <v>4913.696306158672</v>
       </c>
       <c r="E181" t="n">
-        <v>5021.23486328125</v>
+        <v>4654.67138671875</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46096</v>
+        <v>46101</v>
       </c>
       <c r="B182" t="n">
-        <v>4905.25713259</v>
+        <v>4691.959772929795</v>
       </c>
       <c r="C182" t="n">
-        <v>4735.41933497558</v>
+        <v>4516.750040705691</v>
       </c>
       <c r="D182" t="n">
-        <v>5072.568941836215</v>
+        <v>4851.334111963411</v>
       </c>
       <c r="E182" t="n">
-        <v>4984.1162109375</v>
+        <v>4509.33447265625</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46097</v>
+        <v>46102</v>
       </c>
       <c r="B183" t="n">
-        <v>4873.077693505968</v>
+        <v>4656.581623473804</v>
       </c>
       <c r="C183" t="n">
-        <v>4694.551792666667</v>
+        <v>4477.016144039854</v>
       </c>
       <c r="D183" t="n">
-        <v>5032.669408993667</v>
+        <v>4822.533981291665</v>
       </c>
       <c r="E183" t="n">
-        <v>5000.9228515625</v>
+        <v>4504.21630859375</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46098</v>
+        <v>46103</v>
       </c>
       <c r="B184" t="n">
-        <v>4821.260130053191</v>
+        <v>4619.628740356285</v>
       </c>
       <c r="C184" t="n">
-        <v>4654.032524380462</v>
+        <v>4446.213085636182</v>
       </c>
       <c r="D184" t="n">
-        <v>5001.626691702385</v>
+        <v>4793.249174290953</v>
       </c>
       <c r="E184" t="n">
-        <v>4994.1279296875</v>
+        <v>4471.259765625</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46099</v>
+        <v>46104</v>
       </c>
       <c r="B185" t="n">
-        <v>4791.040510677137</v>
+        <v>4604.132973558467</v>
       </c>
       <c r="C185" t="n">
-        <v>4614.442873718252</v>
+        <v>4429.37582788791</v>
       </c>
       <c r="D185" t="n">
-        <v>4956.307909617383</v>
+        <v>4778.519462488262</v>
       </c>
       <c r="E185" t="n">
-        <v>4827.228515625</v>
+        <v>4444.1826171875</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46100</v>
+        <v>46105</v>
       </c>
       <c r="B186" t="n">
-        <v>4736.780249130609</v>
+        <v>4571.140841280531</v>
       </c>
       <c r="C186" t="n">
-        <v>4565.196810695485</v>
+        <v>4394.160505763994</v>
       </c>
       <c r="D186" t="n">
-        <v>4907.216176435798</v>
+        <v>4734.564380965468</v>
       </c>
       <c r="E186" t="n">
-        <v>4654.67138671875</v>
+        <v>4548.10546875</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46101</v>
+        <v>46106</v>
       </c>
       <c r="B187" t="n">
-        <v>4690.829020757859</v>
+        <v>4564.201388256199</v>
       </c>
       <c r="C187" t="n">
-        <v>4519.597198211464</v>
+        <v>4393.117261781103</v>
       </c>
       <c r="D187" t="n">
-        <v>4860.979795677799</v>
+        <v>4738.912554899339</v>
       </c>
       <c r="E187" t="n">
-        <v>4509.33447265625</v>
+        <v>4499.9892578125</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46102</v>
+        <v>46107</v>
       </c>
       <c r="B188" t="n">
-        <v>4655.400585992004</v>
+        <v>4539.975656691647</v>
       </c>
       <c r="C188" t="n">
-        <v>4498.67392396233</v>
+        <v>4373.472097088229</v>
       </c>
       <c r="D188" t="n">
-        <v>4821.653733127099</v>
+        <v>4706.660816259512</v>
       </c>
       <c r="E188" t="n">
-        <v>4504.21630859375</v>
+        <v>4406.93994140625</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46103</v>
+        <v>46108</v>
       </c>
       <c r="B189" t="n">
-        <v>4618.543029846405</v>
+        <v>4522.86751272913</v>
       </c>
       <c r="C189" t="n">
-        <v>4464.381572937156</v>
+        <v>4359.386386940583</v>
       </c>
       <c r="D189" t="n">
-        <v>4798.722365513062</v>
+        <v>4703.938626285327</v>
       </c>
       <c r="E189" t="n">
-        <v>4471.259765625</v>
+        <v>4499.17333984375</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46104</v>
+        <v>46109</v>
       </c>
       <c r="B190" t="n">
-        <v>4602.414964602078</v>
+        <v>4518.444837175568</v>
       </c>
       <c r="C190" t="n">
-        <v>4429.313106171187</v>
+        <v>4356.48643811149</v>
       </c>
       <c r="D190" t="n">
-        <v>4766.386914049674</v>
+        <v>4709.885967779169</v>
       </c>
       <c r="E190" t="n">
-        <v>4444.1826171875</v>
+        <v>4497.9765625</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46105</v>
+        <v>46110</v>
       </c>
       <c r="B191" t="n">
-        <v>4570.727727167768</v>
+        <v>4513.618471884902</v>
       </c>
       <c r="C191" t="n">
-        <v>4398.97549864115</v>
+        <v>4340.746448803837</v>
       </c>
       <c r="D191" t="n">
-        <v>4726.085795528194</v>
+        <v>4673.653630294404</v>
       </c>
       <c r="E191" t="n">
-        <v>4548.10546875</v>
+        <v>4452.71044921875</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46106</v>
+        <v>46111</v>
       </c>
       <c r="B192" t="n">
-        <v>4564.27398308856</v>
+        <v>4530.735304872091</v>
       </c>
       <c r="C192" t="n">
-        <v>4389.188267289177</v>
+        <v>4358.072849873815</v>
       </c>
       <c r="D192" t="n">
-        <v>4738.191260573411</v>
+        <v>4698.817740497984</v>
       </c>
       <c r="E192" t="n">
-        <v>4499.9892578125</v>
+        <v>4507.97314453125</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="B193" t="n">
-        <v>4536.892476421621</v>
+        <v>4530.154888146112</v>
       </c>
       <c r="C193" t="n">
-        <v>4363.598494246233</v>
+        <v>4358.123718673933</v>
       </c>
       <c r="D193" t="n">
-        <v>4724.503863661687</v>
+        <v>4701.572846991286</v>
       </c>
       <c r="E193" t="n">
-        <v>4406.93994140625</v>
+        <v>4683.30615234375</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="B194" t="n">
-        <v>4520.343842540509</v>
+        <v>4554.753729507622</v>
       </c>
       <c r="C194" t="n">
-        <v>4350.606638079514</v>
+        <v>4396.039396002511</v>
       </c>
       <c r="D194" t="n">
-        <v>4692.327290652293</v>
+        <v>4725.626520117901</v>
       </c>
       <c r="E194" t="n">
-        <v>4499.17333984375</v>
+        <v>4767.40576171875</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46109</v>
+        <v>46114</v>
       </c>
       <c r="B195" t="n">
-        <v>4516.200924655754</v>
+        <v>4560.550693137774</v>
       </c>
       <c r="C195" t="n">
-        <v>4329.284980755664</v>
+        <v>4392.323852474959</v>
       </c>
       <c r="D195" t="n">
-        <v>4687.231646578345</v>
+        <v>4732.184644118898</v>
       </c>
       <c r="E195" t="n">
-        <v>4497.9765625</v>
+        <v>4668.07666015625</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46110</v>
+        <v>46115</v>
       </c>
       <c r="B196" t="n">
-        <v>4511.83472300892</v>
+        <v>4571.352847760752</v>
       </c>
       <c r="C196" t="n">
-        <v>4336.821108396872</v>
+        <v>4408.287982576584</v>
       </c>
       <c r="D196" t="n">
-        <v>4685.673882479366</v>
+        <v>4744.202723061881</v>
       </c>
       <c r="E196" t="n">
-        <v>4452.71044921875</v>
+        <v>4648.1611328125</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46111</v>
+        <v>46116</v>
       </c>
       <c r="B197" t="n">
-        <v>4528.707113789611</v>
+        <v>4592.19039416277</v>
       </c>
       <c r="C197" t="n">
-        <v>4352.918013583164</v>
+        <v>4425.919413495172</v>
       </c>
       <c r="D197" t="n">
-        <v>4711.821103526208</v>
+        <v>4756.158616247478</v>
       </c>
       <c r="E197" t="n">
-        <v>4507.97314453125</v>
+        <v>4649.1181640625</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46112</v>
+        <v>46117</v>
       </c>
       <c r="B198" t="n">
-        <v>4529.829940253106</v>
+        <v>4609.507721631762</v>
       </c>
       <c r="C198" t="n">
-        <v>4373.690064856034</v>
+        <v>4425.359820963205</v>
       </c>
       <c r="D198" t="n">
-        <v>4692.94991053618</v>
+        <v>4776.098275999802</v>
       </c>
       <c r="E198" t="n">
-        <v>4683.30615234375</v>
+        <v>4601.5048828125</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B199" t="n">
-        <v>4555.310451010809</v>
+        <v>4645.266681646294</v>
       </c>
       <c r="C199" t="n">
-        <v>4383.823742477703</v>
+        <v>4473.516951664666</v>
       </c>
       <c r="D199" t="n">
-        <v>4733.581225983522</v>
+        <v>4811.365689438427</v>
       </c>
       <c r="E199" t="n">
-        <v>4767.40576171875</v>
+        <v>4643.5390625</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B200" t="n">
-        <v>4558.332392085946</v>
+        <v>4659.531229531503</v>
       </c>
       <c r="C200" t="n">
-        <v>4385.520431887721</v>
+        <v>4485.906063224518</v>
       </c>
       <c r="D200" t="n">
-        <v>4740.11939318571</v>
+        <v>4824.666234774928</v>
       </c>
       <c r="E200" t="n">
-        <v>4668.07666015625</v>
+        <v>4794.943359375</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46115</v>
+        <v>46120</v>
       </c>
       <c r="B201" t="n">
-        <v>4570.047252401626</v>
+        <v>4694.977391405369</v>
       </c>
       <c r="C201" t="n">
-        <v>4402.477938775845</v>
+        <v>4521.964697015345</v>
       </c>
       <c r="D201" t="n">
-        <v>4746.996484183692</v>
+        <v>4878.254450079743</v>
       </c>
       <c r="E201" t="n">
-        <v>4648.1611328125</v>
+        <v>4700.63037109375</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46116</v>
+        <v>46121</v>
       </c>
       <c r="B202" t="n">
-        <v>4591.478714291254</v>
+        <v>4707.521870933263</v>
       </c>
       <c r="C202" t="n">
-        <v>4413.41763141889</v>
+        <v>4526.044881128705</v>
       </c>
       <c r="D202" t="n">
-        <v>4763.714853224558</v>
+        <v>4871.203209331648</v>
       </c>
       <c r="E202" t="n">
-        <v>4649.1181640625</v>
+        <v>4747.31787109375</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46117</v>
+        <v>46122</v>
       </c>
       <c r="B203" t="n">
-        <v>4609.521081889357</v>
+        <v>4720.96857937235</v>
       </c>
       <c r="C203" t="n">
-        <v>4441.296216365352</v>
+        <v>4553.736586199001</v>
       </c>
       <c r="D203" t="n">
-        <v>4798.254670609213</v>
+        <v>4896.486099947506</v>
       </c>
       <c r="E203" t="n">
-        <v>4601.5048828125</v>
+        <v>4735.64111328125</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46118</v>
+        <v>46123</v>
       </c>
       <c r="B204" t="n">
-        <v>4645.242519562832</v>
+        <v>4740.441733586335</v>
       </c>
       <c r="C204" t="n">
-        <v>4467.604342314859</v>
+        <v>4563.482238934173</v>
       </c>
       <c r="D204" t="n">
-        <v>4826.939940864828</v>
+        <v>4922.026263917744</v>
       </c>
       <c r="E204" t="n">
-        <v>4643.5390625</v>
+        <v>4733.71923828125</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46119</v>
+        <v>46124</v>
       </c>
       <c r="B205" t="n">
-        <v>4661.352448186925</v>
+        <v>4752.572649459597</v>
       </c>
       <c r="C205" t="n">
-        <v>4479.95251204442</v>
+        <v>4578.888533434622</v>
       </c>
       <c r="D205" t="n">
-        <v>4827.406488181686</v>
+        <v>4919.659094782721</v>
       </c>
       <c r="E205" t="n">
-        <v>4794.943359375</v>
+        <v>4652.7919921875</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c r="B206" t="n">
-        <v>4697.752881512455</v>
+        <v>4779.596460552872</v>
       </c>
       <c r="C206" t="n">
-        <v>4534.259240038484</v>
+        <v>4600.983803223951</v>
       </c>
       <c r="D206" t="n">
-        <v>4865.963349185252</v>
+        <v>4943.845405394629</v>
       </c>
       <c r="E206" t="n">
-        <v>4700.63037109375</v>
+        <v>4742.3955078125</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46121</v>
+        <v>46126</v>
       </c>
       <c r="B207" t="n">
-        <v>4707.522881374967</v>
+        <v>4781.928113027592</v>
       </c>
       <c r="C207" t="n">
-        <v>4542.615500366786</v>
+        <v>4618.795316899498</v>
       </c>
       <c r="D207" t="n">
-        <v>4879.635002929502</v>
+        <v>4941.148780400843</v>
       </c>
       <c r="E207" t="n">
-        <v>4747.31787109375</v>
+        <v>4828.4228515625</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46122</v>
+        <v>46127</v>
       </c>
       <c r="B208" t="n">
-        <v>4721.810571887455</v>
+        <v>4802.661847460169</v>
       </c>
       <c r="C208" t="n">
-        <v>4546.844316216768</v>
+        <v>4623.991060111548</v>
       </c>
       <c r="D208" t="n">
-        <v>4897.447580651111</v>
+        <v>4972.885816118436</v>
       </c>
       <c r="E208" t="n">
-        <v>4735.64111328125</v>
+        <v>4812.73828125</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46123</v>
+        <v>46128</v>
       </c>
       <c r="B209" t="n">
-        <v>4741.735772259615</v>
+        <v>4798.187780560918</v>
       </c>
       <c r="C209" t="n">
-        <v>4571.483677410516</v>
+        <v>4625.263547851843</v>
       </c>
       <c r="D209" t="n">
-        <v>4909.757386913921</v>
+        <v>4966.037739926076</v>
       </c>
       <c r="E209" t="n">
-        <v>4733.71923828125</v>
+        <v>4777.44384765625</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46124</v>
+        <v>46129</v>
       </c>
       <c r="B210" t="n">
-        <v>4754.384101256001</v>
+        <v>4792.825206873691</v>
       </c>
       <c r="C210" t="n">
-        <v>4585.224289396162</v>
+        <v>4601.703623338961</v>
       </c>
       <c r="D210" t="n">
-        <v>4931.864720704542</v>
+        <v>4969.691650721624</v>
       </c>
       <c r="E210" t="n">
-        <v>4652.7919921875</v>
+        <v>4821.47607421875</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46125</v>
+        <v>46130</v>
       </c>
       <c r="B211" t="n">
-        <v>4781.103526118912</v>
+        <v>4792.241628100792</v>
       </c>
       <c r="C211" t="n">
-        <v>4636.358278989372</v>
+        <v>4623.221118863999</v>
       </c>
       <c r="D211" t="n">
-        <v>4948.891223881405</v>
+        <v>4956.636613961208</v>
       </c>
       <c r="E211" t="n">
-        <v>4742.3955078125</v>
+        <v>4777.1845703125</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46126</v>
+        <v>46131</v>
       </c>
       <c r="B212" t="n">
-        <v>4784.96290940506</v>
+        <v>4783.625019052804</v>
       </c>
       <c r="C212" t="n">
-        <v>4605.302911158356</v>
+        <v>4612.974864294482</v>
       </c>
       <c r="D212" t="n">
-        <v>4958.025239167818</v>
+        <v>4954.841159511315</v>
       </c>
       <c r="E212" t="n">
-        <v>4828.4228515625</v>
+        <v>4738.798828125</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46127</v>
+        <v>46132</v>
       </c>
       <c r="B213" t="n">
-        <v>4806.292595074972</v>
+        <v>4789.766035012652</v>
       </c>
       <c r="C213" t="n">
-        <v>4629.174380128204</v>
+        <v>4624.259954651882</v>
       </c>
       <c r="D213" t="n">
-        <v>4977.011353490322</v>
+        <v>4958.749494088304</v>
       </c>
       <c r="E213" t="n">
-        <v>4812.73828125</v>
+        <v>4807.7041015625</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46128</v>
+        <v>46133</v>
       </c>
       <c r="B214" t="n">
-        <v>4798.656520269463</v>
+        <v>4771.619463545396</v>
       </c>
       <c r="C214" t="n">
-        <v>4633.582143098645</v>
+        <v>4594.87238800217</v>
       </c>
       <c r="D214" t="n">
-        <v>4961.921697367188</v>
+        <v>4947.628621985275</v>
       </c>
       <c r="E214" t="n">
-        <v>4777.44384765625</v>
+        <v>4729.26611328125</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B215" t="n">
-        <v>4793.730637553814</v>
+        <v>4772.790368760207</v>
       </c>
       <c r="C215" t="n">
-        <v>4630.758963860814</v>
+        <v>4606.952725037162</v>
       </c>
       <c r="D215" t="n">
-        <v>4959.911936858222</v>
+        <v>4941.414586324414</v>
       </c>
       <c r="E215" t="n">
-        <v>4821.47607421875</v>
+        <v>4714.892578125</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46130</v>
+        <v>46135</v>
       </c>
       <c r="B216" t="n">
-        <v>4793.191083542119</v>
+        <v>4750.138022758709</v>
       </c>
       <c r="C216" t="n">
-        <v>4631.142749201915</v>
+        <v>4583.427409101844</v>
       </c>
       <c r="D216" t="n">
-        <v>4982.003366635642</v>
+        <v>4932.092374117846</v>
       </c>
       <c r="E216" t="n">
-        <v>4777.1845703125</v>
+        <v>4687.91357421875</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46131</v>
+        <v>46136</v>
       </c>
       <c r="B217" t="n">
-        <v>4784.693339985245</v>
+        <v>4728.397992499914</v>
       </c>
       <c r="C217" t="n">
-        <v>4625.752305236362</v>
+        <v>4559.571029860617</v>
       </c>
       <c r="D217" t="n">
-        <v>4948.887839660135</v>
+        <v>4901.603848511634</v>
       </c>
       <c r="E217" t="n">
-        <v>4738.798828125</v>
+        <v>4697.42529296875</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46132</v>
+        <v>46137</v>
       </c>
       <c r="B218" t="n">
-        <v>4790.153761824093</v>
+        <v>4713.59157749795</v>
       </c>
       <c r="C218" t="n">
-        <v>4625.051665155976</v>
+        <v>4543.646086162345</v>
       </c>
       <c r="D218" t="n">
-        <v>4963.404917340203</v>
+        <v>4893.482758170047</v>
       </c>
       <c r="E218" t="n">
-        <v>4807.7041015625</v>
+        <v>4692.419921875</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46133</v>
+        <v>46138</v>
       </c>
       <c r="B219" t="n">
-        <v>4773.19342410327</v>
+        <v>4693.190334089175</v>
       </c>
       <c r="C219" t="n">
-        <v>4610.983002112018</v>
+        <v>4527.538347970903</v>
       </c>
       <c r="D219" t="n">
-        <v>4949.721140725738</v>
+        <v>4867.98043539883</v>
       </c>
       <c r="E219" t="n">
-        <v>4729.26611328125</v>
+        <v>4675.0712890625</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46134</v>
+        <v>46139</v>
       </c>
       <c r="B220" t="n">
-        <v>4774.664713803499</v>
+        <v>4690.192478034193</v>
       </c>
       <c r="C220" t="n">
-        <v>4609.916541813002</v>
+        <v>4526.793943083361</v>
       </c>
       <c r="D220" t="n">
-        <v>4959.242439022961</v>
+        <v>4866.825848500914</v>
       </c>
       <c r="E220" t="n">
-        <v>4714.892578125</v>
+        <v>4684.798828125</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46135</v>
+        <v>46140</v>
       </c>
       <c r="B221" t="n">
-        <v>4748.610512870096</v>
+        <v>4665.68101796698</v>
       </c>
       <c r="C221" t="n">
-        <v>4581.148540602867</v>
+        <v>4499.11604881236</v>
       </c>
       <c r="D221" t="n">
-        <v>4916.996010585466</v>
+        <v>4843.376227200286</v>
       </c>
       <c r="E221" t="n">
-        <v>4687.91357421875</v>
+        <v>4586.419921875</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="B222" t="n">
-        <v>4727.131085327828</v>
+        <v>4663.308258582408</v>
       </c>
       <c r="C222" t="n">
-        <v>4557.02625404261</v>
+        <v>4498.929279210396</v>
       </c>
       <c r="D222" t="n">
-        <v>4891.35916409561</v>
+        <v>4842.920141216593</v>
       </c>
       <c r="E222" t="n">
-        <v>4697.42529296875</v>
+        <v>4551.4296875</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46137</v>
+        <v>46142</v>
       </c>
       <c r="B223" t="n">
-        <v>4712.262387898668</v>
+        <v>4639.900631082548</v>
       </c>
       <c r="C223" t="n">
-        <v>4539.941763179321</v>
+        <v>4464.803309718762</v>
       </c>
       <c r="D223" t="n">
-        <v>4881.620464681912</v>
+        <v>4797.335753591338</v>
       </c>
       <c r="E223" t="n">
-        <v>4692.419921875</v>
+        <v>4618.77001953125</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46138</v>
+        <v>46143</v>
       </c>
       <c r="B224" t="n">
-        <v>4691.947286321362</v>
+        <v>4620.083723573066</v>
       </c>
       <c r="C224" t="n">
-        <v>4516.156401499535</v>
+        <v>4444.492479931278</v>
       </c>
       <c r="D224" t="n">
-        <v>4865.152705826817</v>
+        <v>4789.623539955147</v>
       </c>
       <c r="E224" t="n">
-        <v>4675.0712890625</v>
+        <v>4604.0791015625</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46139</v>
+        <v>46144</v>
       </c>
       <c r="B225" t="n">
-        <v>4688.311231875351</v>
+        <v>4609.696674124802</v>
       </c>
       <c r="C225" t="n">
-        <v>4515.629458984047</v>
+        <v>4449.432809722015</v>
       </c>
       <c r="D225" t="n">
-        <v>4858.898871535708</v>
+        <v>4785.273556687399</v>
       </c>
       <c r="E225" t="n">
-        <v>4684.798828125</v>
+        <v>4597.361328125</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46140</v>
+        <v>46145</v>
       </c>
       <c r="B226" t="n">
-        <v>4665.102471445883</v>
+        <v>4595.963490624398</v>
       </c>
       <c r="C226" t="n">
-        <v>4506.035684235008</v>
+        <v>4432.436183821338</v>
       </c>
       <c r="D226" t="n">
-        <v>4836.473119673798</v>
+        <v>4745.591165819559</v>
       </c>
       <c r="E226" t="n">
-        <v>4586.419921875</v>
+        <v>4607.44873046875</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46141</v>
+        <v>46146</v>
       </c>
       <c r="B227" t="n">
-        <v>4663.217275957238</v>
+        <v>4601.577870103941</v>
       </c>
       <c r="C227" t="n">
-        <v>4492.183287669944</v>
+        <v>4416.388617767732</v>
       </c>
       <c r="D227" t="n">
-        <v>4840.474834707082</v>
+        <v>4761.662370886845</v>
       </c>
       <c r="E227" t="n">
-        <v>4551.4296875</v>
+        <v>4515.73046875</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46142</v>
+        <v>46147</v>
       </c>
       <c r="B228" t="n">
-        <v>4636.660030218686</v>
+        <v>4587.271110892038</v>
       </c>
       <c r="C228" t="n">
-        <v>4461.807388319154</v>
+        <v>4410.791246189982</v>
       </c>
       <c r="D228" t="n">
-        <v>4820.033263966431</v>
+        <v>4756.450440839975</v>
       </c>
       <c r="E228" t="n">
-        <v>4618.77001953125</v>
+        <v>4583.22998046875</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46143</v>
+        <v>46148</v>
       </c>
       <c r="B229" t="n">
-        <v>4617.413231911665</v>
+        <v>4596.307464568274</v>
       </c>
       <c r="C229" t="n">
-        <v>4446.944526474666</v>
+        <v>4423.03007788851</v>
       </c>
       <c r="D229" t="n">
-        <v>4791.393843052741</v>
+        <v>4764.832618065439</v>
       </c>
       <c r="E229" t="n">
-        <v>4604.0791015625</v>
+        <v>4685.2685546875</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46144</v>
+        <v>46149</v>
       </c>
       <c r="B230" t="n">
-        <v>4607.320994981063</v>
+        <v>4585.100569251733</v>
       </c>
       <c r="C230" t="n">
-        <v>4449.701980183373</v>
+        <v>4413.5545999692</v>
       </c>
       <c r="D230" t="n">
-        <v>4784.194463344244</v>
+        <v>4762.998684714968</v>
       </c>
       <c r="E230" t="n">
-        <v>4597.361328125</v>
+        <v>4695.97412109375</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46145</v>
+        <v>46150</v>
       </c>
       <c r="B231" t="n">
-        <v>4594.067360639533</v>
+        <v>4577.850505891388</v>
       </c>
       <c r="C231" t="n">
-        <v>4429.485828070595</v>
+        <v>4405.346691877044</v>
       </c>
       <c r="D231" t="n">
-        <v>4768.206677501727</v>
+        <v>4745.634138977367</v>
       </c>
       <c r="E231" t="n">
-        <v>4607.44873046875</v>
+        <v>4706.30517578125</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46146</v>
+        <v>46151</v>
       </c>
       <c r="B232" t="n">
-        <v>4599.460742664338</v>
+        <v>4579.970303710988</v>
       </c>
       <c r="C232" t="n">
-        <v>4424.605612273656</v>
+        <v>4407.475902478959</v>
       </c>
       <c r="D232" t="n">
-        <v>4774.594426393938</v>
+        <v>4758.023530449238</v>
       </c>
       <c r="E232" t="n">
-        <v>4515.73046875</v>
+        <v>4711.15576171875</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46147</v>
+        <v>46152</v>
       </c>
       <c r="B233" t="n">
-        <v>4586.884309785508</v>
+        <v>4578.269125818035</v>
       </c>
       <c r="C233" t="n">
-        <v>4411.83870723349</v>
+        <v>4413.079762188337</v>
       </c>
       <c r="D233" t="n">
-        <v>4757.344736467888</v>
+        <v>4741.965828264024</v>
       </c>
       <c r="E233" t="n">
-        <v>4583.22998046875</v>
+        <v>4689.40771484375</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="B234" t="n">
-        <v>4596.832486270021</v>
+        <v>4595.048387800031</v>
       </c>
       <c r="C234" t="n">
-        <v>4427.357830251143</v>
+        <v>4438.613913764735</v>
       </c>
       <c r="D234" t="n">
-        <v>4761.759524742186</v>
+        <v>4773.262610604964</v>
       </c>
       <c r="E234" t="n">
-        <v>4685.2685546875</v>
+        <v>4754.81640625</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46149</v>
+        <v>46154</v>
       </c>
       <c r="B235" t="n">
-        <v>4582.883084295003</v>
+        <v>4590.680104012785</v>
       </c>
       <c r="C235" t="n">
-        <v>4417.328096625253</v>
+        <v>4415.356017460253</v>
       </c>
       <c r="D235" t="n">
-        <v>4749.70458890904</v>
+        <v>4757.948918086455</v>
       </c>
       <c r="E235" t="n">
-        <v>4695.97412109375</v>
+        <v>4711.0009765625</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46150</v>
+        <v>46155</v>
       </c>
       <c r="B236" t="n">
-        <v>4576.579770942037</v>
+        <v>4608.111539414365</v>
       </c>
       <c r="C236" t="n">
-        <v>4420.8659909193</v>
+        <v>4436.738251435447</v>
       </c>
       <c r="D236" t="n">
-        <v>4741.266112071354</v>
+        <v>4780.056288356716</v>
       </c>
       <c r="E236" t="n">
-        <v>4706.30517578125</v>
+        <v>4685.81005859375</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46151</v>
+        <v>46156</v>
       </c>
       <c r="B237" t="n">
-        <v>4579.328114797704</v>
+        <v>4603.489575878382</v>
       </c>
       <c r="C237" t="n">
-        <v>4397.671014489381</v>
+        <v>4434.813728640335</v>
       </c>
       <c r="D237" t="n">
-        <v>4755.523400706164</v>
+        <v>4772.802358623677</v>
       </c>
       <c r="E237" t="n">
-        <v>4711.15576171875</v>
+        <v>4647.783203125</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46152</v>
+        <v>46157</v>
       </c>
       <c r="B238" t="n">
-        <v>4578.386167899166</v>
+        <v>4600.80414387326</v>
       </c>
       <c r="C238" t="n">
-        <v>4411.970740508464</v>
+        <v>4440.092911736491</v>
       </c>
       <c r="D238" t="n">
-        <v>4748.589636025018</v>
+        <v>4775.474520048386</v>
       </c>
       <c r="E238" t="n">
-        <v>4689.40771484375</v>
+        <v>4540.41552734375</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46153</v>
+        <v>46158</v>
       </c>
       <c r="B239" t="n">
-        <v>4595.16057740577</v>
+        <v>4605.319402212755</v>
       </c>
       <c r="C239" t="n">
-        <v>4428.653741532594</v>
+        <v>4432.417247015786</v>
       </c>
       <c r="D239" t="n">
-        <v>4759.775034870815</v>
+        <v>4782.537080857399</v>
       </c>
       <c r="E239" t="n">
-        <v>4754.81640625</v>
+        <v>4535.490234375</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46154</v>
+        <v>46159</v>
       </c>
       <c r="B240" t="n">
-        <v>4592.667718933466</v>
+        <v>4603.75980299661</v>
       </c>
       <c r="C240" t="n">
-        <v>4427.329542839072</v>
+        <v>4425.878136735637</v>
       </c>
       <c r="D240" t="n">
-        <v>4759.455360530093</v>
+        <v>4774.203649098292</v>
       </c>
       <c r="E240" t="n">
-        <v>4711.0009765625</v>
+        <v>4534.8125</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="B241" t="n">
-        <v>4611.079753199437</v>
+        <v>4618.407252521208</v>
       </c>
       <c r="C241" t="n">
-        <v>4447.644013941306</v>
+        <v>4447.325999248167</v>
       </c>
       <c r="D241" t="n">
-        <v>4794.09615180763</v>
+        <v>4791.014077951049</v>
       </c>
       <c r="E241" t="n">
-        <v>4685.81005859375</v>
+        <v>4574.75048828125</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46156</v>
+        <v>46161</v>
       </c>
       <c r="B242" t="n">
-        <v>4603.70487825814</v>
+        <v>4609.678672726786</v>
       </c>
       <c r="C242" t="n">
-        <v>4433.703164046736</v>
+        <v>4436.358038853729</v>
       </c>
       <c r="D242" t="n">
-        <v>4774.356675277552</v>
+        <v>4779.194410114341</v>
       </c>
       <c r="E242" t="n">
-        <v>4647.783203125</v>
+        <v>4491.31494140625</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="B243" t="n">
-        <v>4601.876283277381</v>
+        <v>4620.628101618866</v>
       </c>
       <c r="C243" t="n">
-        <v>4437.154573749934</v>
+        <v>4449.20911934647</v>
       </c>
       <c r="D243" t="n">
-        <v>4776.153173145655</v>
+        <v>4799.162035746401</v>
       </c>
       <c r="E243" t="n">
-        <v>4540.41552734375</v>
+        <v>4535.93505859375</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46158</v>
+        <v>46163</v>
       </c>
       <c r="B244" t="n">
-        <v>4606.852900604185</v>
+        <v>4607.56685008693</v>
       </c>
       <c r="C244" t="n">
-        <v>4428.775323417804</v>
+        <v>4438.041765609863</v>
       </c>
       <c r="D244" t="n">
-        <v>4781.032497971003</v>
+        <v>4779.990991031314</v>
       </c>
       <c r="E244" t="n">
-        <v>4535.490234375</v>
+        <v>4524.57861328125</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46159</v>
+        <v>46164</v>
       </c>
       <c r="B245" t="n">
-        <v>4605.812817271183</v>
+        <v>4594.701219021296</v>
       </c>
       <c r="C245" t="n">
-        <v>4429.133865441727</v>
+        <v>4430.244385415873</v>
       </c>
       <c r="D245" t="n">
-        <v>4767.917829468844</v>
+        <v>4748.684771661352</v>
       </c>
       <c r="E245" t="n">
-        <v>4534.8125</v>
+        <v>4494.931640625</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46160</v>
+        <v>46165</v>
       </c>
       <c r="B246" t="n">
-        <v>4620.150298382708</v>
+        <v>4587.556650890694</v>
       </c>
       <c r="C246" t="n">
-        <v>4439.128033888111</v>
+        <v>4409.455321555621</v>
       </c>
       <c r="D246" t="n">
-        <v>4793.305656939016</v>
+        <v>4772.534141529271</v>
       </c>
       <c r="E246" t="n">
-        <v>4574.75048828125</v>
+        <v>4522.34521484375</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46161</v>
+        <v>46166</v>
       </c>
       <c r="B247" t="n">
-        <v>4612.935927967132</v>
+        <v>4573.155677687115</v>
       </c>
       <c r="C247" t="n">
-        <v>4447.354111023702</v>
+        <v>4412.189638732344</v>
       </c>
       <c r="D247" t="n">
-        <v>4806.356669795621</v>
+        <v>4752.613332600284</v>
       </c>
       <c r="E247" t="n">
-        <v>4491.31494140625</v>
+        <v>4562.1640625</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="B248" t="n">
-        <v>4624.459835751843</v>
+        <v>4574.106126042845</v>
       </c>
       <c r="C248" t="n">
-        <v>4458.117369408981</v>
+        <v>4407.236320675936</v>
       </c>
       <c r="D248" t="n">
-        <v>4806.040513588571</v>
+        <v>4757.425566690442</v>
       </c>
       <c r="E248" t="n">
-        <v>4535.93505859375</v>
+        <v>4548.4677734375</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="B249" t="n">
-        <v>4608.207398177543</v>
+        <v>4551.169153632431</v>
       </c>
       <c r="C249" t="n">
-        <v>4430.239913324553</v>
+        <v>4391.531665870441</v>
       </c>
       <c r="D249" t="n">
-        <v>4786.076535459561</v>
+        <v>4730.074265435743</v>
       </c>
       <c r="E249" t="n">
-        <v>4524.57861328125</v>
+        <v>4515.7841796875</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B250" t="n">
-        <v>4595.742083418777</v>
+        <v>4547.751533574026</v>
       </c>
       <c r="C250" t="n">
-        <v>4431.829516036944</v>
+        <v>4378.536071174789</v>
       </c>
       <c r="D250" t="n">
-        <v>4766.888406749724</v>
+        <v>4727.72504015472</v>
       </c>
       <c r="E250" t="n">
-        <v>4494.931640625</v>
+        <v>4443.1279296875</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46165</v>
+        <v>46170</v>
       </c>
       <c r="B251" t="n">
-        <v>4588.598740502625</v>
+        <v>4520.515985948683</v>
       </c>
       <c r="C251" t="n">
-        <v>4416.853583713299</v>
+        <v>4340.035624158485</v>
       </c>
       <c r="D251" t="n">
-        <v>4770.060142346718</v>
+        <v>4702.483399557234</v>
       </c>
       <c r="E251" t="n">
-        <v>4522.34521484375</v>
+        <v>4480.20751953125</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46166</v>
+        <v>46171</v>
       </c>
       <c r="B252" t="n">
-        <v>4574.268431727717</v>
+        <v>4494.009335738654</v>
       </c>
       <c r="C252" t="n">
-        <v>4404.20120714261</v>
+        <v>4303.0525836075</v>
       </c>
       <c r="D252" t="n">
-        <v>4737.106814788587</v>
+        <v>4662.90509839021</v>
       </c>
       <c r="E252" t="n">
-        <v>4562.1640625</v>
+        <v>4529.62451171875</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
-        <v>46167</v>
+        <v>46172</v>
       </c>
       <c r="B253" t="n">
-        <v>4574.486025653905</v>
+        <v>4474.077633299575</v>
       </c>
       <c r="C253" t="n">
-        <v>4401.757810182156</v>
+        <v>4302.00062112445</v>
       </c>
       <c r="D253" t="n">
-        <v>4736.984764226874</v>
+        <v>4655.419765688659</v>
       </c>
       <c r="E253" t="n">
-        <v>4548.4677734375</v>
+        <v>4517.13134765625</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
-        <v>46168</v>
+        <v>46173</v>
       </c>
       <c r="B254" t="n">
-        <v>4552.680339985391</v>
+        <v>4448.035840430027</v>
       </c>
       <c r="C254" t="n">
-        <v>4378.853396817986</v>
+        <v>4270.6148412011</v>
       </c>
       <c r="D254" t="n">
-        <v>4720.987496738354</v>
+        <v>4622.562885437088</v>
       </c>
       <c r="E254" t="n">
-        <v>4515.7841796875</v>
+        <v>4530.79296875</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
-        <v>46169</v>
+        <v>46174</v>
       </c>
       <c r="B255" t="n">
-        <v>4549.507096465145</v>
+        <v>4438.748757312074</v>
       </c>
       <c r="C255" t="n">
-        <v>4371.794813760662</v>
+        <v>4270.247532158042</v>
       </c>
       <c r="D255" t="n">
-        <v>4723.660853110782</v>
+        <v>4607.331103818406</v>
       </c>
       <c r="E255" t="n">
-        <v>4443.1279296875</v>
+        <v>4475.79248046875</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
-        <v>46170</v>
+        <v>46175</v>
       </c>
       <c r="B256" t="n">
-        <v>4518.814372791</v>
+        <v>4407.19294498352</v>
       </c>
       <c r="C256" t="n">
-        <v>4358.586201222575</v>
+        <v>4242.90653683586</v>
       </c>
       <c r="D256" t="n">
-        <v>4680.452390463968</v>
+        <v>4588.887377836746</v>
       </c>
       <c r="E256" t="n">
-        <v>4480.20751953125</v>
+        <v>4463.0302734375</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B257" t="n">
-        <v>4492.515509728613</v>
+        <v>4396.944204980899</v>
       </c>
       <c r="C257" t="n">
-        <v>4312.946434716424</v>
+        <v>4219.480506313053</v>
       </c>
       <c r="D257" t="n">
-        <v>4670.580316582461</v>
+        <v>4562.753721339865</v>
       </c>
       <c r="E257" t="n">
-        <v>4529.62451171875</v>
+        <v>4448.11572265625</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
-        <v>46172</v>
+        <v>46177</v>
       </c>
       <c r="B258" t="n">
-        <v>4472.473048314153</v>
+        <v>4364.784518433202</v>
       </c>
       <c r="C258" t="n">
-        <v>4298.363937012819</v>
+        <v>4189.006462298246</v>
       </c>
       <c r="D258" t="n">
-        <v>4649.454919473784</v>
+        <v>4548.610215500515</v>
       </c>
       <c r="E258" t="n">
-        <v>4517.13134765625</v>
+        <v>4453.0693359375</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
-        <v>46173</v>
+        <v>46178</v>
       </c>
       <c r="B259" t="n">
-        <v>4446.475048400186</v>
+        <v>4335.328284942787</v>
       </c>
       <c r="C259" t="n">
-        <v>4272.890133673224</v>
+        <v>4165.886360848519</v>
       </c>
       <c r="D259" t="n">
-        <v>4610.902709430044</v>
+        <v>4502.38400694654</v>
       </c>
       <c r="E259" t="n">
-        <v>4530.79296875</v>
+        <v>4320.01220703125</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
-        <v>46174</v>
+        <v>46179</v>
       </c>
       <c r="B260" t="n">
-        <v>4436.515227868944</v>
+        <v>4314.437014432029</v>
       </c>
       <c r="C260" t="n">
-        <v>4277.752661992758</v>
+        <v>4137.087966403698</v>
       </c>
       <c r="D260" t="n">
-        <v>4600.520218339514</v>
+        <v>4487.303833213853</v>
       </c>
       <c r="E260" t="n">
-        <v>4475.79248046875</v>
+        <v>4296.80859375</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
-        <v>46175</v>
+        <v>46180</v>
       </c>
       <c r="B261" t="n">
-        <v>4406.236900991892</v>
+        <v>4289.390050027612</v>
       </c>
       <c r="C261" t="n">
-        <v>4235.179578435012</v>
+        <v>4128.848521565432</v>
       </c>
       <c r="D261" t="n">
-        <v>4583.388992814257</v>
+        <v>4455.468661351042</v>
       </c>
       <c r="E261" t="n">
-        <v>4463.0302734375</v>
+        <v>4334.697265625</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
-        <v>46176</v>
+        <v>46181</v>
       </c>
       <c r="B262" t="n">
-        <v>4396.461124545807</v>
+        <v>4282.967929591214</v>
       </c>
       <c r="C262" t="n">
-        <v>4221.544138271702</v>
+        <v>4116.752856945172</v>
       </c>
       <c r="D262" t="n">
-        <v>4563.012557194626</v>
+        <v>4449.365893460537</v>
       </c>
       <c r="E262" t="n">
-        <v>4448.11572265625</v>
+        <v>4308.56982421875</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
-        <v>46177</v>
+        <v>46182</v>
       </c>
       <c r="B263" t="n">
-        <v>4361.148842080403</v>
+        <v>4256.018035392991</v>
       </c>
       <c r="C263" t="n">
-        <v>4194.474853020055</v>
+        <v>4084.959253302339</v>
       </c>
       <c r="D263" t="n">
-        <v>4531.227639542165</v>
+        <v>4425.198586724006</v>
       </c>
       <c r="E263" t="n">
-        <v>4453.0693359375</v>
+        <v>4215.26708984375</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
-        <v>46178</v>
+        <v>46183</v>
       </c>
       <c r="B264" t="n">
-        <v>4332.272043594116</v>
+        <v>4251.946953445542</v>
       </c>
       <c r="C264" t="n">
-        <v>4157.799086353457</v>
+        <v>4079.68533032556</v>
       </c>
       <c r="D264" t="n">
-        <v>4501.34242778295</v>
+        <v>4417.899211844246</v>
       </c>
       <c r="E264" t="n">
-        <v>4320.01220703125</v>
+        <v>4049.58642578125</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
-        <v>46179</v>
+        <v>46184</v>
       </c>
       <c r="B265" t="n">
-        <v>4311.697528495696</v>
+        <v>4227.333275018503</v>
       </c>
       <c r="C265" t="n">
-        <v>4128.26923189429</v>
+        <v>4070.478841401913</v>
       </c>
       <c r="D265" t="n">
-        <v>4495.794739625759</v>
+        <v>4411.685960093564</v>
       </c>
       <c r="E265" t="n">
-        <v>4296.80859375</v>
+        <v>4211.1201171875</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
-        <v>46180</v>
+        <v>46185</v>
       </c>
       <c r="B266" t="n">
-        <v>4287.164590264916</v>
+        <v>4206.560486771045</v>
       </c>
       <c r="C266" t="n">
-        <v>4111.555256668803</v>
+        <v>4038.853651250566</v>
       </c>
       <c r="D266" t="n">
-        <v>4460.00181688773</v>
+        <v>4370.499937606885</v>
       </c>
       <c r="E266" t="n">
-        <v>4334.697265625</v>
+        <v>4209.83251953125</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
-        <v>46181</v>
+        <v>46186</v>
       </c>
       <c r="B267" t="n">
-        <v>4280.567986358534</v>
+        <v>4195.238891316893</v>
       </c>
       <c r="C267" t="n">
-        <v>4112.745397677522</v>
+        <v>4034.03160527326</v>
       </c>
       <c r="D267" t="n">
-        <v>4451.54148881627</v>
+        <v>4370.752540554183</v>
       </c>
       <c r="E267" t="n">
-        <v>4308.56982421875</v>
+        <v>4220.650390625</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
-        <v>46182</v>
+        <v>46187</v>
       </c>
       <c r="B268" t="n">
-        <v>4255.406053240794</v>
+        <v>4180.383912693089</v>
       </c>
       <c r="C268" t="n">
-        <v>4083.105667775443</v>
+        <v>4006.446650768972</v>
       </c>
       <c r="D268" t="n">
-        <v>4426.88800574162</v>
+        <v>4366.092347024075</v>
       </c>
       <c r="E268" t="n">
-        <v>4215.26708984375</v>
+        <v>4286.2568359375</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
-        <v>46183</v>
+        <v>46188</v>
       </c>
       <c r="B269" t="n">
-        <v>4252.314223022331</v>
+        <v>4184.507167619035</v>
       </c>
       <c r="C269" t="n">
-        <v>4091.284341632921</v>
+        <v>4016.518822060601</v>
       </c>
       <c r="D269" t="n">
-        <v>4418.440723385414</v>
+        <v>4348.147574576404</v>
       </c>
       <c r="E269" t="n">
-        <v>4049.58642578125</v>
+        <v>4306.87744140625</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
-        <v>46184</v>
+        <v>46189</v>
       </c>
       <c r="B270" t="n">
-        <v>4225.03354667688</v>
+        <v>4168.189726667498</v>
       </c>
       <c r="C270" t="n">
-        <v>4053.98105687276</v>
+        <v>3994.028201191663</v>
       </c>
       <c r="D270" t="n">
-        <v>4377.354735070697</v>
+        <v>4338.271779278257</v>
       </c>
       <c r="E270" t="n">
-        <v>4211.1201171875</v>
+        <v>4319.31689453125</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>46185</v>
+        <v>46190</v>
       </c>
       <c r="B271" t="n">
-        <v>4205.289031506813</v>
+        <v>4174.581770755134</v>
       </c>
       <c r="C271" t="n">
-        <v>4022.499758000664</v>
+        <v>4006.258185463542</v>
       </c>
       <c r="D271" t="n">
-        <v>4372.355654532419</v>
+        <v>4346.192799531698</v>
       </c>
       <c r="E271" t="n">
-        <v>4209.83251953125</v>
+        <v>4265.73486328125</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B272" t="n">
-        <v>4194.681152375119</v>
+        <v>4160.022174695741</v>
       </c>
       <c r="C272" t="n">
-        <v>4016.093619840134</v>
+        <v>3982.829571310825</v>
       </c>
       <c r="D272" t="n">
-        <v>4367.991042972667</v>
+        <v>4331.416573769117</v>
       </c>
       <c r="E272" t="n">
-        <v>4220.650390625</v>
+        <v>4180.39892578125</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>46187</v>
+        <v>46192</v>
       </c>
       <c r="B273" t="n">
-        <v>4180.671616160986</v>
+        <v>4148.677483320706</v>
       </c>
       <c r="C273" t="n">
-        <v>4010.078501064342</v>
+        <v>3972.747205125668</v>
       </c>
       <c r="D273" t="n">
-        <v>4364.081452871638</v>
+        <v>4320.976635916324</v>
       </c>
       <c r="E273" t="n">
-        <v>4286.2568359375</v>
+        <v>4151.90771484375</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>46188</v>
+        <v>46193</v>
       </c>
       <c r="B274" t="n">
-        <v>4184.874499221144</v>
+        <v>4145.969067628816</v>
       </c>
       <c r="C274" t="n">
-        <v>4021.880682779329</v>
+        <v>3965.202719269268</v>
       </c>
       <c r="D274" t="n">
-        <v>4369.419212679159</v>
+        <v>4311.907231943424</v>
       </c>
       <c r="E274" t="n">
-        <v>4306.87744140625</v>
+        <v>4149.44677734375</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>46189</v>
+        <v>46194</v>
       </c>
       <c r="B275" t="n">
-        <v>4170.512377971468</v>
+        <v>4138.75568973494</v>
       </c>
       <c r="C275" t="n">
-        <v>3999.645598523428</v>
+        <v>3971.735615063548</v>
       </c>
       <c r="D275" t="n">
-        <v>4351.467503724839</v>
+        <v>4306.068448025374</v>
       </c>
       <c r="E275" t="n">
-        <v>4319.31689453125</v>
+        <v>4134.23193359375</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B276" t="n">
-        <v>4177.957479452448</v>
+        <v>4149.427764572602</v>
       </c>
       <c r="C276" t="n">
-        <v>4006.880419878994</v>
+        <v>3972.720063868491</v>
       </c>
       <c r="D276" t="n">
-        <v>4341.837549007002</v>
+        <v>4312.81769862797</v>
       </c>
       <c r="E276" t="n">
-        <v>4265.73486328125</v>
+        <v>4179.84033203125</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>46191</v>
+        <v>46196</v>
       </c>
       <c r="B277" t="n">
-        <v>4160.707244261179</v>
+        <v>4138.482683889089</v>
       </c>
       <c r="C277" t="n">
-        <v>3977.55794640093</v>
+        <v>3969.603286979696</v>
       </c>
       <c r="D277" t="n">
-        <v>4331.392677467764</v>
+        <v>4312.502786176184</v>
       </c>
       <c r="E277" t="n">
-        <v>4180.39892578125</v>
+        <v>4091.5751953125</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>46192</v>
+        <v>46197</v>
       </c>
       <c r="B278" t="n">
-        <v>4150.268919852988</v>
+        <v>4149.025384670113</v>
       </c>
       <c r="C278" t="n">
-        <v>3977.762831221805</v>
+        <v>3981.688613493236</v>
       </c>
       <c r="D278" t="n">
-        <v>4317.976247477695</v>
+        <v>4318.309504375663</v>
       </c>
       <c r="E278" t="n">
-        <v>4151.90771484375</v>
+        <v>4007.2138671875</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>46193</v>
+        <v>46198</v>
       </c>
       <c r="B279" t="n">
-        <v>4148.056382429872</v>
+        <v>4137.387705168931</v>
       </c>
       <c r="C279" t="n">
-        <v>3990.445379226034</v>
+        <v>3962.605549324718</v>
       </c>
       <c r="D279" t="n">
-        <v>4327.727086310918</v>
+        <v>4300.226155852389</v>
       </c>
       <c r="E279" t="n">
-        <v>4149.44677734375</v>
+        <v>4008.37060546875</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>46194</v>
+        <v>46199</v>
       </c>
       <c r="B280" t="n">
-        <v>4141.380137241195</v>
+        <v>4127.766040034949</v>
       </c>
       <c r="C280" t="n">
-        <v>3982.640255208643</v>
+        <v>3963.243579192236</v>
       </c>
       <c r="D280" t="n">
-        <v>4324.941500830478</v>
+        <v>4298.552055863807</v>
       </c>
       <c r="E280" t="n">
-        <v>4134.23193359375</v>
+        <v>4076.42822265625</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>46195</v>
+        <v>46200</v>
       </c>
       <c r="B281" t="n">
-        <v>4151.741523773451</v>
+        <v>4125.646158360923</v>
       </c>
       <c r="C281" t="n">
-        <v>3976.834142051447</v>
+        <v>3966.021025502107</v>
       </c>
       <c r="D281" t="n">
-        <v>4318.330177027078</v>
+        <v>4307.059497915813</v>
       </c>
       <c r="E281" t="n">
-        <v>4179.84033203125</v>
+        <v>4069.586181640625</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="B282" t="n">
-        <v>4142.290689569278</v>
+        <v>4117.982518928001</v>
       </c>
       <c r="C282" t="n">
-        <v>3986.280427751941</v>
+        <v>3943.328910022317</v>
       </c>
       <c r="D282" t="n">
-        <v>4318.268540766511</v>
+        <v>4288.428218695058</v>
       </c>
       <c r="E282" t="n">
-        <v>4091.5751953125</v>
+        <v>4053.93408203125</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="B283" t="n">
-        <v>4153.368341075643</v>
+        <v>4127.28849951222</v>
       </c>
       <c r="C283" t="n">
-        <v>3976.406794063015</v>
+        <v>3950.642071781772</v>
       </c>
       <c r="D283" t="n">
-        <v>4323.528266928207</v>
+        <v>4300.887743345776</v>
       </c>
       <c r="E283" t="n">
-        <v>4007.2138671875</v>
+        <v>4007.720947265625</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>46198</v>
+        <v>46203</v>
       </c>
       <c r="B284" t="n">
-        <v>4138.480684984735</v>
+        <v>4114.207055709491</v>
       </c>
       <c r="C284" t="n">
-        <v>3968.796628648023</v>
+        <v>3941.51317591271</v>
       </c>
       <c r="D284" t="n">
-        <v>4293.567530383509</v>
+        <v>4289.474599201902</v>
       </c>
       <c r="E284" t="n">
-        <v>4008.37060546875</v>
+        <v>3999.095458984375</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>46199</v>
+        <v>46204</v>
       </c>
       <c r="B285" t="n">
-        <v>4129.182233420003</v>
+        <v>4122.006153995378</v>
       </c>
       <c r="C285" t="n">
-        <v>3974.590173544963</v>
+        <v>3950.84114353546</v>
       </c>
       <c r="D285" t="n">
-        <v>4295.384052127225</v>
+        <v>4299.570742229778</v>
       </c>
       <c r="E285" t="n">
-        <v>4076.42822265625</v>
+        <v>4029.442138671875</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>46200</v>
+        <v>46205</v>
       </c>
       <c r="B286" t="n">
-        <v>4126.969762036529</v>
+        <v>4107.192695110154</v>
       </c>
       <c r="C286" t="n">
-        <v>3952.622605210051</v>
+        <v>3942.80888390237</v>
       </c>
       <c r="D286" t="n">
-        <v>4299.614220628535</v>
+        <v>4285.206750296524</v>
       </c>
       <c r="E286" t="n">
-        <v>4069.586181640625</v>
+        <v>4120.0087890625</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>46201</v>
+        <v>46206</v>
       </c>
       <c r="B287" t="n">
-        <v>4119.268491337004</v>
+        <v>4094.144614995055</v>
       </c>
       <c r="C287" t="n">
-        <v>3937.101774868373</v>
+        <v>3938.588706833647</v>
       </c>
       <c r="D287" t="n">
-        <v>4286.614036700857</v>
+        <v>4261.925974594975</v>
       </c>
       <c r="E287" t="n">
-        <v>4053.93408203125</v>
+        <v>4166.45947265625</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>46202</v>
+        <v>46207</v>
       </c>
       <c r="B288" t="n">
-        <v>4127.721664120709</v>
+        <v>4088.53020067444</v>
       </c>
       <c r="C288" t="n">
-        <v>3948.162620072355</v>
+        <v>3919.049457071237</v>
       </c>
       <c r="D288" t="n">
-        <v>4289.431720555938</v>
+        <v>4264.76750722319</v>
       </c>
       <c r="E288" t="n">
-        <v>4007.720947265625</v>
+        <v>4164.49365234375</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>46203</v>
+        <v>46208</v>
       </c>
       <c r="B289" t="n">
-        <v>4115.643249831795</v>
+        <v>4077.482121206469</v>
       </c>
       <c r="C289" t="n">
-        <v>3941.880077099138</v>
+        <v>3909.247293480028</v>
       </c>
       <c r="D289" t="n">
-        <v>4280.156538594924</v>
+        <v>4244.061440980249</v>
       </c>
       <c r="E289" t="n">
-        <v>3999.095458984375</v>
+        <v>4175.6865234375</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B290" t="n">
-        <v>4123.553966903162</v>
+        <v>4083.682744273469</v>
       </c>
       <c r="C290" t="n">
-        <v>3957.904640673172</v>
+        <v>3923.107538380153</v>
       </c>
       <c r="D290" t="n">
-        <v>4292.373622716846</v>
+        <v>4257.054915907867</v>
       </c>
       <c r="E290" t="n">
-        <v>4029.442138671875</v>
+        <v>4152.48388671875</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B291" t="n">
-        <v>4105.150226593501</v>
+        <v>4067.930389045195</v>
       </c>
       <c r="C291" t="n">
-        <v>3928.677207044278</v>
+        <v>3883.687145942809</v>
       </c>
       <c r="D291" t="n">
-        <v>4279.365998511539</v>
+        <v>4249.396379557858</v>
       </c>
       <c r="E291" t="n">
-        <v>4120.0087890625</v>
+        <v>4092.410888671875</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>46206</v>
+        <v>46211</v>
       </c>
       <c r="B292" t="n">
-        <v>4092.180866660992</v>
+        <v>4073.630975968149</v>
       </c>
       <c r="C292" t="n">
-        <v>3927.539313430686</v>
+        <v>3909.125508747062</v>
       </c>
       <c r="D292" t="n">
-        <v>4254.036662162904</v>
+        <v>4248.388474625905</v>
       </c>
       <c r="E292" t="n">
-        <v>4166.45947265625</v>
+        <v>4069.62353515625</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>46207</v>
+        <v>46212</v>
       </c>
       <c r="B293" t="n">
-        <v>4086.335153909864</v>
+        <v>4057.408880027032</v>
       </c>
       <c r="C293" t="n">
-        <v>3907.744801099596</v>
+        <v>3872.324625903444</v>
       </c>
       <c r="D293" t="n">
-        <v>4243.158803618645</v>
+        <v>4226.424661862836</v>
       </c>
       <c r="E293" t="n">
-        <v>4164.49365234375</v>
+        <v>4114.41064453125</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>46208</v>
+        <v>46213</v>
       </c>
       <c r="B294" t="n">
-        <v>4075.223307267979</v>
+        <v>4043.736739415717</v>
       </c>
       <c r="C294" t="n">
-        <v>3910.590597917546</v>
+        <v>3869.858893130927</v>
       </c>
       <c r="D294" t="n">
-        <v>4238.820866363472</v>
+        <v>4212.032184242181</v>
       </c>
       <c r="E294" t="n">
-        <v>4175.6865234375</v>
+        <v>4110.74462890625</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
-        <v>46209</v>
+        <v>46214</v>
       </c>
       <c r="B295" t="n">
-        <v>4080.660880391948</v>
+        <v>4038.353293401303</v>
       </c>
       <c r="C295" t="n">
-        <v>3907.972552290135</v>
+        <v>3853.931160170434</v>
       </c>
       <c r="D295" t="n">
-        <v>4258.787504848201</v>
+        <v>4209.443748529058</v>
       </c>
       <c r="E295" t="n">
-        <v>4152.48388671875</v>
+        <v>4100.0029296875</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
-        <v>46210</v>
+        <v>46215</v>
       </c>
       <c r="B296" t="n">
-        <v>4066.11688167189</v>
+        <v>4028.436759084627</v>
       </c>
       <c r="C296" t="n">
-        <v>3894.856352572693</v>
+        <v>3852.410056522922</v>
       </c>
       <c r="D296" t="n">
-        <v>4226.104969942156</v>
+        <v>4205.532894821305</v>
       </c>
       <c r="E296" t="n">
-        <v>4092.410888671875</v>
+        <v>4074.627685546875</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
-        <v>46211</v>
+        <v>46216</v>
       </c>
       <c r="B297" t="n">
-        <v>4072.245944754969</v>
+        <v>4036.690297879545</v>
       </c>
       <c r="C297" t="n">
-        <v>3901.561532349312</v>
+        <v>3869.316810353363</v>
       </c>
       <c r="D297" t="n">
-        <v>4240.834736450184</v>
+        <v>4200.058932053696</v>
       </c>
       <c r="E297" t="n">
-        <v>4069.62353515625</v>
+        <v>3992.321533203125</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
-        <v>46212</v>
+        <v>46217</v>
       </c>
       <c r="B298" t="n">
-        <v>4052.854248545395</v>
+        <v>4023.909177734053</v>
       </c>
       <c r="C298" t="n">
-        <v>3883.732506733079</v>
+        <v>3830.423706385799</v>
       </c>
       <c r="D298" t="n">
-        <v>4221.685894686285</v>
+        <v>4205.082574330904</v>
       </c>
       <c r="E298" t="n">
-        <v>4114.41064453125</v>
+        <v>4046.171875</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="B299" t="n">
-        <v>4039.774120363844</v>
+        <v>4033.47402269954</v>
       </c>
       <c r="C299" t="n">
-        <v>3874.896861246832</v>
+        <v>3873.122358455895</v>
       </c>
       <c r="D299" t="n">
-        <v>4215.60069229216</v>
+        <v>4200.977589693955</v>
       </c>
       <c r="E299" t="n">
-        <v>4110.74462890625</v>
+        <v>4048.7763671875</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
-        <v>46214</v>
+        <v>46219</v>
       </c>
       <c r="B300" t="n">
-        <v>4034.75083547477</v>
+        <v>4021.963866528833</v>
       </c>
       <c r="C300" t="n">
-        <v>3854.805001762888</v>
+        <v>3856.842081654513</v>
       </c>
       <c r="D300" t="n">
-        <v>4216.756722377227</v>
+        <v>4186.435209743214</v>
       </c>
       <c r="E300" t="n">
-        <v>4100.0029296875</v>
+        <v>3977.87548828125</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
-        <v>46215</v>
+        <v>46220</v>
       </c>
       <c r="B301" t="n">
-        <v>4025.422867156149</v>
+        <v>4013.788655016555</v>
       </c>
       <c r="C301" t="n">
-        <v>3860.056763457294</v>
+        <v>3834.950206615186</v>
       </c>
       <c r="D301" t="n">
-        <v>4196.687474458978</v>
+        <v>4175.331957640559</v>
       </c>
       <c r="E301" t="n">
-        <v>4074.627685546875</v>
+        <v>4003.6015625</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
-        <v>46216</v>
+        <v>46221</v>
       </c>
       <c r="B302" t="n">
-        <v>4033.606898190587</v>
+        <v>4014.61015104603</v>
       </c>
       <c r="C302" t="n">
-        <v>3871.304877999024</v>
+        <v>3848.15287071758</v>
       </c>
       <c r="D302" t="n">
-        <v>4209.342965720401</v>
+        <v>4198.263757255119</v>
       </c>
       <c r="E302" t="n">
-        <v>3992.321533203125</v>
+        <v>4008.41796875</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
-        <v>46217</v>
+        <v>46222</v>
       </c>
       <c r="B303" t="n">
-        <v>4022.747413420845</v>
+        <v>4011.518622309031</v>
       </c>
       <c r="C303" t="n">
-        <v>3870.973612628276</v>
+        <v>3841.147692847252</v>
       </c>
       <c r="D303" t="n">
-        <v>4191.710330891164</v>
+        <v>4181.721248150602</v>
       </c>
       <c r="E303" t="n">
-        <v>4046.171875</v>
+        <v>3989.054931640625</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="B304" t="n">
-        <v>4033.451102608178</v>
+        <v>4027.121730634871</v>
       </c>
       <c r="C304" t="n">
-        <v>3856.080434567285</v>
+        <v>3864.118638328204</v>
       </c>
       <c r="D304" t="n">
-        <v>4198.588732823016</v>
+        <v>4188.66950445594</v>
       </c>
       <c r="E304" t="n">
-        <v>4048.7763671875</v>
+        <v>4002.884765625</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="B305" t="n">
-        <v>4019.455664556267</v>
+        <v>4022.115096633407</v>
       </c>
       <c r="C305" t="n">
-        <v>3852.999331279684</v>
+        <v>3856.909854768265</v>
       </c>
       <c r="D305" t="n">
-        <v>4200.505707557052</v>
+        <v>4187.332502793804</v>
       </c>
       <c r="E305" t="n">
-        <v>3977.87548828125</v>
+        <v>4072.03076171875</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="B306" t="n">
-        <v>4012.507819332034</v>
+        <v>4039.778804993355</v>
       </c>
       <c r="C306" t="n">
-        <v>3830.071868317162</v>
+        <v>3865.733912807264</v>
       </c>
       <c r="D306" t="n">
-        <v>4168.247876456215</v>
+        <v>4206.260455480983</v>
       </c>
       <c r="E306" t="n">
-        <v>4003.6015625</v>
+        <v>4123.4501953125</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
-        <v>46221</v>
+        <v>46226</v>
       </c>
       <c r="B307" t="n">
-        <v>4014.253900416981</v>
+        <v>4036.593450680007</v>
       </c>
       <c r="C307" t="n">
-        <v>3839.343632044862</v>
+        <v>3866.564979214516</v>
       </c>
       <c r="D307" t="n">
-        <v>4191.103081327149</v>
+        <v>4207.867636140803</v>
       </c>
       <c r="E307" t="n">
-        <v>4008.41796875</v>
+        <v>4043.264404296875</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
-        <v>46222</v>
+        <v>46227</v>
       </c>
       <c r="B308" t="n">
-        <v>4012.224130227083</v>
+        <v>4036.875268205338</v>
       </c>
       <c r="C308" t="n">
-        <v>3857.409144521838</v>
+        <v>3860.069067883531</v>
       </c>
       <c r="D308" t="n">
-        <v>4170.540172692288</v>
+        <v>4201.483410219123</v>
       </c>
       <c r="E308" t="n">
-        <v>3989.054931640625</v>
+        <v>4050.573486328125</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
-        <v>46223</v>
+        <v>46228</v>
       </c>
       <c r="B309" t="n">
-        <v>4028.121735148202</v>
+        <v>4046.199212722441</v>
       </c>
       <c r="C309" t="n">
-        <v>3852.338182195378</v>
+        <v>3871.33755620465</v>
       </c>
       <c r="D309" t="n">
-        <v>4183.638162225594</v>
+        <v>4204.000064963726</v>
       </c>
       <c r="E309" t="n">
-        <v>4002.884765625</v>
+        <v>4052.02490234375</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
-        <v>46224</v>
+        <v>46229</v>
       </c>
       <c r="B310" t="n">
-        <v>4025.276566409641</v>
+        <v>4051.577307813178</v>
       </c>
       <c r="C310" t="n">
-        <v>3854.564774858171</v>
+        <v>3889.026394895964</v>
       </c>
       <c r="D310" t="n">
-        <v>4199.301342016064</v>
+        <v>4225.929911331527</v>
       </c>
       <c r="E310" t="n">
-        <v>4072.03076171875</v>
+        <v>4083.52392578125</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
-        <v>46225</v>
+        <v>46230</v>
       </c>
       <c r="B311" t="n">
-        <v>4044.183309433638</v>
+        <v>4075.548635965461</v>
       </c>
       <c r="C311" t="n">
-        <v>3873.830805279074</v>
+        <v>3906.689432469933</v>
       </c>
       <c r="D311" t="n">
-        <v>4212.546833715549</v>
+        <v>4248.177928420718</v>
       </c>
       <c r="E311" t="n">
-        <v>4123.4501953125</v>
+        <v>4062.4287109375</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="n">
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="B312" t="n">
-        <v>4038.473737747174</v>
+        <v>4078.75042590182</v>
       </c>
       <c r="C312" t="n">
-        <v>3863.320447424799</v>
+        <v>3910.584838194327</v>
       </c>
       <c r="D312" t="n">
-        <v>4211.605021501937</v>
+        <v>4256.751545170159</v>
       </c>
       <c r="E312" t="n">
-        <v>4043.264404296875</v>
+        <v>4017.01123046875</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="n">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="B313" t="n">
-        <v>4039.797699694024</v>
+        <v>4104.414506353777</v>
       </c>
       <c r="C313" t="n">
-        <v>3873.283671946293</v>
+        <v>3936.606844165684</v>
       </c>
       <c r="D313" t="n">
-        <v>4217.863922872049</v>
+        <v>4274.36682677311</v>
       </c>
       <c r="E313" t="n">
-        <v>4050.573486328125</v>
+        <v>4078.895751953125</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="n">
-        <v>46228</v>
+        <v>46233</v>
       </c>
       <c r="B314" t="n">
-        <v>4049.716111421533</v>
+        <v>4108.982754127809</v>
       </c>
       <c r="C314" t="n">
-        <v>3882.960467700426</v>
+        <v>3931.955373130063</v>
       </c>
       <c r="D314" t="n">
-        <v>4221.94644543771</v>
+        <v>4286.786941055141</v>
       </c>
       <c r="E314" t="n">
-        <v>4052.02490234375</v>
+        <v>4098.5625</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="n">
-        <v>46229</v>
+        <v>46234</v>
       </c>
       <c r="B315" t="n">
-        <v>4055.686984683188</v>
+        <v>4116.741128304003</v>
       </c>
       <c r="C315" t="n">
-        <v>3868.208163927672</v>
+        <v>3948.724624883956</v>
       </c>
       <c r="D315" t="n">
-        <v>4219.647272869707</v>
+        <v>4288.484376814162</v>
       </c>
       <c r="E315" t="n">
-        <v>4083.52392578125</v>
+        <v>4043.583740234375</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="n">
-        <v>46230</v>
+        <v>46235</v>
       </c>
       <c r="B316" t="n">
-        <v>4079.355596562928</v>
+        <v>4133.241228996511</v>
       </c>
       <c r="C316" t="n">
-        <v>3907.180482506671</v>
+        <v>3974.411078685796</v>
       </c>
       <c r="D316" t="n">
-        <v>4242.302534159202</v>
+        <v>4305.094219772643</v>
       </c>
       <c r="E316" t="n">
-        <v>4062.4287109375</v>
+        <v>4044.826904296875</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
-        <v>46231</v>
+        <v>46236</v>
       </c>
       <c r="B317" t="n">
-        <v>4084.008445748451</v>
+        <v>4145.476782462373</v>
       </c>
       <c r="C317" t="n">
-        <v>3910.071919375889</v>
+        <v>3979.304257992024</v>
       </c>
       <c r="D317" t="n">
-        <v>4264.666108932985</v>
+        <v>4302.058488714122</v>
       </c>
       <c r="E317" t="n">
-        <v>4017.01123046875</v>
+        <v>4066.402587890625</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="B318" t="n">
-        <v>4110.111084178782</v>
+        <v>4175.971529330728</v>
       </c>
       <c r="C318" t="n">
-        <v>3933.801332733546</v>
+        <v>3997.421181841137</v>
       </c>
       <c r="D318" t="n">
-        <v>4286.573459814397</v>
+        <v>4359.252990402703</v>
       </c>
       <c r="E318" t="n">
-        <v>4078.895751953125</v>
+        <v>4047.6044921875</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="B319" t="n">
-        <v>4111.279313797994</v>
+        <v>4185.348080875201</v>
       </c>
       <c r="C319" t="n">
-        <v>3931.457109882744</v>
+        <v>4015.79140176792</v>
       </c>
       <c r="D319" t="n">
-        <v>4287.266794205574</v>
+        <v>4364.906181532488</v>
       </c>
       <c r="E319" t="n">
-        <v>4098.5625</v>
+        <v>4064.322265625</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
-        <v>46234</v>
+        <v>46239</v>
       </c>
       <c r="B320" t="n">
-        <v>4119.158496378395</v>
+        <v>4216.822129432849</v>
       </c>
       <c r="C320" t="n">
-        <v>3936.508003327736</v>
+        <v>4043.479472295708</v>
       </c>
       <c r="D320" t="n">
-        <v>4296.987687313127</v>
+        <v>4394.072744976917</v>
       </c>
       <c r="E320" t="n">
-        <v>4043.583740234375</v>
+        <v>4265.63232421875</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B321" t="n">
-        <v>4135.314333421739</v>
+        <v>4226.815758619407</v>
       </c>
       <c r="C321" t="n">
-        <v>3971.590561038641</v>
+        <v>4050.437623724807</v>
       </c>
       <c r="D321" t="n">
-        <v>4312.297830800379</v>
+        <v>4398.856121925011</v>
       </c>
       <c r="E321" t="n">
-        <v>4044.826904296875</v>
+        <v>4244.072265625</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
-        <v>46236</v>
+        <v>46241</v>
       </c>
       <c r="B322" t="n">
-        <v>4147.216248927</v>
+        <v>4239.589559767604</v>
       </c>
       <c r="C322" t="n">
-        <v>3976.293638781052</v>
+        <v>4071.681339185283</v>
       </c>
       <c r="D322" t="n">
-        <v>4321.268041418725</v>
+        <v>4404.778161136655</v>
       </c>
       <c r="E322" t="n">
-        <v>4066.402587890625</v>
+        <v>4340.7705078125</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
-        <v>46237</v>
+        <v>46242</v>
       </c>
       <c r="B323" t="n">
-        <v>4176.524603277014</v>
+        <v>4260.662599957358</v>
       </c>
       <c r="C323" t="n">
-        <v>3999.523589016395</v>
+        <v>4084.327993871212</v>
       </c>
       <c r="D323" t="n">
-        <v>4352.144275474468</v>
+        <v>4432.571868372675</v>
       </c>
       <c r="E323" t="n">
-        <v>4047.6044921875</v>
+        <v>4343.48876953125</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
-        <v>46238</v>
+        <v>46243</v>
       </c>
       <c r="B324" t="n">
-        <v>4186.541516517658</v>
+        <v>4276.987738544321</v>
       </c>
       <c r="C324" t="n">
-        <v>4004.836678386458</v>
+        <v>4105.402349738436</v>
       </c>
       <c r="D324" t="n">
-        <v>4359.36464490448</v>
+        <v>4452.918903641006</v>
       </c>
       <c r="E324" t="n">
-        <v>4064.322265625</v>
+        <v>4331.46240234375</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B325" t="n">
-        <v>4217.745531156415</v>
+        <v>4311.038848461683</v>
       </c>
       <c r="C325" t="n">
-        <v>4059.598468226731</v>
+        <v>4152.654023834401</v>
       </c>
       <c r="D325" t="n">
-        <v>4378.632296208859</v>
+        <v>4474.780202771964</v>
       </c>
       <c r="E325" t="n">
-        <v>4265.63232421875</v>
+        <v>4390.552734375</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="B326" t="n">
-        <v>4223.759748044929</v>
+        <v>4323.379567841847</v>
       </c>
       <c r="C326" t="n">
-        <v>4055.847727267645</v>
+        <v>4148.579466970715</v>
       </c>
       <c r="D326" t="n">
-        <v>4380.329449124471</v>
+        <v>4492.510045030085</v>
       </c>
       <c r="E326" t="n">
-        <v>4244.072265625</v>
+        <v>4364.71484375</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="B327" t="n">
-        <v>4236.228324441834</v>
+        <v>4357.158007167268</v>
       </c>
       <c r="C327" t="n">
-        <v>4068.111987825312</v>
+        <v>4193.098546859213</v>
       </c>
       <c r="D327" t="n">
-        <v>4396.495495703453</v>
+        <v>4534.716367599899</v>
       </c>
       <c r="E327" t="n">
-        <v>4340.7705078125</v>
+        <v>4401.5400390625</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
-        <v>46242</v>
+        <v>46247</v>
       </c>
       <c r="B328" t="n">
-        <v>4256.704824525812</v>
+        <v>4368.721173292571</v>
       </c>
       <c r="C328" t="n">
-        <v>4091.043180506888</v>
+        <v>4209.701041161178</v>
       </c>
       <c r="D328" t="n">
-        <v>4432.956181151764</v>
+        <v>4544.099874219371</v>
       </c>
       <c r="E328" t="n">
-        <v>4343.48876953125</v>
+        <v>4353.865234375</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B329" t="n">
-        <v>4272.633675614445</v>
+        <v>4382.248807942759</v>
       </c>
       <c r="C329" t="n">
-        <v>4091.704471302878</v>
+        <v>4209.220840806056</v>
       </c>
       <c r="D329" t="n">
-        <v>4434.285149560321</v>
+        <v>4569.193704520377</v>
       </c>
       <c r="E329" t="n">
-        <v>4331.46240234375</v>
+        <v>4374.42626953125</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
-        <v>46244</v>
+        <v>46249</v>
       </c>
       <c r="B330" t="n">
-        <v>4305.636061482157</v>
+        <v>4403.175652472079</v>
       </c>
       <c r="C330" t="n">
-        <v>4131.347093041373</v>
+        <v>4249.211267117848</v>
       </c>
       <c r="D330" t="n">
-        <v>4467.080956794259</v>
+        <v>4582.106731877184</v>
       </c>
       <c r="E330" t="n">
-        <v>4390.552734375</v>
+        <v>4374.23486328125</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
-        <v>46245</v>
+        <v>46250</v>
       </c>
       <c r="B331" t="n">
-        <v>4318.96011290735</v>
+        <v>4418.369578059294</v>
       </c>
       <c r="C331" t="n">
-        <v>4157.671962383776</v>
+        <v>4248.403106020623</v>
       </c>
       <c r="D331" t="n">
-        <v>4482.281216923341</v>
+        <v>4594.723948595338</v>
       </c>
       <c r="E331" t="n">
-        <v>4364.71484375</v>
+        <v>4364.1181640625</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="B332" t="n">
-        <v>4353.015682867643</v>
+        <v>4450.222057208187</v>
       </c>
       <c r="C332" t="n">
-        <v>4174.345990146095</v>
+        <v>4279.931507076058</v>
       </c>
       <c r="D332" t="n">
-        <v>4519.989606947833</v>
+        <v>4613.501079742405</v>
       </c>
       <c r="E332" t="n">
-        <v>4401.5400390625</v>
+        <v>4413.7080078125</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="B333" t="n">
-        <v>4361.343370215861</v>
+        <v>4459.220501303233</v>
       </c>
       <c r="C333" t="n">
-        <v>4184.248694897563</v>
+        <v>4291.382598231793</v>
       </c>
       <c r="D333" t="n">
-        <v>4519.122800619494</v>
+        <v>4642.420536773973</v>
       </c>
       <c r="E333" t="n">
-        <v>4353.865234375</v>
+        <v>4332.75439453125</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
-        <v>46248</v>
+        <v>46253</v>
       </c>
       <c r="B334" t="n">
-        <v>4375.492682603455</v>
+        <v>4488.446771280121</v>
       </c>
       <c r="C334" t="n">
-        <v>4194.45077060628</v>
+        <v>4320.821385234673</v>
       </c>
       <c r="D334" t="n">
-        <v>4553.323980331217</v>
+        <v>4657.826663035619</v>
       </c>
       <c r="E334" t="n">
-        <v>4374.42626953125</v>
+        <v>4496.87548828125</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
-        <v>46249</v>
+        <v>46254</v>
       </c>
       <c r="B335" t="n">
-        <v>4396.912801381557</v>
+        <v>4494.195490939396</v>
       </c>
       <c r="C335" t="n">
-        <v>4231.872740860173</v>
+        <v>4314.543264853713</v>
       </c>
       <c r="D335" t="n">
-        <v>4565.852027576745</v>
+        <v>4663.940558016061</v>
       </c>
       <c r="E335" t="n">
-        <v>4374.23486328125</v>
+        <v>4513.38232421875</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
-        <v>46250</v>
+        <v>46255</v>
       </c>
       <c r="B336" t="n">
-        <v>4412.937145354274</v>
+        <v>4500.611719267732</v>
       </c>
       <c r="C336" t="n">
-        <v>4245.72181831847</v>
+        <v>4346.224677955133</v>
       </c>
       <c r="D336" t="n">
-        <v>4585.787303942941</v>
+        <v>4677.946395372401</v>
       </c>
       <c r="E336" t="n">
-        <v>4364.1181640625</v>
+        <v>4598.94677734375</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
-        <v>46251</v>
+        <v>46256</v>
       </c>
       <c r="B337" t="n">
-        <v>4445.072980906863</v>
+        <v>4513.116847533764</v>
       </c>
       <c r="C337" t="n">
-        <v>4264.144879841438</v>
+        <v>4348.759671091753</v>
       </c>
       <c r="D337" t="n">
-        <v>4612.088098037413</v>
+        <v>4670.740550822533</v>
       </c>
       <c r="E337" t="n">
-        <v>4413.7080078125</v>
+        <v>4586.66064453125</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
-        <v>46252</v>
+        <v>46257</v>
       </c>
       <c r="B338" t="n">
-        <v>4456.455829575914</v>
+        <v>4518.590014440277</v>
       </c>
       <c r="C338" t="n">
-        <v>4277.873879910354</v>
+        <v>4365.616858475588</v>
       </c>
       <c r="D338" t="n">
-        <v>4644.894680547914</v>
+        <v>4693.332968600612</v>
       </c>
       <c r="E338" t="n">
-        <v>4332.75439453125</v>
+        <v>4611.45068359375</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="B339" t="n">
-        <v>4487.388829407844</v>
+        <v>4539.461374457354</v>
       </c>
       <c r="C339" t="n">
-        <v>4324.93248599772</v>
+        <v>4368.644971309945</v>
       </c>
       <c r="D339" t="n">
-        <v>4671.052121459961</v>
+        <v>4717.966878464184</v>
       </c>
       <c r="E339" t="n">
-        <v>4496.87548828125</v>
+        <v>4671.80908203125</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
-        <v>46254</v>
+        <v>46259</v>
       </c>
       <c r="B340" t="n">
-        <v>4491.316564821441</v>
+        <v>4536.286613437688</v>
       </c>
       <c r="C340" t="n">
-        <v>4331.795842773588</v>
+        <v>4379.721783421063</v>
       </c>
       <c r="D340" t="n">
-        <v>4658.764643363756</v>
+        <v>4701.705731298723</v>
       </c>
       <c r="E340" t="n">
-        <v>4513.38232421875</v>
+        <v>4648.12109375</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="B341" t="n">
-        <v>4499.708093218055</v>
+        <v>4552.246902763783</v>
       </c>
       <c r="C341" t="n">
-        <v>4334.893998925705</v>
+        <v>4375.602627258006</v>
       </c>
       <c r="D341" t="n">
-        <v>4663.02442972373</v>
+        <v>4717.269343046964</v>
       </c>
       <c r="E341" t="n">
-        <v>4598.94677734375</v>
+        <v>4616.73388671875</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
-        <v>46256</v>
+        <v>46261</v>
       </c>
       <c r="B342" t="n">
-        <v>4513.95246030531</v>
+        <v>4543.767824938695</v>
       </c>
       <c r="C342" t="n">
-        <v>4347.335369072631</v>
+        <v>4374.063728600685</v>
       </c>
       <c r="D342" t="n">
-        <v>4684.999887159718</v>
+        <v>4701.651352544811</v>
       </c>
       <c r="E342" t="n">
-        <v>4586.66064453125</v>
+        <v>4588.3125</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
-        <v>46257</v>
+        <v>46262</v>
       </c>
       <c r="B343" t="n">
-        <v>4521.347727521553</v>
+        <v>4535.156753392384</v>
       </c>
       <c r="C343" t="n">
-        <v>4345.429112930397</v>
+        <v>4371.071855907758</v>
       </c>
       <c r="D343" t="n">
-        <v>4704.288597126954</v>
+        <v>4705.846114506525</v>
       </c>
       <c r="E343" t="n">
-        <v>4611.45068359375</v>
+        <v>4462.6953125</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
-        <v>46258</v>
+        <v>46263</v>
       </c>
       <c r="B344" t="n">
-        <v>4543.394588603361</v>
+        <v>4532.027504873186</v>
       </c>
       <c r="C344" t="n">
-        <v>4375.756914926986</v>
+        <v>4358.52480811281</v>
       </c>
       <c r="D344" t="n">
-        <v>4714.443459353639</v>
+        <v>4700.741319492494</v>
       </c>
       <c r="E344" t="n">
-        <v>4671.80908203125</v>
+        <v>4464.5947265625</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
-        <v>46259</v>
+        <v>46264</v>
       </c>
       <c r="B345" t="n">
-        <v>4543.254164605757</v>
+        <v>4521.479538906529</v>
       </c>
       <c r="C345" t="n">
-        <v>4376.533830441891</v>
+        <v>4355.136353100354</v>
       </c>
       <c r="D345" t="n">
-        <v>4713.315901850211</v>
+        <v>4706.963632191878</v>
       </c>
       <c r="E345" t="n">
-        <v>4648.12109375</v>
+        <v>4447.748046875</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="B346" t="n">
-        <v>4561.28998624868</v>
+        <v>4526.18805077359</v>
       </c>
       <c r="C346" t="n">
-        <v>4387.691033456206</v>
+        <v>4371.055204603796</v>
       </c>
       <c r="D346" t="n">
-        <v>4738.0541532259</v>
+        <v>4705.201362481695</v>
       </c>
       <c r="E346" t="n">
-        <v>4616.73388671875</v>
+        <v>4447.16064453125</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
-        <v>46261</v>
+        <v>46266</v>
       </c>
       <c r="B347" t="n">
-        <v>4551.043550314837</v>
+        <v>4506.974394183299</v>
       </c>
       <c r="C347" t="n">
-        <v>4380.126311046817</v>
+        <v>4332.205033243695</v>
       </c>
       <c r="D347" t="n">
-        <v>4718.317359032593</v>
+        <v>4678.259664118666</v>
       </c>
       <c r="E347" t="n">
-        <v>4588.3125</v>
+        <v>4339.46044921875</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
-        <v>46262</v>
+        <v>46267</v>
       </c>
       <c r="B348" t="n">
-        <v>4544.118074509114</v>
+        <v>4507.301097343913</v>
       </c>
       <c r="C348" t="n">
-        <v>4376.624685353178</v>
+        <v>4340.273351191202</v>
       </c>
       <c r="D348" t="n">
-        <v>4714.044031213346</v>
+        <v>4668.132232995484</v>
       </c>
       <c r="E348" t="n">
-        <v>4462.6953125</v>
+        <v>4393.13720703125</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
-        <v>46263</v>
+        <v>46268</v>
       </c>
       <c r="B349" t="n">
-        <v>4542.073667065142</v>
+        <v>4483.885106866873</v>
       </c>
       <c r="C349" t="n">
-        <v>4374.084736324652</v>
+        <v>4311.373902587491</v>
       </c>
       <c r="D349" t="n">
-        <v>4715.196632771416</v>
+        <v>4647.733485187567</v>
       </c>
       <c r="E349" t="n">
-        <v>4464.5947265625</v>
+        <v>4479.80419921875</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
-        <v>46264</v>
+        <v>46269</v>
       </c>
       <c r="B350" t="n">
-        <v>4532.414890140863</v>
+        <v>4461.328870593958</v>
       </c>
       <c r="C350" t="n">
-        <v>4376.366608866166</v>
+        <v>4291.881785874578</v>
       </c>
       <c r="D350" t="n">
-        <v>4720.255918539502</v>
+        <v>4627.740003829483</v>
       </c>
       <c r="E350" t="n">
-        <v>4447.748046875</v>
+        <v>4432.97021484375</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
-        <v>46265</v>
+        <v>46270</v>
       </c>
       <c r="B351" t="n">
-        <v>4536.881783280534</v>
+        <v>4445.538229677152</v>
       </c>
       <c r="C351" t="n">
-        <v>4358.993526579914</v>
+        <v>4281.966925455273</v>
       </c>
       <c r="D351" t="n">
-        <v>4702.847485531868</v>
+        <v>4622.944935590644</v>
       </c>
       <c r="E351" t="n">
-        <v>4447.16064453125</v>
+        <v>4432.44287109375</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
-        <v>46266</v>
+        <v>46271</v>
       </c>
       <c r="B352" t="n">
-        <v>4518.903960313193</v>
+        <v>4423.894566027581</v>
       </c>
       <c r="C352" t="n">
-        <v>4361.16270650802</v>
+        <v>4256.711578123516</v>
       </c>
       <c r="D352" t="n">
-        <v>4704.432676867425</v>
+        <v>4585.489686508415</v>
       </c>
       <c r="E352" t="n">
-        <v>4339.46044921875</v>
+        <v>4420.9033203125</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="n">
-        <v>46267</v>
+        <v>46272</v>
       </c>
       <c r="B353" t="n">
-        <v>4519.137847613928</v>
+        <v>4419.337738236415</v>
       </c>
       <c r="C353" t="n">
-        <v>4351.86920442147</v>
+        <v>4243.316081513246</v>
       </c>
       <c r="D353" t="n">
-        <v>4691.447826082721</v>
+        <v>4587.142748314321</v>
       </c>
       <c r="E353" t="n">
-        <v>4393.13720703125</v>
+        <v>4421.685546875</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B354" t="n">
-        <v>4491.436543583772</v>
+        <v>4392.929438576005</v>
       </c>
       <c r="C354" t="n">
-        <v>4317.58265623579</v>
+        <v>4219.140568027321</v>
       </c>
       <c r="D354" t="n">
-        <v>4662.646283170956</v>
+        <v>4563.026949555678</v>
       </c>
       <c r="E354" t="n">
-        <v>4479.80419921875</v>
+        <v>4355.5458984375</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="B355" t="n">
-        <v>4467.727048979804</v>
+        <v>4388.341435365024</v>
       </c>
       <c r="C355" t="n">
-        <v>4302.315296603789</v>
+        <v>4219.614996711957</v>
       </c>
       <c r="D355" t="n">
-        <v>4633.113918587128</v>
+        <v>4566.794167894131</v>
       </c>
       <c r="E355" t="n">
-        <v>4432.97021484375</v>
+        <v>4393.83203125</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
-        <v>46270</v>
+        <v>46275</v>
       </c>
       <c r="B356" t="n">
-        <v>4449.898238671136</v>
+        <v>4362.462533959658</v>
       </c>
       <c r="C356" t="n">
-        <v>4280.84425910451</v>
+        <v>4188.512585640961</v>
       </c>
       <c r="D356" t="n">
-        <v>4615.278046751862</v>
+        <v>4532.239884573591</v>
       </c>
       <c r="E356" t="n">
-        <v>4432.44287109375</v>
+        <v>4319.04443359375</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
-        <v>46271</v>
+        <v>46276</v>
       </c>
       <c r="B357" t="n">
-        <v>4425.780733250973</v>
+        <v>4340.024058580331</v>
       </c>
       <c r="C357" t="n">
-        <v>4249.737727722972</v>
+        <v>4168.615778230317</v>
       </c>
       <c r="D357" t="n">
-        <v>4589.803955008905</v>
+        <v>4509.149141003276</v>
       </c>
       <c r="E357" t="n">
-        <v>4420.9033203125</v>
+        <v>4354.66845703125</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="B358" t="n">
-        <v>4417.429936458208</v>
+        <v>4327.01300285273</v>
       </c>
       <c r="C358" t="n">
-        <v>4238.041258329063</v>
+        <v>4167.68550174831</v>
       </c>
       <c r="D358" t="n">
-        <v>4575.922958603126</v>
+        <v>4498.62469476266</v>
       </c>
       <c r="E358" t="n">
-        <v>4421.685546875</v>
+        <v>4354.5498046875</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="B359" t="n">
-        <v>4388.572066220111</v>
+        <v>4310.840453599447</v>
       </c>
       <c r="C359" t="n">
-        <v>4223.919727170995</v>
+        <v>4131.713195157688</v>
       </c>
       <c r="D359" t="n">
-        <v>4555.850290352464</v>
+        <v>4484.239737124817</v>
       </c>
       <c r="E359" t="n">
-        <v>4355.5458984375</v>
+        <v>4336.236328125</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="B360" t="n">
-        <v>4380.133470379593</v>
+        <v>4314.421955166188</v>
       </c>
       <c r="C360" t="n">
-        <v>4215.462616163056</v>
+        <v>4154.788948305649</v>
       </c>
       <c r="D360" t="n">
-        <v>4553.077515093383</v>
+        <v>4490.215677367391</v>
       </c>
       <c r="E360" t="n">
-        <v>4393.83203125</v>
+        <v>4294.3330078125</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="B361" t="n">
-        <v>4346.202932355749</v>
+        <v>4298.739552350818</v>
       </c>
       <c r="C361" t="n">
-        <v>4179.784430974398</v>
+        <v>4126.941539519079</v>
       </c>
       <c r="D361" t="n">
-        <v>4520.092612178031</v>
+        <v>4466.025008367601</v>
       </c>
       <c r="E361" t="n">
-        <v>4319.04443359375</v>
+        <v>4284.474609375</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="B362" t="n">
-        <v>4318.901937393771</v>
+        <v>4307.330049250087</v>
       </c>
       <c r="C362" t="n">
-        <v>4152.949839731677</v>
+        <v>4144.448878239937</v>
       </c>
       <c r="D362" t="n">
-        <v>4494.845623532009</v>
+        <v>4462.930914421953</v>
       </c>
       <c r="E362" t="n">
-        <v>4354.66845703125</v>
+        <v>4274.7861328125</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
-        <v>46277</v>
+        <v>46282</v>
       </c>
       <c r="B363" t="n">
-        <v>4300.266480026568</v>
+        <v>4296.893355057007</v>
       </c>
       <c r="C363" t="n">
-        <v>4136.580191297728</v>
+        <v>4127.729778648242</v>
       </c>
       <c r="D363" t="n">
-        <v>4456.869323544933</v>
+        <v>4467.258064458901</v>
       </c>
       <c r="E363" t="n">
-        <v>4354.5498046875</v>
+        <v>4343.3779296875</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
-        <v>46278</v>
+        <v>46283</v>
       </c>
       <c r="B364" t="n">
-        <v>4278.221763860216</v>
+        <v>4291.920719701823</v>
       </c>
       <c r="C364" t="n">
-        <v>4114.115758367911</v>
+        <v>4115.886535133709</v>
       </c>
       <c r="D364" t="n">
-        <v>4438.83612017717</v>
+        <v>4468.414312132101</v>
       </c>
       <c r="E364" t="n">
-        <v>4336.236328125</v>
+        <v>4368.39892578125</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
-        <v>46279</v>
+        <v>46284</v>
       </c>
       <c r="B365" t="n">
-        <v>4274.861228969214</v>
+        <v>4298.111970030418</v>
       </c>
       <c r="C365" t="n">
-        <v>4099.159015676522</v>
+        <v>4133.982094762867</v>
       </c>
       <c r="D365" t="n">
-        <v>4452.005377616013</v>
+        <v>4464.578815858745</v>
       </c>
       <c r="E365" t="n">
-        <v>4294.3330078125</v>
+        <v>4364.8544921875</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B366" t="n">
-        <v>4253.889875309868</v>
+        <v>4327.784005607423</v>
       </c>
       <c r="C366" t="n">
-        <v>4079.842356526417</v>
+        <v>4148.205680598714</v>
       </c>
       <c r="D366" t="n">
-        <v>4433.607345759039</v>
+        <v>4505.959620951727</v>
       </c>
       <c r="E366" t="n">
-        <v>4284.474609375</v>
+        <v>4363.64013671875</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="B367" t="n">
-        <v>4256.152280460574</v>
+        <v>4334.406255267996</v>
       </c>
       <c r="C367" t="n">
-        <v>4102.824333573173</v>
+        <v>4155.25111942821</v>
       </c>
       <c r="D367" t="n">
-        <v>4430.535494838807</v>
-      </c>
-      <c r="E367" t="n">
-        <v>4330.77001953125</v>
-      </c>
+        <v>4502.3170571542</v>
+      </c>
+      <c r="E367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="B368" t="n">
-        <v>4235.595087114642</v>
+        <v>4365.541429802314</v>
       </c>
       <c r="C368" t="n">
-        <v>4055.272795763664</v>
+        <v>4194.743577142577</v>
       </c>
       <c r="D368" t="n">
-        <v>4409.792858244292</v>
+        <v>4531.834708815064</v>
       </c>
       <c r="E368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="B369" t="n">
-        <v>4224.138961420169</v>
+        <v>4377.467531337386</v>
       </c>
       <c r="C369" t="n">
-        <v>4047.839476645354</v>
+        <v>4212.068432225424</v>
       </c>
       <c r="D369" t="n">
-        <v>4384.226875606212</v>
+        <v>4541.063088058441</v>
       </c>
       <c r="E369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B370" t="n">
-        <v>4223.563591933389</v>
+        <v>4394.252746156916</v>
       </c>
       <c r="C370" t="n">
-        <v>4049.960361888883</v>
+        <v>4228.773138303145</v>
       </c>
       <c r="D370" t="n">
-        <v>4391.76262998272</v>
+        <v>4561.865027241952</v>
       </c>
       <c r="E370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
-        <v>46285</v>
+        <v>46291</v>
       </c>
       <c r="B371" t="n">
-        <v>4221.487027784839</v>
+        <v>4421.182202650097</v>
       </c>
       <c r="C371" t="n">
-        <v>4044.830882477185</v>
+        <v>4249.936378885952</v>
       </c>
       <c r="D371" t="n">
-        <v>4389.162871004505</v>
+        <v>4589.166194344299</v>
       </c>
       <c r="E371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
-        <v>46286</v>
+        <v>46292</v>
       </c>
       <c r="B372" t="n">
-        <v>4239.650698010311</v>
+        <v>4444.941187090434</v>
       </c>
       <c r="C372" t="n">
-        <v>4068.450006731092</v>
+        <v>4279.394660004519</v>
       </c>
       <c r="D372" t="n">
-        <v>4411.167622890786</v>
+        <v>4613.308037972804</v>
       </c>
       <c r="E372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
-        <v>46287</v>
+        <v>46293</v>
       </c>
       <c r="B373" t="n">
-        <v>4241.369948343959</v>
+        <v>4487.711128849199</v>
       </c>
       <c r="C373" t="n">
-        <v>4074.530663846954</v>
+        <v>4324.956042151251</v>
       </c>
       <c r="D373" t="n">
-        <v>4416.831713595607</v>
+        <v>4664.115113945062</v>
       </c>
       <c r="E373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="B374" t="n">
-        <v>4267.070326077157</v>
+        <v>4509.747709209818</v>
       </c>
       <c r="C374" t="n">
-        <v>4082.572029295077</v>
+        <v>4337.725697988014</v>
       </c>
       <c r="D374" t="n">
-        <v>4435.596388291364</v>
+        <v>4677.788105749971</v>
       </c>
       <c r="E374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="B375" t="n">
-        <v>4270.259189369872</v>
+        <v>4553.885229241365</v>
       </c>
       <c r="C375" t="n">
-        <v>4103.324207030192</v>
+        <v>4378.372720219456</v>
       </c>
       <c r="D375" t="n">
-        <v>4434.658245412753</v>
+        <v>4723.722548582001</v>
       </c>
       <c r="E375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
-        <v>46290</v>
+        <v>46296</v>
       </c>
       <c r="B376" t="n">
-        <v>4282.407416938798</v>
+        <v>4576.160698873398</v>
       </c>
       <c r="C376" t="n">
-        <v>4110.513994998728</v>
+        <v>4414.69123067532</v>
       </c>
       <c r="D376" t="n">
-        <v>4463.90376185722</v>
+        <v>4730.886233033241</v>
       </c>
       <c r="E376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
-        <v>46291</v>
+        <v>46297</v>
       </c>
       <c r="B377" t="n">
-        <v>4304.844542617559</v>
+        <v>4600.457045389733</v>
       </c>
       <c r="C377" t="n">
-        <v>4132.762303252405</v>
+        <v>4426.443562472821</v>
       </c>
       <c r="D377" t="n">
-        <v>4474.40313598093</v>
+        <v>4755.234919637893</v>
       </c>
       <c r="E377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
-        <v>46292</v>
+        <v>46298</v>
       </c>
       <c r="B378" t="n">
-        <v>4324.748354663181</v>
+        <v>4631.934162857633</v>
       </c>
       <c r="C378" t="n">
-        <v>4158.886444714862</v>
+        <v>4462.701667813366</v>
       </c>
       <c r="D378" t="n">
-        <v>4486.151972343784</v>
+        <v>4792.276215334399</v>
       </c>
       <c r="E378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
-        <v>46293</v>
+        <v>46299</v>
       </c>
       <c r="B379" t="n">
-        <v>4363.440036709033</v>
+        <v>4657.21496956629</v>
       </c>
       <c r="C379" t="n">
-        <v>4194.910360398864</v>
+        <v>4489.905931167342</v>
       </c>
       <c r="D379" t="n">
-        <v>4539.064679248086</v>
+        <v>4825.003129824791</v>
       </c>
       <c r="E379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
-        <v>46294</v>
+        <v>46300</v>
       </c>
       <c r="B380" t="n">
-        <v>4383.844422636602</v>
+        <v>4698.482703950841</v>
       </c>
       <c r="C380" t="n">
-        <v>4203.75029161467</v>
+        <v>4534.76539800604</v>
       </c>
       <c r="D380" t="n">
-        <v>4555.697841387857</v>
+        <v>4861.200871142289</v>
       </c>
       <c r="E380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
-        <v>46295</v>
+        <v>46301</v>
       </c>
       <c r="B381" t="n">
-        <v>4426.035340375062</v>
+        <v>4716.058772798692</v>
       </c>
       <c r="C381" t="n">
-        <v>4250.963928249726</v>
+        <v>4551.624371818649</v>
       </c>
       <c r="D381" t="n">
-        <v>4607.708210801135</v>
+        <v>4880.51065213279</v>
       </c>
       <c r="E381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
-        <v>46296</v>
+        <v>46302</v>
       </c>
       <c r="B382" t="n">
-        <v>4443.215381070851</v>
+        <v>4752.905288997306</v>
       </c>
       <c r="C382" t="n">
-        <v>4283.090641241415</v>
+        <v>4582.585425119963</v>
       </c>
       <c r="D382" t="n">
-        <v>4606.93952032046</v>
+        <v>4932.715667325821</v>
       </c>
       <c r="E382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
-        <v>46297</v>
+        <v>46303</v>
       </c>
       <c r="B383" t="n">
-        <v>4466.604652086569</v>
+        <v>4765.245805155258</v>
       </c>
       <c r="C383" t="n">
-        <v>4297.128220425019</v>
+        <v>4591.807080028231</v>
       </c>
       <c r="D383" t="n">
-        <v>4641.889798990184</v>
+        <v>4935.47664333516</v>
       </c>
       <c r="E383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
-        <v>46298</v>
+        <v>46304</v>
       </c>
       <c r="B384" t="n">
-        <v>4497.341649579404</v>
+        <v>4777.203726907922</v>
       </c>
       <c r="C384" t="n">
-        <v>4326.09967028554</v>
+        <v>4607.092747988481</v>
       </c>
       <c r="D384" t="n">
-        <v>4664.249976268125</v>
+        <v>4946.526412909935</v>
       </c>
       <c r="E384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
-        <v>46299</v>
+        <v>46305</v>
       </c>
       <c r="B385" t="n">
-        <v>4522.477135970279</v>
+        <v>4794.227252245602</v>
       </c>
       <c r="C385" t="n">
-        <v>4350.390664895551</v>
+        <v>4615.395345245664</v>
       </c>
       <c r="D385" t="n">
-        <v>4685.608984969631</v>
+        <v>4965.538353083206</v>
       </c>
       <c r="E385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
-        <v>46300</v>
+        <v>46306</v>
       </c>
       <c r="B386" t="n">
-        <v>4563.271983343753</v>
+        <v>4803.268164688349</v>
       </c>
       <c r="C386" t="n">
-        <v>4396.865813763931</v>
+        <v>4627.215458537297</v>
       </c>
       <c r="D386" t="n">
-        <v>4737.681761693692</v>
+        <v>4970.214722195316</v>
       </c>
       <c r="E386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
-        <v>46301</v>
+        <v>46307</v>
       </c>
       <c r="B387" t="n">
-        <v>4582.65848133939</v>
+        <v>4826.87090310594</v>
       </c>
       <c r="C387" t="n">
-        <v>4421.861302131683</v>
+        <v>4649.765926550886</v>
       </c>
       <c r="D387" t="n">
-        <v>4754.199467395099</v>
+        <v>4993.717800214721</v>
       </c>
       <c r="E387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
-        <v>46302</v>
+        <v>46308</v>
       </c>
       <c r="B388" t="n">
-        <v>4620.785055242698</v>
+        <v>4825.741440619083</v>
       </c>
       <c r="C388" t="n">
-        <v>4446.068329277313</v>
+        <v>4651.380687045305</v>
       </c>
       <c r="D388" t="n">
-        <v>4785.979625425657</v>
+        <v>5004.121623412412</v>
       </c>
       <c r="E388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
-        <v>46303</v>
+        <v>46309</v>
       </c>
       <c r="B389" t="n">
-        <v>4630.99374683102</v>
+        <v>4843.240348739206</v>
       </c>
       <c r="C389" t="n">
-        <v>4452.576514287175</v>
+        <v>4671.531280900743</v>
       </c>
       <c r="D389" t="n">
-        <v>4802.442658929414</v>
+        <v>5012.214483402841</v>
       </c>
       <c r="E389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
-        <v>46304</v>
+        <v>46310</v>
       </c>
       <c r="B390" t="n">
-        <v>4644.705077678525</v>
+        <v>4835.99380559735</v>
       </c>
       <c r="C390" t="n">
-        <v>4480.23761176474</v>
+        <v>4663.057854013955</v>
       </c>
       <c r="D390" t="n">
-        <v>4812.95084681417</v>
+        <v>5008.178013747943</v>
       </c>
       <c r="E390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
-        <v>46305</v>
+        <v>46311</v>
       </c>
       <c r="B391" t="n">
-        <v>4663.313535469692</v>
+        <v>4828.522291149619</v>
       </c>
       <c r="C391" t="n">
-        <v>4499.995966482547</v>
+        <v>4656.13988013745</v>
       </c>
       <c r="D391" t="n">
-        <v>4827.536725664918</v>
+        <v>4992.512091065706</v>
       </c>
       <c r="E391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
-        <v>46306</v>
+        <v>46312</v>
       </c>
       <c r="B392" t="n">
-        <v>4674.174714167813</v>
+        <v>4826.6560740555</v>
       </c>
       <c r="C392" t="n">
-        <v>4505.104436146971</v>
+        <v>4659.112132051175</v>
       </c>
       <c r="D392" t="n">
-        <v>4853.170675837844</v>
+        <v>4993.579145717758</v>
       </c>
       <c r="E392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
-        <v>46307</v>
+        <v>46313</v>
       </c>
       <c r="B393" t="n">
-        <v>4698.895251344298</v>
+        <v>4817.705068421882</v>
       </c>
       <c r="C393" t="n">
-        <v>4523.313127231032</v>
+        <v>4636.829160597621</v>
       </c>
       <c r="D393" t="n">
-        <v>4859.629182031789</v>
+        <v>5000.502235851864</v>
       </c>
       <c r="E393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
-        <v>46308</v>
+        <v>46314</v>
       </c>
       <c r="B394" t="n">
-        <v>4700.785275182223</v>
+        <v>4824.539718534679</v>
       </c>
       <c r="C394" t="n">
-        <v>4532.231545994007</v>
+        <v>4647.549120148967</v>
       </c>
       <c r="D394" t="n">
-        <v>4871.848201583487</v>
+        <v>4987.404352337936</v>
       </c>
       <c r="E394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
-        <v>46309</v>
+        <v>46315</v>
       </c>
       <c r="B395" t="n">
-        <v>4720.393546512562</v>
+        <v>4808.152657629912</v>
       </c>
       <c r="C395" t="n">
-        <v>4539.489562424717</v>
+        <v>4647.286379713633</v>
       </c>
       <c r="D395" t="n">
-        <v>4889.998987836218</v>
+        <v>4993.797887855249</v>
       </c>
       <c r="E395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
-        <v>46310</v>
+        <v>46316</v>
       </c>
       <c r="B396" t="n">
-        <v>4711.474907070758</v>
+        <v>4812.145702752347</v>
       </c>
       <c r="C396" t="n">
-        <v>4534.147363650503</v>
+        <v>4645.535619359356</v>
       </c>
       <c r="D396" t="n">
-        <v>4878.181600087742</v>
+        <v>4993.824703430767</v>
       </c>
       <c r="E396" t="inlineStr"/>
-    </row>
-    <row r="397">
-      <c r="A397" s="1" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B397" t="n">
-        <v>4705.864924013026</v>
-      </c>
-      <c r="C397" t="n">
-        <v>4535.701511225338</v>
-      </c>
-      <c r="D397" t="n">
-        <v>4882.432441718302</v>
-      </c>
-      <c r="E397" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
